--- a/networkmap/data/contacts_all.xlsx
+++ b/networkmap/data/contacts_all.xlsx
@@ -19,14 +19,14 @@
     <sheet name="Roche-Genentech" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Contacts'!$A$1:$I$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AbbVie'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Contacts'!$A$1:$I$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AbbVie'!$A$1:$I$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AstraZeneca'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BMS'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BMS'!$A$1:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Eli Lilly'!$A$1:$I$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Johnson &amp; Johnson'!$A$1:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Novartis'!$A$1:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Novo Nordisk'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Novo Nordisk'!$A$1:$I$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Roche-Genentech'!$A$1:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>199 named contacts across 8 accounts. Tiers = influence over valve spec/procurement/lifecycle. Generated 2026-07-17.</t>
+          <t>205 named contacts across 8 accounts. Tiers = influence over valve spec/procurement/lifecycle. Generated 2026-07-17.</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
@@ -1728,7 +1728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2007,12 +2007,12 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Emilie Leonard</t>
+          <t>Elvir J.</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Head of MSAT</t>
+          <t>Category Manager, Capital Projects (Pharmaceutical)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Talence, Nouvelle-Aquitaine, France (Europe)</t>
+          <t>Niles, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Procurement (Capital Projects)</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -2043,19 +2043,19 @@
       <c r="H7" s="13" t="inlineStr"/>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Gerard McWalter</t>
+          <t>Emilie Leonard</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Head of MSAT</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>County Mayo, Ireland (Europe)</t>
+          <t>Talence, Nouvelle-Aquitaine, France (Europe)</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -2086,19 +2086,19 @@
       <c r="H8" s="13" t="inlineStr"/>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Grégory Capdepuy</t>
+          <t>Gerard McWalter</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Head of Manufacturing and MSAT department</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Martillac, Nouvelle-Aquitaine, France (Europe)</t>
+          <t>County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing / MSAT</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -2129,19 +2129,19 @@
       <c r="H9" s="13" t="inlineStr"/>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Joe Brodt</t>
+          <t>Grégory Capdepuy</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Business Excellence</t>
+          <t>Head of Manufacturing and MSAT department</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Greater Chicago Area</t>
+          <t>Martillac, Nouvelle-Aquitaine, France (Europe)</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Manufacturing / MSAT</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -2172,19 +2172,19 @@
       <c r="H10" s="13" t="inlineStr"/>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Malcolm Garde</t>
+          <t>Joe Brodt</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Site Director, AbbVie Cork (Carrigtwohill)</t>
+          <t>Associate Director, Business Excellence</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -2199,35 +2199,35 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Carrigtwohill (Cork), Ireland (Europe)</t>
+          <t>Greater Chicago Area</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr"/>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Mark Shannon</t>
+          <t>Malcolm Garde</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Director, MSAT</t>
+          <t>Site Director, AbbVie Cork (Carrigtwohill)</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -2242,35 +2242,35 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston (US)</t>
+          <t>Carrigtwohill (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr"/>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Richard Harrington</t>
+          <t>Mark Shannon</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Capital Projects Engineering Manager</t>
+          <t>Director, MSAT</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Dublin 17, County Dublin, Ireland (Europe)</t>
+          <t>Greater Boston (US)</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -2301,19 +2301,19 @@
       <c r="H13" s="13" t="inlineStr"/>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Simon Kuehbauch</t>
+          <t>Richard Harrington</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer Pilot Plants</t>
+          <t>Capital Projects Engineering Manager</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Ketsch, Baden-Württemberg, Germany (Europe)</t>
+          <t>Dublin 17, County Dublin, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -2344,19 +2344,19 @@
       <c r="H14" s="13" t="inlineStr"/>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Titi Adeyemi</t>
+          <t>Simon Kuehbauch</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Project Engineer Pilot Plants</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Lincolnshire, Illinois, United States (US)</t>
+          <t>Ketsch, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -2387,19 +2387,19 @@
       <c r="H15" s="13" t="inlineStr"/>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Victor Lee</t>
+          <t>Titi Adeyemi</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer, Global Packaging</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Greater Chicago Area</t>
+          <t>Lincolnshire, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -2430,19 +2430,19 @@
       <c r="H16" s="13" t="inlineStr"/>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Xiaobei Zeng</t>
+          <t>Victor Lee</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Director, MSAT</t>
+          <t>Senior Project Engineer, Global Packaging</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Greater Chicago Area</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -2473,24 +2473,24 @@
       <c r="H17" s="13" t="inlineStr"/>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Andy Wigley</t>
+          <t>Xiaobei Zeng</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Director, MSAT</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Stockport, England, United Kingdom (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -2516,19 +2516,19 @@
       <c r="H18" s="13" t="inlineStr"/>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Chris Leman</t>
+          <t>Andy Wigley</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Global C&amp;Q Director</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom (Europe)</t>
+          <t>Stockport, England, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Global)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -2566,12 +2566,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Desmond Madden</t>
+          <t>Chris Leman</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Global C&amp;Q Director</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering / C&amp;Q (Global)</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
@@ -2609,12 +2609,12 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Hanae BELAHBIB</t>
+          <t>Desmond Madden</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Ingénieur projets</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Paris, Île-de-France, France (Europe)</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -2652,12 +2652,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Mark Benesch</t>
+          <t>Hanae BELAHBIB</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Capital Projects Portfolio - Americas</t>
+          <t>Ingénieur projets</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Catonsville, Maryland, United States (US)</t>
+          <t>Paris, Île-de-France, France (Europe)</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -2688,19 +2688,19 @@
       <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Praneet Muktineni</t>
+          <t>Mark Benesch</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Senior Director, Capital Projects Portfolio - Americas</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Frederick, Maryland, United States (US)</t>
+          <t>Catonsville, Maryland, United States (US)</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -2731,19 +2731,19 @@
       <c r="H23" s="13" t="inlineStr"/>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Rob Goldstraw</t>
+          <t>Praneet Muktineni</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Macclesfield, England, United Kingdom (Europe)</t>
+          <t>Frederick, Maryland, United States (US)</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Simon Goldfarb</t>
+          <t>Rob Goldstraw</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Head of Capital Projects</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Emsworth, England, United Kingdom (Europe)</t>
+          <t>Macclesfield, England, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -2817,19 +2817,19 @@
       <c r="H25" s="13" t="inlineStr"/>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Stuart Cameron</t>
+          <t>Simon Goldfarb</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q/CSV Manager (Projects)</t>
+          <t>Head of Capital Projects</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Birmingham, England, United Kingdom (Europe)</t>
+          <t>Emsworth, England, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="H26" s="13" t="inlineStr"/>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Tobi Ogunribido</t>
+          <t>Stuart Cameron</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>C&amp;Q/CSV Manager (Projects)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Macclesfield, England, United Kingdom (Europe)</t>
+          <t>Birmingham, England, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -2910,17 +2910,17 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Andrew Chaffkin</t>
+          <t>Tobi Ogunribido</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Associate Director - MSAT Compliance &amp; Investigations</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Greater Seattle Area (US)</t>
+          <t>Macclesfield, England, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
@@ -2946,19 +2946,19 @@
       <c r="H28" s="13" t="inlineStr"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>Anna Smyth</t>
+          <t>Andrew Chaffkin</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Senior Specialist, CQV Engineer</t>
+          <t>Associate Director - MSAT Compliance &amp; Investigations</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Dublin, County Dublin, Ireland (Europe)</t>
+          <t>Greater Seattle Area (US)</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
@@ -2989,19 +2989,19 @@
       <c r="H29" s="13" t="inlineStr"/>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Bruno Sequeira</t>
+          <t>Anna Smyth</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Commissioning, Qualification and Validation (CQV)</t>
+          <t>Senior Specialist, CQV Engineer</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Bern, Switzerland (Europe)</t>
+          <t>Dublin, County Dublin, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -3039,12 +3039,12 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Daniel Post</t>
+          <t>Bruno Sequeira</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Technical Services Engineering</t>
+          <t>Commissioning, Qualification and Validation (CQV)</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -3059,35 +3059,35 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>Bern, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects / Utilities)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr"/>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>Fabio Lastrucci</t>
+          <t>Daniel Post</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead</t>
+          <t>Associate Director, Technical Services Engineering</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -3102,35 +3102,35 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Solothurn, Switzerland (Europe)</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects / Utilities)</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr"/>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Falguni Patel</t>
+          <t>Eoin Howard</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, MSAT Process Engineering</t>
+          <t>CQV Lead (Formulation &amp; Component Prep)</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -3145,12 +3145,12 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston (US)</t>
+          <t>Navan, County Meath, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -3161,19 +3161,19 @@
       <c r="H33" s="13" t="inlineStr"/>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>Felix Butkevich</t>
+          <t>Fabio Lastrucci</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, CQV</t>
+          <t>CQV Lead</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Solothurn, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>Jamie McDonald</t>
+          <t>Falguni Patel</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Capital Projects Manager</t>
+          <t>Associate Director, MSAT Process Engineering</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>MSAT / Process Engineering</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -3247,19 +3247,19 @@
       <c r="H35" s="13" t="inlineStr"/>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Joel Garcia</t>
+          <t>Felix Butkevich</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Senior Manager- CTO Capital Projects</t>
+          <t>Associate Director, CQV</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Caldwell, New Jersey, United States (US)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
@@ -3290,19 +3290,19 @@
       <c r="H36" s="13" t="inlineStr"/>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>Joel Garcia, PMP</t>
+          <t>Jamie McDonald</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Senior Manager - CTO Capital Projects</t>
+          <t>Capital Projects Manager</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Caldwell, New Jersey, United States (US)</t>
+          <t>Greater Boston (US)</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -3340,12 +3340,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Lisa Martins</t>
+          <t>Joel Garcia</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Senior Manager, Capital Projects</t>
+          <t>Senior Manager- CTO Capital Projects</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>Upton, Massachusetts, United States</t>
+          <t>Caldwell, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -3383,12 +3383,12 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Melissa I. Jiménez</t>
+          <t>Joel Garcia, PMP</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Buyer: Capital Projects and Compliance</t>
+          <t>Senior Manager - CTO Capital Projects</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Caldwell, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -3426,12 +3426,12 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>Odile Smith</t>
+          <t>Lisa Martins</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Vice President &amp; Devens Campus Lead</t>
+          <t>Senior Manager, Capital Projects</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
@@ -3446,35 +3446,35 @@
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>Upton, Massachusetts, United States</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr"/>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Padraig Keane</t>
+          <t>Mahesh S.</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Vice President &amp; General Manager, Cruiserath Biologics Campus</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -3489,35 +3489,35 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Cruiserath (Dublin), Ireland (Europe)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr"/>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>Piero Malaspina</t>
+          <t>Melissa I. Jiménez</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Process Lead</t>
+          <t>Buyer: Capital Projects and Compliance</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Grenchen, Solothurn, Switzerland (Europe)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -3548,19 +3548,19 @@
       <c r="H42" s="13" t="inlineStr"/>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Raymond Matos</t>
+          <t>Odile Smith</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Senior C&amp;Q Consultant</t>
+          <t>Vice President &amp; Devens Campus Lead</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -3575,35 +3575,35 @@
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Manati, Puerto Rico (US)</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr"/>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>Roe Hau</t>
+          <t>Padraig Keane</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Director, MSAT Process Engineering</t>
+          <t>Vice President &amp; General Manager, Cruiserath Biologics Campus</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -3618,35 +3618,35 @@
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Cruiserath (Dublin), Ireland (Europe)</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Engineering</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr"/>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Rémy Pereira</t>
+          <t>Piero Malaspina</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Senior IT Manufacturing Engineer C&amp;Q</t>
+          <t>C&amp;Q Process Lead</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>Marin-Epagnier, Neuchâtel, Switzerland (Europe)</t>
+          <t>Grenchen, Solothurn, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (IT)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
@@ -3684,12 +3684,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Troy M</t>
+          <t>Rachel Miles</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Manager, Maintenance</t>
+          <t>Director of Capital Projects</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>Westminster, Massachusetts, United States</t>
+          <t>Manteno, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
@@ -3720,24 +3720,24 @@
       <c r="H46" s="13" t="inlineStr"/>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Alessandro Massimo Carassai</t>
+          <t>Raymond Matos</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>CQV Project Lead</t>
+          <t>Senior C&amp;Q Consultant</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>Italy (Europe)</t>
+          <t>Manati, Puerto Rico (US)</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -3770,17 +3770,17 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Bryan Trapp</t>
+          <t>Roe Hau</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>LP1 Maintenance Manager</t>
+          <t>Director, MSAT Process Engineering</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>Lafayette, Indiana, United States (US)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT / Process Engineering</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr">
@@ -3806,24 +3806,24 @@
       <c r="H48" s="13" t="inlineStr"/>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Carolina Serrano Martinez</t>
+          <t>Rémy Pereira</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Operations Improvement Engineer</t>
+          <t>Senior IT Manufacturing Engineer C&amp;Q</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>US (Great Lakes region)</t>
+          <t>Marin-Epagnier, Neuchâtel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Operations Improvement)</t>
+          <t>Engineering / C&amp;Q (IT)</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Dave Riordan</t>
+          <t>Troy M</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; Site Head, Lilly Limerick</t>
+          <t>Manager, Maintenance</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
@@ -3876,35 +3876,35 @@
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>Limerick, Ireland (Europe)</t>
+          <t>Westminster, Massachusetts, United States</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership (Capital Project)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr"/>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Dean F.</t>
+          <t>Alessandro Massimo Carassai</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>CQV Project Lead</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Germany (Europe)</t>
+          <t>Italy (Europe)</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -3942,12 +3942,12 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Dermot Cawley</t>
+          <t>Bryan Trapp</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>LP1 Maintenance Manager</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Lafayette, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -3978,19 +3978,19 @@
       <c r="H52" s="13" t="inlineStr"/>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Eamon Davern</t>
+          <t>Carolina Serrano Martinez</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>BMS/QBMS CQV Engineer</t>
+          <t>Operations Improvement Engineer</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Mainz, Rhineland-Palatinate, Germany (Europe)</t>
+          <t>US (Great Lakes region)</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Operations Improvement)</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr"/>
@@ -4028,12 +4028,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Eamon Judge</t>
+          <t>Dave Riordan</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>EMEA Major Project Planning Leader</t>
+          <t>VP &amp; Site Head, Lilly Limerick</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>Ireland (EMEA) (Europe)</t>
+          <t>Limerick, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Project Planning)</t>
+          <t>Site Leadership (Capital Project)</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>Edwin Bosshart</t>
+          <t>Dean F.</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Whitestown, Indiana, United States (US)</t>
+          <t>Germany (Europe)</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -4107,19 +4107,19 @@
       <c r="H55" s="13" t="inlineStr"/>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Eliyes A.</t>
+          <t>Dermot Cawley</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Senior C&amp;Q Engineer</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>Greater Strasbourg Metropolitan Area (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -4157,12 +4157,12 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>Felipe Rivera-Monserrate</t>
+          <t>Eamon Davern</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineering Automation Owner's Representative</t>
+          <t>BMS/QBMS CQV Engineer</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Mainz, Rhineland-Palatinate, Germany (Europe)</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Automation)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
@@ -4200,12 +4200,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Frank A Glad</t>
+          <t>Eamon Judge</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Manager of Engineering</t>
+          <t>EMEA Major Project Planning Leader</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -4220,35 +4220,35 @@
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>Indianapolis, Indiana, United States (US)</t>
+          <t>Ireland (EMEA) (Europe)</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (Capital Project Planning)</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr"/>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>Hafid Gomez Rodriguez</t>
+          <t>Edwin Bosshart</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Senior C&amp;Q Engineer</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>Carmel, Indiana, United States (US)</t>
+          <t>Whitestown, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
@@ -4279,19 +4279,19 @@
       <c r="H59" s="13" t="inlineStr"/>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Himanshu Sharma</t>
+          <t>Eliyes A.</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q</t>
+          <t>Senior C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>Dublin, County Dublin, Ireland (Europe)</t>
+          <t>Greater Strasbourg Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -4329,12 +4329,12 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>Jamie Hodnett</t>
+          <t>Felipe Rivera-Monserrate</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>Commissioning Engineer</t>
+          <t>CQV Engineering Automation Owner's Representative</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering / C&amp;Q (Automation)</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -4372,12 +4372,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>John Hillmer</t>
+          <t>Frank A Glad</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Major Capital Projects Procurement Lead</t>
+          <t>Manager of Engineering</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Atlanta Metropolitan Area (US)</t>
+          <t>Indianapolis, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects) / Procurement</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
@@ -4408,19 +4408,19 @@
       <c r="H62" s="13" t="inlineStr"/>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Jorge Paraliticci</t>
+          <t>Hafid Gomez Rodriguez</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Sr. Project Engineer</t>
+          <t>Senior C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Carmel, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
@@ -4458,12 +4458,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>Karl Johnson</t>
+          <t>Himanshu Sharma</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Sr. Project Engineer</t>
+          <t>C&amp;Q</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Dublin, County Dublin, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>Karthick Pachaiyappan</t>
+          <t>Jamie Hodnett</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Project DeltaV Engineer</t>
+          <t>Commissioning Engineer</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>Limerick, County Limerick, Ireland (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
@@ -4544,12 +4544,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Keerthi Reddy Saripalli</t>
+          <t>John Hillmer</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Sr Principal Engineer - Major Capital Projects &amp; PMO</t>
+          <t>Major Capital Projects Procurement Lead</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Atlanta Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Capital Projects) / Procurement</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
@@ -4580,19 +4580,19 @@
       <c r="H66" s="13" t="inlineStr"/>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Keith Weseli</t>
+          <t>Jorge Paraliticci</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Advisor - Program Manager</t>
+          <t>Sr. Project Engineer</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
@@ -4607,24 +4607,20 @@
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>Engineering / Program Management (Aseptic)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H67" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Aseptic Conference 2026 (Conference Chair)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr"/>
       <c r="I67" s="14" t="inlineStr">
         <is>
           <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
@@ -4634,12 +4630,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>Kenneth Swank</t>
+          <t>Karl Johnson</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Sr. Director - Major Capital Projects</t>
+          <t>Sr. Project Engineer</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -4654,12 +4650,12 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>Greenwood, Indiana, United States (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
@@ -4670,19 +4666,19 @@
       <c r="H68" s="13" t="inlineStr"/>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>Keshav Jha</t>
+          <t>Karthick Pachaiyappan</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Project DeltaV Engineer</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -4697,12 +4693,12 @@
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Limerick, County Limerick, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
@@ -4720,12 +4716,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Kieran Houlihan</t>
+          <t>Keerthi Reddy Saripalli</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Senior CQV Engineer</t>
+          <t>Sr Principal Engineer - Major Capital Projects &amp; PMO</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -4740,12 +4736,12 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
@@ -4756,19 +4752,19 @@
       <c r="H70" s="13" t="inlineStr"/>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Kofi Appiah-Nkansah</t>
+          <t>Keith Weseli</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Technical Services / Mfg Science (MSAT)</t>
+          <t>Advisor - Program Manager</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -4783,35 +4779,39 @@
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Services</t>
+          <t>Engineering / Program Management (Aseptic)</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H71" s="13" t="inlineStr"/>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Aseptic Conference 2026 (Conference Chair)</t>
+        </is>
+      </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>Matthew von Zirkelbach</t>
+          <t>Kenneth Swank</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Vice President &amp; Site Head, Lilly Medicine Foundry (Lebanon)</t>
+          <t>Sr. Director - Major Capital Projects</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, IN (US)</t>
+          <t>Greenwood, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership (Capital Project)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr"/>
@@ -4849,12 +4849,12 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Murielle Pernel</t>
+          <t>Keshav Jha</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>Sr Principal Scientist (MSAT process expert)</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Geispolsheim, Grand Est, France (Europe)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Expert</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -4885,19 +4885,19 @@
       <c r="H73" s="13" t="inlineStr"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>Nitu Gupta</t>
+          <t>Kieran Houlihan</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Advisor -Engineering Projects/ Capital Steward</t>
+          <t>Senior CQV Engineer</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
@@ -4935,12 +4935,12 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Orlagh Moran</t>
+          <t>Kofi Appiah-Nkansah</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>EHS Lead Construction &amp; C&amp;Q</t>
+          <t>Associate Director, Technical Services / Mfg Science (MSAT)</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Germany (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>MSAT / Technical Services</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
@@ -4971,19 +4971,19 @@
       <c r="H75" s="13" t="inlineStr"/>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>Patrick Harnedy</t>
+          <t>Matthew von Zirkelbach</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>Senior Principal Engineer</t>
+          <t>Vice President &amp; Site Head, Lilly Medicine Foundry (Lebanon)</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Lebanon, IN (US)</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Site Leadership (Capital Project)</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -5011,26 +5011,22 @@
           <t>Public research</t>
         </is>
       </c>
-      <c r="H76" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
-        </is>
-      </c>
+      <c r="H76" s="13" t="inlineStr"/>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Paul Linehan</t>
+          <t>Murielle Pernel</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Engineer - C&amp;Q Strategy</t>
+          <t>Sr Principal Scientist (MSAT process expert)</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -5045,12 +5041,12 @@
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Geispolsheim, Grand Est, France (Europe)</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>MSAT / Process Expert</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
@@ -5061,19 +5057,19 @@
       <c r="H77" s="13" t="inlineStr"/>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>Paul McGinley</t>
+          <t>Nitu Gupta</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead</t>
+          <t>Advisor -Engineering Projects/ Capital Steward</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -5088,12 +5084,12 @@
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>Kilbirnie, Scotland, United Kingdom (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
@@ -5111,12 +5107,12 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>Puja Tanwani</t>
+          <t>Orlagh Moran</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Associate Director - Process Design (Global Engineering Capital Projects)</t>
+          <t>EHS Lead Construction &amp; C&amp;Q</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -5131,12 +5127,12 @@
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Germany (Europe)</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects / Process Design)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -5154,12 +5150,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>Rick Rowe</t>
+          <t>Patrick Harnedy</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Project Manager, Eli Lilly</t>
+          <t>Senior Principal Engineer</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -5174,35 +5170,39 @@
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>Bargersville, Indiana, United States (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F80" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Project / PM)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H80" s="13" t="inlineStr"/>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+        </is>
+      </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>Robert O'Keeffe</t>
+          <t>Paul Linehan</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Engineering Tech Centre</t>
+          <t>Engineer - C&amp;Q Strategy</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Limerick NGB) (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -5227,14 +5227,10 @@
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H81" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H81" s="13" t="inlineStr"/>
       <c r="I81" s="14" t="inlineStr">
         <is>
           <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
@@ -5244,12 +5240,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>Sasha Adib-Yaghmai</t>
+          <t>Paul McGinley</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>NPI Engineer – Capital Projects &amp; Operational Readiness</t>
+          <t>CQV Lead</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -5264,12 +5260,12 @@
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom (Europe)</t>
+          <t>Kilbirnie, Scotland, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
@@ -5280,19 +5276,19 @@
       <c r="H82" s="13" t="inlineStr"/>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>Shane Dorgan</t>
+          <t>Puja Tanwani</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Lead C&amp;Q Engineer small molecule projects IE8</t>
+          <t>Associate Director - Process Design (Global Engineering Capital Projects)</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -5307,12 +5303,12 @@
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects / Process Design)</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
@@ -5323,19 +5319,19 @@
       <c r="H83" s="13" t="inlineStr"/>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>Sinead Dullaghan</t>
+          <t>Rick Rowe</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Senior Principal Scientist, TSMS</t>
+          <t>Project Manager, Eli Lilly</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -5350,39 +5346,35 @@
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Bargersville, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing Science (TSMS)</t>
+          <t>Engineering (Capital Project / PM)</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H84" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H84" s="13" t="inlineStr"/>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>Tara Tibbs</t>
+          <t>Robert O'Keeffe</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>SVP &amp; Site Head, Lilly Kinsale</t>
+          <t>Senior Director, Engineering Tech Centre</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -5397,12 +5389,12 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Kinsale (Cork), Ireland (Europe)</t>
+          <t>Ireland (Limerick NGB) (Europe)</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
@@ -5410,22 +5402,26 @@
           <t>Public research</t>
         </is>
       </c>
-      <c r="H85" s="13" t="inlineStr"/>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
+        </is>
+      </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>Theofylaktos Tokas</t>
+          <t>Sasha Adib-Yaghmai</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>NPI Engineer – Capital Projects &amp; Operational Readiness</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -5440,12 +5436,12 @@
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>Germany (Europe)</t>
+          <t>United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G86" s="13" t="inlineStr">
@@ -5456,19 +5452,19 @@
       <c r="H86" s="13" t="inlineStr"/>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>Tracy McEntee</t>
+          <t>Shane Dorgan</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>Lead C&amp;Q Engineer small molecule projects IE8</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -5483,7 +5479,7 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Dundalk, County Louth, Ireland (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
@@ -5506,12 +5502,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>Victor Cruz</t>
+          <t>Sinead Dullaghan</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>SVP, Corporate Engineering &amp; Global Health, Safety &amp; Environmental</t>
+          <t>Senior Principal Scientist, TSMS</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -5526,12 +5522,12 @@
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Global (Indianapolis) (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Corporate)</t>
+          <t>Manufacturing Science (TSMS)</t>
         </is>
       </c>
       <c r="G88" s="13" t="inlineStr">
@@ -5541,29 +5537,29 @@
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>ISPE Facilities of the Future 2026</t>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>Binghui Li</t>
+          <t>Tara Tibbs</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>SVP &amp; Site Head, Lilly Kinsale</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
@@ -5573,40 +5569,40 @@
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Nijmegen, Gelderland, Netherlands (Europe)</t>
+          <t>Kinsale (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr"/>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>Ciaran Kelleher</t>
+          <t>Theofylaktos Tokas</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>Senior Principal Engineer, Janssen Supply Chain</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
@@ -5616,44 +5612,40 @@
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (Europe)</t>
+          <t>Germany (Europe)</t>
         </is>
       </c>
       <c r="F90" s="13" t="inlineStr">
         <is>
-          <t>Engineering (C&amp;Q/Standards)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
-        </is>
-      </c>
-      <c r="H90" s="13" t="inlineStr">
-        <is>
-          <t>ASME BPE Subcommittee on Systems Design (ongoing working-group meetings, not a trade show)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H90" s="13" t="inlineStr"/>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>Conor O' Connell</t>
+          <t>Tracy McEntee</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>CQV Process Lead</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
@@ -5663,7 +5655,7 @@
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Wake Forest, North Carolina, United States (US)</t>
+          <t>Dundalk, County Louth, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
@@ -5686,17 +5678,17 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>Craig Walsh</t>
+          <t>Victor Cruz</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Innovation and Technology team, clinical manufacturing (PAT focus)</t>
+          <t>SVP, Corporate Engineering &amp; Global Health, Safety &amp; Environmental</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
@@ -5706,22 +5698,22 @@
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>Schaffhausen, Switzerland (Europe)</t>
+          <t>Global (Indianapolis) (US)</t>
         </is>
       </c>
       <c r="F92" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Manufacturing Technology</t>
+          <t>Engineering (Corporate)</t>
         </is>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+          <t>ISPE Facilities of the Future 2026</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
@@ -5733,12 +5725,12 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>Dana Daneshvari</t>
+          <t>Binghui Li</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>General Manager &amp; VP Manufacturing, Large Molecule Site</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -5753,17 +5745,17 @@
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>Nijmegen, Gelderland, Netherlands (Europe)</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Manufacturing (Site GM)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr"/>
@@ -5776,12 +5768,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>Donald Powers</t>
+          <t>Ciaran Kelleher</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>Sr Director Advanced Therapies MSAT</t>
+          <t>Senior Principal Engineer, Janssen Supply Chain</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -5796,35 +5788,39 @@
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>Greater Philadelphia (US)</t>
+          <t>Not specified in source (Europe)</t>
         </is>
       </c>
       <c r="F94" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Engineering (C&amp;Q/Standards)</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H94" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>ASME BPE Subcommittee on Systems Design (ongoing working-group meetings, not a trade show)</t>
+        </is>
+      </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>Federico Sabini</t>
+          <t>Conor O' Connell</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>LCM Manager, MSAT Large Molecule Drug Product Platform</t>
+          <t>CQV Process Lead</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -5839,39 +5835,35 @@
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (Europe)</t>
+          <t>Wake Forest, North Carolina, United States (US)</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
-        </is>
-      </c>
-      <c r="H95" s="13" t="inlineStr">
-        <is>
-          <t>PDA Parenteral Packaging Conference 2026 (Apr 14-15, Munich)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H95" s="13" t="inlineStr"/>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>Goeran Crucius</t>
+          <t>Craig Walsh</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Director MSAT Cross Platform Engineering</t>
+          <t>Innovation and Technology team, clinical manufacturing (PAT focus)</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -5891,30 +5883,34 @@
       </c>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Engineering</t>
+          <t>Engineering/Manufacturing Technology</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H96" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+        </is>
+      </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>Greg Jama</t>
+          <t>Dana Daneshvari</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Project Manager - Engineering</t>
+          <t>General Manager &amp; VP Manufacturing, Large Molecule Site</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -5929,35 +5925,35 @@
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Mt. Joy, Pennsylvania, United States (US)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Project / PM)</t>
+          <t>Engineering/Manufacturing (Site GM)</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr"/>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>Gregory Strollo, CAM</t>
+          <t>Donald Powers</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Sr Director Advanced Therapies MSAT</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -5972,12 +5968,12 @@
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Greater Philadelphia (US)</t>
         </is>
       </c>
       <c r="F98" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G98" s="13" t="inlineStr">
@@ -5988,19 +5984,19 @@
       <c r="H98" s="13" t="inlineStr"/>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>Kathryn E. Wengel</t>
+          <t>Federico Sabini</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Technical Operations &amp; Risk Officer</t>
+          <t>LCM Manager, MSAT Large Molecule Drug Product Platform</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -6015,12 +6011,12 @@
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Enterprise-wide (Global) (US)</t>
+          <t>Not specified in source (Europe)</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Quality/Supply Chain (Executive)</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -6028,22 +6024,26 @@
           <t>Public research (J&amp;J)</t>
         </is>
       </c>
-      <c r="H99" s="13" t="inlineStr"/>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>PDA Parenteral Packaging Conference 2026 (Apr 14-15, Munich)</t>
+        </is>
+      </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>Marco Fimbres</t>
+          <t>Goeran Crucius</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Director MSAT Cross Platform Engineering</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Mexico (Americas)</t>
+          <t>Schaffhausen, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F100" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT / Engineering</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
@@ -6074,19 +6074,19 @@
       <c r="H100" s="13" t="inlineStr"/>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>Mary Houchin</t>
+          <t>Greg Jama</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>MSAT Site Director</t>
+          <t>Project Manager - Engineering</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
+          <t>Mt. Joy, Pennsylvania, United States (US)</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Site Director)</t>
+          <t>Engineering (Capital Project / PM)</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -6117,19 +6117,19 @@
       <c r="H101" s="13" t="inlineStr"/>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>Moufid B.</t>
+          <t>Gregory Strollo, CAM</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>CQV Expert &amp; Compliance SME (Risk-Based Approach)</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Belgium (Europe)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F102" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
@@ -6160,19 +6160,19 @@
       <c r="H102" s="13" t="inlineStr"/>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>Nader Al-Tahan</t>
+          <t>Kathryn E. Wengel</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>Upstream CQV Lead</t>
+          <t>EVP, Chief Technical Operations &amp; Risk Officer</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -6187,17 +6187,17 @@
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Wilson, North Carolina, United States (US)</t>
+          <t>Enterprise-wide (Global) (US)</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering/Quality/Supply Chain (Executive)</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr"/>
@@ -6210,12 +6210,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>Peter Millili, PhD</t>
+          <t>Marco Fimbres</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Manufacturing Science and Technology (MSAT), Advanced Therapies</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -6230,39 +6230,35 @@
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Philadelphia / Spring House, PA</t>
+          <t>Mexico (Americas)</t>
         </is>
       </c>
       <c r="F104" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
-        </is>
-      </c>
-      <c r="H104" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual Meeting &amp; Expo 2026 (Oct 18-21, National Harbor, MD)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H104" s="13" t="inlineStr"/>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>Rafael J. Riera</t>
+          <t>Mary Houchin</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Production Engineering Manager</t>
+          <t>MSAT Site Director</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -6277,12 +6273,12 @@
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
         </is>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Production)</t>
+          <t>MSAT (Site Director)</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -6293,19 +6289,19 @@
       <c r="H105" s="13" t="inlineStr"/>
       <c r="I105" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>Stephanie Striegler</t>
+          <t>Moufid B.</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>General Manager, Janssen Schaffhausen</t>
+          <t>CQV Expert &amp; Compliance SME (Risk-Based Approach)</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -6320,35 +6316,35 @@
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Schaffhausen, Switzerland (Europe)</t>
+          <t>Belgium (Europe)</t>
         </is>
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
-          <t>Executive (Site GM)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H106" s="13" t="inlineStr"/>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>Thomas Kelly</t>
+          <t>Nader Al-Tahan</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>Director, Cell Engineering &amp; Analytical Sciences</t>
+          <t>Upstream CQV Lead</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
@@ -6363,24 +6359,20 @@
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (US)</t>
+          <t>Wilson, North Carolina, United States (US)</t>
         </is>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D/Manufacturing Science</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
-        </is>
-      </c>
-      <c r="H107" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International 2026 (Sep 22-25, Boston, MA)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H107" s="13" t="inlineStr"/>
       <c r="I107" s="14" t="inlineStr">
         <is>
           <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
@@ -6390,17 +6382,17 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>A Glenn</t>
+          <t>Peter Millili, PhD</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Senior Director, Manufacturing Science and Technology (MSAT), Advanced Therapies</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
@@ -6410,40 +6402,44 @@
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Aurora, Colorado, United States (US)</t>
+          <t>Philadelphia / Spring House, PA</t>
         </is>
       </c>
       <c r="F108" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H108" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H108" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual Meeting &amp; Expo 2026 (Oct 18-21, National Harbor, MD)</t>
+        </is>
+      </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>Balaji Mangiri</t>
+          <t>Rafael J. Riera</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>Manager Commissioning &amp; Qualification (CQV/C&amp;Q) &amp; Global Engineering Compliance</t>
+          <t>Production Engineering Manager</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -6453,12 +6449,12 @@
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>India (Asia)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Production)</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -6476,17 +6472,17 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>Daniel Irby</t>
+          <t>Stephanie Striegler</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>Consulting Project Engineer</t>
+          <t>General Manager, Janssen Schaffhausen</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
@@ -6496,40 +6492,40 @@
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Schaffhausen, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F110" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Executive (Site GM)</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H110" s="13" t="inlineStr"/>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>Filip Grujevski</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>Engineering Standards Manager</t>
+          <t>Director, Cell Engineering &amp; Analytical Sciences</t>
         </is>
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
@@ -6539,20 +6535,24 @@
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Ljubljana, Ljubljana, Slovenia (Europe)</t>
+          <t>Not specified in source (US)</t>
         </is>
       </c>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>R&amp;D/Manufacturing Science</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H111" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International 2026 (Sep 22-25, Boston, MA)</t>
+        </is>
+      </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
           <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
@@ -6562,12 +6562,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>Filip Grujevski, MBA</t>
+          <t>A Glenn</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>Engineering Standards Manager</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Ljubljana, Slovenia (Europe)</t>
+          <t>Aurora, Colorado, United States (US)</t>
         </is>
       </c>
       <c r="F112" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Standards)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G112" s="13" t="inlineStr">
@@ -6598,19 +6598,19 @@
       <c r="H112" s="13" t="inlineStr"/>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>Masthan N</t>
+          <t>Balaji Mangiri</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>Senior Validation &amp; Process Engineer (CSV/CQV)</t>
+          <t>Manager Commissioning &amp; Qualification (CQV/C&amp;Q) &amp; Global Engineering Compliance</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>India (Asia)</t>
         </is>
       </c>
       <c r="F113" s="13" t="inlineStr">
@@ -6648,12 +6648,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>Megan Crandall</t>
+          <t>Daniel Irby</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, MSAT DP</t>
+          <t>Consulting Project Engineer</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Garner, North Carolina, United States (US)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="F114" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G114" s="13" t="inlineStr">
@@ -6684,19 +6684,19 @@
       <c r="H114" s="13" t="inlineStr"/>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>Miha Vouk</t>
+          <t>Filip Grujevski</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Engineering Standards Manager</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Ljubljana Metropolitan Area (Europe)</t>
+          <t>Ljubljana, Ljubljana, Slovenia (Europe)</t>
         </is>
       </c>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
@@ -6734,12 +6734,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>Mila Georgieva</t>
+          <t>Filip Grujevski, MBA</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>Jr C&amp;Q Engineer</t>
+          <t>Engineering Standards Manager</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Breda, North Brabant, Netherlands (Europe)</t>
+          <t>Ljubljana, Slovenia (Europe)</t>
         </is>
       </c>
       <c r="F116" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Standards)</t>
         </is>
       </c>
       <c r="G116" s="13" t="inlineStr">
@@ -6777,12 +6777,12 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>Rajeev Kumar</t>
+          <t>Masthan N</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>Engineering Manager - Global Project</t>
+          <t>Senior Validation &amp; Process Engineer (CSV/CQV)</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India (Asia)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -6820,12 +6820,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>Shankar Birajdar</t>
+          <t>Megan Crandall</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer, Global Projects</t>
+          <t>Associate Director, MSAT DP</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Thane, Maharashtra, India (Asia)</t>
+          <t>Garner, North Carolina, United States (US)</t>
         </is>
       </c>
       <c r="F118" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
@@ -6856,19 +6856,19 @@
       <c r="H118" s="13" t="inlineStr"/>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>Soma shekara</t>
+          <t>Miha Vouk</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>Director - Global Project Engineering</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Ljubljana Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Global Project Engineering)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
@@ -6906,17 +6906,17 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>Anne-Sophie Eriksen</t>
+          <t>Mila Georgieva</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>Director Life Cycle Management, MSAT &amp; QC</t>
+          <t>Jr C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Farum, Capital Region of Denmark, Denmark (Europe)</t>
+          <t>Breda, North Brabant, Netherlands (Europe)</t>
         </is>
       </c>
       <c r="F120" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QC</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
@@ -6942,24 +6942,24 @@
       <c r="H120" s="13" t="inlineStr"/>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>Bettina Jakobsen</t>
+          <t>Rajeev Kumar</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>Senior Manager API QA MSAT &amp; Support</t>
+          <t>Engineering Manager - Global Project</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
+          <t>Hyderabad, Telangana, India (Asia)</t>
         </is>
       </c>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QA</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
@@ -6985,24 +6985,24 @@
       <c r="H121" s="13" t="inlineStr"/>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>Camilla Ulrich Hassager</t>
+          <t>Shankar Birajdar</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>Scientific Director, API Quality IT &amp; MSAT</t>
+          <t>C&amp;Q Engineer, Global Projects</t>
         </is>
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
+          <t>Thane, Maharashtra, India (Asia)</t>
         </is>
       </c>
       <c r="F122" s="13" t="inlineStr">
         <is>
-          <t>MSAT / API Quality</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
@@ -7028,24 +7028,24 @@
       <c r="H122" s="13" t="inlineStr"/>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>Dermot Farnan</t>
+          <t>Soma shekara</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Director - Global Project Engineering</t>
         </is>
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering (Global Project Engineering)</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
@@ -7078,12 +7078,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>Flemming Dahl</t>
+          <t>Anne-Sophie Eriksen</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>SVP, Head of Product Supply Fill &amp; Finish Expansions</t>
+          <t>Director Life Cycle Management, MSAT &amp; QC</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
@@ -7098,35 +7098,35 @@
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Global (Denmark) (Europe)</t>
+          <t>Farum, Capital Region of Denmark, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F124" s="13" t="inlineStr">
         <is>
-          <t>Engineering / Capital Project (Fill-Finish Expansions)</t>
+          <t>MSAT / QC</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr"/>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>Hao Jiang</t>
+          <t>Bettina Jakobsen</t>
         </is>
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>Director, Synthetic API MSAT</t>
+          <t>Senior Manager API QA MSAT &amp; Support</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Synthetic API)</t>
+          <t>MSAT / QA</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
@@ -7164,12 +7164,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>Jacquelyn White</t>
+          <t>Camilla Ulrich Hassager</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>Engineering Manager, API Expansions</t>
+          <t>Scientific Director, API Quality IT &amp; MSAT</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Capital Region of Denmark, Denmark (Europe)</t>
+          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F126" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>MSAT / API Quality</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
@@ -7200,19 +7200,19 @@
       <c r="H126" s="13" t="inlineStr"/>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>Jason Trussell</t>
+          <t>Dermot Farnan</t>
         </is>
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>Director - Bioteam, MSAT and QC</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Grantham, New Hampshire, United States (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QC</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
@@ -7243,19 +7243,19 @@
       <c r="H127" s="13" t="inlineStr"/>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>Jay Kuykendall</t>
+          <t>Dev R.</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>Project Vice President, Clayton (NC) Expansion</t>
+          <t>CQV Consultant</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
@@ -7270,35 +7270,35 @@
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC (US)</t>
+          <t>Greater Boston (US)</t>
         </is>
       </c>
       <c r="F128" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Capital Project</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr"/>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>Jesper Kløve</t>
+          <t>Flemming Dahl</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>CEO, NNE (Novo Nordisk Engineering)</t>
+          <t>SVP, Head of Product Supply Fill &amp; Finish Expansions</t>
         </is>
       </c>
       <c r="C129" s="13" t="inlineStr">
@@ -7313,12 +7313,12 @@
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Kalundborg, DK / Clayton, NC (NNE-delivered) (Global)</t>
+          <t>Global (Denmark) (Europe)</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>Engineering (EPCM — capital delivery)</t>
+          <t>Engineering / Capital Project (Fill-Finish Expansions)</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
@@ -7329,19 +7329,19 @@
       <c r="H129" s="13" t="inlineStr"/>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>Kimberley Parker, PhD, PMP</t>
+          <t>Hao Jiang</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>Process Engineer III - Fermentation</t>
+          <t>Director, Synthetic API MSAT</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
@@ -7356,35 +7356,35 @@
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Clayton / Research Triangle, NC (US)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="F130" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Process / Fermentation)</t>
+          <t>MSAT (Synthetic API)</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr"/>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>Larry Lane</t>
+          <t>Jacquelyn White</t>
         </is>
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>Project Director, Construction &amp; Engineering (Clayton Expansion)</t>
+          <t>Engineering Manager, API Expansions</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
@@ -7399,24 +7399,20 @@
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC (US)</t>
+          <t>Copenhagen, Capital Region of Denmark, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Construction / Capital Project)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H131" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr"/>
       <c r="I131" s="14" t="inlineStr">
         <is>
           <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
@@ -7426,12 +7422,12 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>Lars Hovmand-Lyster</t>
+          <t>Jason Trussell</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>Senior Engineering Specialist</t>
+          <t>Director - Bioteam, MSAT and QC</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
@@ -7446,39 +7442,35 @@
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Grantham, New Hampshire, United States (US)</t>
         </is>
       </c>
       <c r="F132" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>MSAT / QC</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H132" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr"/>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>Lasse Brusgaard Demant Schwaneflygel</t>
+          <t>Jay Kuykendall</t>
         </is>
       </c>
       <c r="B133" s="14" t="inlineStr">
         <is>
-          <t>Senior Manager - API MSAT Business Support</t>
+          <t>Project Vice President, Clayton (NC) Expansion</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
@@ -7493,35 +7485,35 @@
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen Metropolitan Area (Europe)</t>
+          <t>Clayton, NC (US)</t>
         </is>
       </c>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>MSAT (API Business Support)</t>
+          <t>Engineering/Capital Project</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr"/>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>Lene Damkjær Iversen</t>
+          <t>Jesper Kløve</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>Senior CQV Specialist, Fill &amp; Finish Expansions</t>
+          <t>CEO, NNE (Novo Nordisk Engineering)</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
@@ -7536,35 +7528,35 @@
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Kalundborg, DK / Clayton, NC (NNE-delivered) (Global)</t>
         </is>
       </c>
       <c r="F134" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Fill &amp; Finish Expansions)</t>
+          <t>Engineering (EPCM — capital delivery)</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr"/>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>Lone Charlotte Larsen</t>
+          <t>Kimberley Parker, PhD, PMP</t>
         </is>
       </c>
       <c r="B135" s="14" t="inlineStr">
         <is>
-          <t>Corporate Vice President, Novo Nordisk Production Chartres</t>
+          <t>Process Engineer III - Fermentation</t>
         </is>
       </c>
       <c r="C135" s="13" t="inlineStr">
@@ -7579,12 +7571,12 @@
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Chartres, France (Europe)</t>
+          <t>Clayton / Research Triangle, NC (US)</t>
         </is>
       </c>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership (Capital Project)</t>
+          <t>Engineering (Process / Fermentation)</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
@@ -7595,19 +7587,19 @@
       <c r="H135" s="13" t="inlineStr"/>
       <c r="I135" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>Mads Overgaard</t>
+          <t>Larry Lane</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>Director - PS API MSAT Technology &amp; Process Facilities</t>
+          <t>Project Director, Construction &amp; Engineering (Clayton Expansion)</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
@@ -7622,35 +7614,39 @@
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Clayton, NC (US)</t>
         </is>
       </c>
       <c r="F136" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Facilities</t>
+          <t>Engineering (Construction / Capital Project)</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H136" s="13" t="inlineStr"/>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H136" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>Peter C. Luke</t>
+          <t>Lars Hovmand-Lyster</t>
         </is>
       </c>
       <c r="B137" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Capital Projects - Drug Substance</t>
+          <t>Senior Engineering Specialist</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
@@ -7665,35 +7661,39 @@
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H137" s="13" t="inlineStr"/>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
+        </is>
+      </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>Søren Rønsted</t>
+          <t>Lasse Brusgaard Demant Schwaneflygel</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>Director, Finished Product Manufacturing and Science (MSAT)</t>
+          <t>Senior Manager - API MSAT Business Support</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Copenhagen Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="F138" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Finished Product)</t>
+          <t>MSAT (API Business Support)</t>
         </is>
       </c>
       <c r="G138" s="13" t="inlineStr">
@@ -7731,12 +7731,12 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>Trent Rogers</t>
+          <t>Lene Damkjær Iversen</t>
         </is>
       </c>
       <c r="B139" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Senior CQV Specialist, Fill &amp; Finish Expansions</t>
         </is>
       </c>
       <c r="C139" s="13" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Kinston, North Carolina, United States (US)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering / C&amp;Q (Fill &amp; Finish Expansions)</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
@@ -7767,19 +7767,19 @@
       <c r="H139" s="13" t="inlineStr"/>
       <c r="I139" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>Trine Eske</t>
+          <t>Lone Charlotte Larsen</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead</t>
+          <t>Corporate Vice President, Novo Nordisk Production Chartres</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
@@ -7794,40 +7794,40 @@
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Chartres, France (Europe)</t>
         </is>
       </c>
       <c r="F140" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Site Leadership (Capital Project)</t>
         </is>
       </c>
       <c r="G140" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H140" s="13" t="inlineStr"/>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>Christian Hakemeyer</t>
+          <t>Mads Overgaard</t>
         </is>
       </c>
       <c r="B141" s="14" t="inlineStr">
         <is>
-          <t>Head of MSAT</t>
+          <t>Director - PS API MSAT Technology &amp; Process Facilities</t>
         </is>
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D141" s="15" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Ilvesheim, Baden-Württemberg, Germany (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>MSAT / Process Facilities</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
@@ -7860,17 +7860,17 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>Christian Rutz</t>
+          <t>Oleksandr Malenko</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>Head of Global PTT Engineering &amp; Technology, Global MSAT/Engineering/Sustainability</t>
+          <t>CQV Project Manager - Fill Finish Expansion</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Mannheim, Baden-Württemberg, Germany (Global)</t>
+          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
         </is>
       </c>
       <c r="F142" s="13" t="inlineStr">
         <is>
-          <t>Engineering / MSAT (Global)</t>
+          <t>Engineering / C&amp;Q (Fill-Finish Expansion)</t>
         </is>
       </c>
       <c r="G142" s="13" t="inlineStr">
@@ -7896,24 +7896,24 @@
       <c r="H142" s="13" t="inlineStr"/>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>Elizabeth Danbe</t>
+          <t>Peter C. Luke</t>
         </is>
       </c>
       <c r="B143" s="14" t="inlineStr">
         <is>
-          <t>Senior Engineer, Global Pharma Technical Engineering</t>
+          <t>Vice President, Capital Projects - Drug Substance</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D143" s="15" t="inlineStr">
@@ -7923,17 +7923,17 @@
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Oceanside / South San Francisco, CA (US)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Automation / Capital Project)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr"/>
@@ -7946,17 +7946,17 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>Ethan Wang</t>
+          <t>Søren Rønsted</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>Head of Maintenance</t>
+          <t>Director, Finished Product Manufacturing and Science (MSAT)</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Shanghai, China (Asia)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F144" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT (Finished Product)</t>
         </is>
       </c>
       <c r="G144" s="13" t="inlineStr">
@@ -7982,24 +7982,24 @@
       <c r="H144" s="13" t="inlineStr"/>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>Fabio Kron</t>
+          <t>Trent Rogers</t>
         </is>
       </c>
       <c r="B145" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer Manufacturing Technology Solutions for Vision Systems and Sensor Solutions</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D145" s="15" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Herxheim, Rhineland-Palatinate, Germany (Europe)</t>
+          <t>Kinston, North Carolina, United States (US)</t>
         </is>
       </c>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
@@ -8025,24 +8025,24 @@
       <c r="H145" s="13" t="inlineStr"/>
       <c r="I145" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>Hiltrud Krenz</t>
+          <t>Trine Eske</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>Projektingenieur</t>
+          <t>CQV Lead</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Greater Munich Metropolitan Area (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F146" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G146" s="13" t="inlineStr">
@@ -8075,7 +8075,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>Marco Wetzstein</t>
+          <t>Christian Hakemeyer</t>
         </is>
       </c>
       <c r="B147" s="14" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>Ilvesheim, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr">
@@ -8118,12 +8118,12 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>Mark Nolden</t>
+          <t>Christian Rutz</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>Head of Global MSAT Drug Substance Process Stewards</t>
+          <t>Head of Global PTT Engineering &amp; Technology, Global MSAT/Engineering/Sustainability</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Iffeldorf, Bavaria, Germany (Global)</t>
+          <t>Mannheim, Baden-Württemberg, Germany (Global)</t>
         </is>
       </c>
       <c r="F148" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Drug Substance)</t>
+          <t>Engineering / MSAT (Global)</t>
         </is>
       </c>
       <c r="G148" s="13" t="inlineStr">
@@ -8161,12 +8161,12 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>Maurice Lambrecht</t>
+          <t>Elizabeth Danbe</t>
         </is>
       </c>
       <c r="B149" s="14" t="inlineStr">
         <is>
-          <t>Head of Maintenance F&amp;E und SHE</t>
+          <t>Senior Engineer, Global Pharma Technical Engineering</t>
         </is>
       </c>
       <c r="C149" s="13" t="inlineStr">
@@ -8181,35 +8181,35 @@
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Mannheim, Baden-Württemberg, Germany (Europe)</t>
+          <t>Oceanside / South San Francisco, CA (US)</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering (Automation / Capital Project)</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr"/>
       <c r="I149" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>Mustafa Wahid</t>
+          <t>Ethan Wang</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>Regional SME - Capital Projects America</t>
+          <t>Head of Maintenance</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Shanghai, China (Asia)</t>
         </is>
       </c>
       <c r="F150" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G150" s="13" t="inlineStr">
@@ -8240,19 +8240,19 @@
       <c r="H150" s="13" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>Nazeli Dertsakian</t>
+          <t>Fabio Kron</t>
         </is>
       </c>
       <c r="B151" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; GM Genentech Oceanside / VP, Global Head Clinical Supply Operations</t>
+          <t>Project Engineer Manufacturing Technology Solutions for Vision Systems and Sensor Solutions</t>
         </is>
       </c>
       <c r="C151" s="13" t="inlineStr">
@@ -8267,39 +8267,35 @@
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Oceanside, CA (US)</t>
+          <t>Herxheim, Rhineland-Palatinate, Germany (Europe)</t>
         </is>
       </c>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H151" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H151" s="13" t="inlineStr"/>
       <c r="I151" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>Pascal Ruf</t>
+          <t>Hiltrud Krenz</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>Head of Site Infrastructure Engineering</t>
+          <t>Projektingenieur</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
@@ -8314,12 +8310,12 @@
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (Europe)</t>
+          <t>Greater Munich Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="F152" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Utilities / Site Infrastructure)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="G152" s="13" t="inlineStr">
@@ -8330,14 +8326,14 @@
       <c r="H152" s="13" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>Qianting Ou</t>
+          <t>Marco Wetzstein</t>
         </is>
       </c>
       <c r="B153" s="14" t="inlineStr">
@@ -8357,7 +8353,7 @@
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>China (Asia)</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F153" s="13" t="inlineStr">
@@ -8380,12 +8376,12 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>Sebastian Stening</t>
+          <t>Mark Nolden</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>VP, Global Head Device, Packaging &amp; Distribution MSAT</t>
+          <t>Head of Global MSAT Drug Substance Process Stewards</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
@@ -8400,12 +8396,12 @@
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (Global)</t>
+          <t>Iffeldorf, Bavaria, Germany (Global)</t>
         </is>
       </c>
       <c r="F154" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Executive)</t>
+          <t>MSAT (Drug Substance)</t>
         </is>
       </c>
       <c r="G154" s="13" t="inlineStr">
@@ -8423,12 +8419,12 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>Stephanie Targgart</t>
+          <t>Maurice Lambrecht</t>
         </is>
       </c>
       <c r="B155" s="14" t="inlineStr">
         <is>
-          <t>Manager - Maintenance</t>
+          <t>Head of Maintenance F&amp;E und SHE</t>
         </is>
       </c>
       <c r="C155" s="13" t="inlineStr">
@@ -8443,7 +8439,7 @@
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Mannheim, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="F155" s="13" t="inlineStr">
@@ -8466,12 +8462,12 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>Troy Farris</t>
+          <t>Mustafa Wahid</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Projects</t>
+          <t>Regional SME - Capital Projects America</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
@@ -8509,32 +8505,32 @@
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>Chris Chumsae, PhD</t>
+          <t>Nazeli Dertsakian</t>
         </is>
       </c>
       <c r="B157" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Process Development Analytics</t>
+          <t>VP &amp; GM Genentech Oceanside / VP, Global Head Clinical Supply Operations</t>
         </is>
       </c>
       <c r="C157" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D157" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>Oceanside, CA (US)</t>
         </is>
       </c>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>Process Development / Analytics</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
@@ -8544,87 +8540,87 @@
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t>The Bioprocessing Summit 2026 (Aug 10-13, Boston, MA)</t>
+          <t>ISPE Facilities of the Future 2026</t>
         </is>
       </c>
       <c r="I157" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>Karin Shanahan</t>
+          <t>Pascal Ruf</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
+          <t>Head of Site Infrastructure Engineering</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D158" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
+          <t>Basel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F158" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Ops)</t>
+          <t>Engineering (Utilities / Site Infrastructure)</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>L. Andrew R.</t>
+          <t>Qianting Ou</t>
         </is>
       </c>
       <c r="B159" s="14" t="inlineStr">
         <is>
-          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
+          <t>Head of MSAT</t>
         </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D159" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, New Jersey, United States (US)</t>
+          <t>China (Asia)</t>
         </is>
       </c>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing IT / Operations</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
@@ -8635,82 +8631,82 @@
       <c r="H159" s="13" t="inlineStr"/>
       <c r="I159" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>Richard Martel</t>
+          <t>Sebastian Stening</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>Upstream Manager, Single-Use Facility</t>
+          <t>VP, Global Head Device, Packaging &amp; Distribution MSAT</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D160" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>Basel, Switzerland (Global)</t>
         </is>
       </c>
       <c r="F160" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Upstream / Single-Use)</t>
+          <t>MSAT (Executive)</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H160" s="13" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>Sean Tonzi</t>
+          <t>Stephanie Targgart</t>
         </is>
       </c>
       <c r="B161" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, CMC Strategy</t>
+          <t>Manager - Maintenance</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D161" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Syracuse, New York, United States</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>CMC / Process Development</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
@@ -8721,71 +8717,67 @@
       <c r="H161" s="13" t="inlineStr"/>
       <c r="I161" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>Ainhoa Nieto</t>
+          <t>Troy Farris</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>Associate VP, Manufacturing</t>
+          <t>Director, Capital Projects</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Japan (Global)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="F162" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H162" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H162" s="13" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>Bill Cook</t>
+          <t>Chris Chumsae, PhD</t>
         </is>
       </c>
       <c r="B163" s="14" t="inlineStr">
         <is>
-          <t>Lean Manufacturing / Operational Excellence - Director</t>
+          <t>Associate Director, Process Development Analytics</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D163" s="16" t="inlineStr">
@@ -8795,40 +8787,44 @@
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Clinton, Indiana, United States (US)</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>Operational Excellence / Lean</t>
+          <t>Process Development / Analytics</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H163" s="13" t="inlineStr"/>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H163" s="13" t="inlineStr">
+        <is>
+          <t>The Bioprocessing Summit 2026 (Aug 10-13, Boston, MA)</t>
+        </is>
+      </c>
       <c r="I163" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>F.R. Casal</t>
+          <t>Karin Shanahan</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>Assistant Director</t>
+          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D164" s="16" t="inlineStr">
@@ -8838,40 +8834,40 @@
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
         </is>
       </c>
       <c r="F164" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Assistant Director)</t>
+          <t>Executive (Supply/Ops)</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H164" s="13" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>Melissa Seymour</t>
+          <t>L. Andrew R.</t>
         </is>
       </c>
       <c r="B165" s="14" t="inlineStr">
         <is>
-          <t>EVP, Global Quality</t>
+          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D165" s="16" t="inlineStr">
@@ -8881,40 +8877,40 @@
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Global (Indianapolis) (US)</t>
+          <t>Lebanon, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="F165" s="13" t="inlineStr">
         <is>
-          <t>Executive (Quality)</t>
+          <t>Manufacturing IT / Operations</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H165" s="13" t="inlineStr"/>
       <c r="I165" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>Armelle Santelli</t>
+          <t>Richard Martel</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
+          <t>Upstream Manager, Single-Use Facility</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D166" s="16" t="inlineStr">
@@ -8924,40 +8920,40 @@
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="F166" s="13" t="inlineStr">
         <is>
-          <t>Quality/Regulatory</t>
+          <t>Manufacturing (Upstream / Single-Use)</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H166" s="13" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>Carlos Arbelaez, PhD</t>
+          <t>Sean Tonzi</t>
         </is>
       </c>
       <c r="B167" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Cell Therapy Process Development</t>
+          <t>Associate Director, CMC Strategy</t>
         </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="D167" s="16" t="inlineStr">
@@ -8967,24 +8963,20 @@
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (US)</t>
+          <t>Syracuse, New York, United States</t>
         </is>
       </c>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Process Development</t>
+          <t>CMC / Process Development</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
-        </is>
-      </c>
-      <c r="H167" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International US West 2026 (Mar 9-11, San Diego, CA) — session confirmed Mar 10, 2:30pm</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H167" s="13" t="inlineStr"/>
       <c r="I167" s="14" t="inlineStr">
         <is>
           <t>Process development / advanced-mfg — specs process equipment early.</t>
@@ -8994,17 +8986,17 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>Dapo Ajayi</t>
+          <t>Ainhoa Nieto</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>VP, Innovative Medicine Supply Chain</t>
+          <t>Associate VP, Manufacturing</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D168" s="16" t="inlineStr">
@@ -9014,40 +9006,44 @@
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Wilson, NC (US)</t>
+          <t>Japan (Global)</t>
         </is>
       </c>
       <c r="F168" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
-        </is>
-      </c>
-      <c r="H168" s="13" t="inlineStr"/>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>Johan Van Hoof, MD</t>
+          <t>Bill Cook</t>
         </is>
       </c>
       <c r="B169" s="14" t="inlineStr">
         <is>
-          <t>Global Therapeutic Area Head IDV, Vaccines</t>
+          <t>Lean Manufacturing / Operational Excellence - Director</t>
         </is>
       </c>
       <c r="C169" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D169" s="16" t="inlineStr">
@@ -9057,17 +9053,17 @@
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Leiden, Netherlands (Europe)</t>
+          <t>Clinton, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="F169" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D/Vaccines</t>
+          <t>Operational Excellence / Lean</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H169" s="13" t="inlineStr"/>
@@ -9080,17 +9076,17 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>Julian Hooks</t>
+          <t>F.R. Casal</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>VP, Global Services Operations &amp; Procurement</t>
+          <t>Assistant Director</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D170" s="16" t="inlineStr">
@@ -9100,40 +9096,40 @@
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Enterprise-wide (Global) (US)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="F170" s="13" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Manufacturing (Assistant Director)</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H170" s="13" t="inlineStr"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>Kimberly Lounds Foster</t>
+          <t>Melissa Seymour</t>
         </is>
       </c>
       <c r="B171" s="14" t="inlineStr">
         <is>
-          <t>Global Head, Advanced Therapies Supply Chain</t>
+          <t>EVP, Global Quality</t>
         </is>
       </c>
       <c r="C171" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D171" s="16" t="inlineStr">
@@ -9143,35 +9139,35 @@
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Advanced therapies manufacturing network (US)</t>
+          <t>Global (Indianapolis) (US)</t>
         </is>
       </c>
       <c r="F171" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Executive (Quality)</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr"/>
       <c r="I171" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>Leila Schwery-Bou-Diab</t>
+          <t>Armelle Santelli</t>
         </is>
       </c>
       <c r="B172" s="14" t="inlineStr">
         <is>
-          <t>VP Manufacturing &amp; Technical Operations</t>
+          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
@@ -9186,12 +9182,12 @@
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="F172" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Technical Operations</t>
+          <t>Quality/Regulatory</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
@@ -9202,19 +9198,19 @@
       <c r="H172" s="13" t="inlineStr"/>
       <c r="I172" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>Marius Muller</t>
+          <t>Carlos Arbelaez, PhD</t>
         </is>
       </c>
       <c r="B173" s="14" t="inlineStr">
         <is>
-          <t>Scientific Senior Manager, TDS Biologics AD</t>
+          <t>Associate Director, Cell Therapy Process Development</t>
         </is>
       </c>
       <c r="C173" s="13" t="inlineStr">
@@ -9229,12 +9225,12 @@
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (Europe)</t>
+          <t>Not specified in source (US)</t>
         </is>
       </c>
       <c r="F173" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing Science/Technical Development</t>
+          <t>Manufacturing/Process Development</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
@@ -9244,24 +9240,24 @@
       </c>
       <c r="H173" s="13" t="inlineStr">
         <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+          <t>BioProcess International US West 2026 (Mar 9-11, San Diego, CA) — session confirmed Mar 10, 2:30pm</t>
         </is>
       </c>
       <c r="I173" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>Maxime Bergman</t>
+          <t>Dapo Ajayi</t>
         </is>
       </c>
       <c r="B174" s="14" t="inlineStr">
         <is>
-          <t>Senior Scientist, Process II, Global Process Development, TDS, Drug Product Development &amp; Delivery</t>
+          <t>VP, Innovative Medicine Supply Chain</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
@@ -9276,12 +9272,12 @@
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (Europe)</t>
+          <t>Wilson, NC (US)</t>
         </is>
       </c>
       <c r="F174" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Process Development</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
@@ -9289,31 +9285,27 @@
           <t>Public research (J&amp;J)</t>
         </is>
       </c>
-      <c r="H174" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
-        </is>
-      </c>
+      <c r="H174" s="13" t="inlineStr"/>
       <c r="I174" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>Roderick Freeman</t>
+          <t>Johan Van Hoof, MD</t>
         </is>
       </c>
       <c r="B175" s="14" t="inlineStr">
         <is>
-          <t>Site Quality Head, Novartis RLT (Radioligand Therapy)</t>
+          <t>Global Therapeutic Area Head IDV, Vaccines</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D175" s="16" t="inlineStr">
@@ -9323,44 +9315,40 @@
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>US (RLT site)</t>
+          <t>Leiden, Netherlands (Europe)</t>
         </is>
       </c>
       <c r="F175" s="13" t="inlineStr">
         <is>
-          <t>Quality (Site)</t>
+          <t>R&amp;D/Vaccines</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H175" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H175" s="13" t="inlineStr"/>
       <c r="I175" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>Roland Gander</t>
+          <t>Julian Hooks</t>
         </is>
       </c>
       <c r="B176" s="14" t="inlineStr">
         <is>
-          <t>Global Head Large Molecules / Cell &amp; Gene Therapies; MD, Novartis Pharmaceutical GmbH (Kundl)</t>
+          <t>VP, Global Services Operations &amp; Procurement</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D176" s="16" t="inlineStr">
@@ -9370,40 +9358,40 @@
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Kundl, Austria (Europe)</t>
+          <t>Enterprise-wide (Global) (US)</t>
         </is>
       </c>
       <c r="F176" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Large Molecules / CGT)</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H176" s="13" t="inlineStr"/>
       <c r="I176" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>Erik Lorin Rasmussen</t>
+          <t>Kimberly Lounds Foster</t>
         </is>
       </c>
       <c r="B177" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Supply, Aseptic Manufacturing</t>
+          <t>Global Head, Advanced Therapies Supply Chain</t>
         </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D177" s="16" t="inlineStr">
@@ -9413,17 +9401,17 @@
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Hillerod, Denmark (Europe)</t>
+          <t>Advanced therapies manufacturing network (US)</t>
         </is>
       </c>
       <c r="F177" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Aseptic)</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr"/>
@@ -9436,17 +9424,17 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>Henrik Wulff</t>
+          <t>Leila Schwery-Bou-Diab</t>
         </is>
       </c>
       <c r="B178" s="14" t="inlineStr">
         <is>
-          <t>EVP, Product Supply, Quality &amp; IT</t>
+          <t>VP Manufacturing &amp; Technical Operations</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D178" s="16" t="inlineStr">
@@ -9456,40 +9444,40 @@
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC / Kalundborg, DK (Global)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="F178" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Quality)</t>
+          <t>Manufacturing/Technical Operations</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H178" s="13" t="inlineStr"/>
       <c r="I178" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>Lasse Holm Clausen</t>
+          <t>Marius Muller</t>
         </is>
       </c>
       <c r="B179" s="14" t="inlineStr">
         <is>
-          <t>Head of Process Management, AI &amp; IT Quality</t>
+          <t>Scientific Senior Manager, TDS Biologics AD</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D179" s="16" t="inlineStr">
@@ -9499,40 +9487,44 @@
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Basel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F179" s="13" t="inlineStr">
         <is>
-          <t>Process Management / IT Quality</t>
+          <t>Manufacturing Science/Technical Development</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H179" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H179" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+        </is>
+      </c>
       <c r="I179" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>Marie Czogalla</t>
+          <t>Maxime Bergman</t>
         </is>
       </c>
       <c r="B180" s="14" t="inlineStr">
         <is>
-          <t>Partnering System Change Specialist Sterile Filling</t>
+          <t>Senior Scientist, Process II, Global Process Development, TDS, Drug Product Development &amp; Delivery</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D180" s="16" t="inlineStr">
@@ -9542,55 +9534,59 @@
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>Not specified in source (Europe)</t>
         </is>
       </c>
       <c r="F180" s="13" t="inlineStr">
         <is>
-          <t>Process / Sterile Filling</t>
+          <t>Manufacturing/Process Development</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H180" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H180" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+        </is>
+      </c>
       <c r="I180" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>Azita Saleki-Gerhardt, PhD</t>
+          <t>Roderick Freeman</t>
         </is>
       </c>
       <c r="B181" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Operations Officer</t>
+          <t>Site Quality Head, Novartis RLT (Radioligand Therapy)</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
-        </is>
-      </c>
-      <c r="D181" s="17" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D181" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Global (mfg/eng/quality/supply) (US)</t>
+          <t>US (RLT site)</t>
         </is>
       </c>
       <c r="F181" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>Quality (Site)</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
@@ -9598,42 +9594,46 @@
           <t>Public research</t>
         </is>
       </c>
-      <c r="H181" s="13" t="inlineStr"/>
+      <c r="H181" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="I181" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>Edgardo Hernandez</t>
+          <t>Roland Gander</t>
         </is>
       </c>
       <c r="B182" s="14" t="inlineStr">
         <is>
-          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
+          <t>Global Head Large Molecules / Cell &amp; Gene Therapies; MD, Novartis Pharmaceutical GmbH (Kundl)</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="D182" s="17" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
+          <t>Kundl, Austria (Europe)</t>
         </is>
       </c>
       <c r="F182" s="13" t="inlineStr">
         <is>
-          <t>Executive (Manufacturing)</t>
+          <t>Manufacturing (Large Molecules / CGT)</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
@@ -9644,39 +9644,39 @@
       <c r="H182" s="13" t="inlineStr"/>
       <c r="I182" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>Syed Abbas Yar-Khan</t>
+          <t>Erik Lorin Rasmussen</t>
         </is>
       </c>
       <c r="B183" s="14" t="inlineStr">
         <is>
-          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
+          <t>SVP, Product Supply, Aseptic Manufacturing</t>
         </is>
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="D183" s="17" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="D183" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Hillerod, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F183" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Parenteral / Devices)</t>
+          <t>Manufacturing (Aseptic)</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
@@ -9684,164 +9684,156 @@
           <t>Public research</t>
         </is>
       </c>
-      <c r="H183" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+      <c r="H183" s="13" t="inlineStr"/>
       <c r="I183" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>Delphine Caron</t>
+          <t>Henrik Wulff</t>
         </is>
       </c>
       <c r="B184" s="14" t="inlineStr">
         <is>
-          <t>President, Janssen-Cilag (France)</t>
+          <t>EVP, Product Supply, Quality &amp; IT</t>
         </is>
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
-        </is>
-      </c>
-      <c r="D184" s="17" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Clayton, NC / Kalundborg, DK (Global)</t>
         </is>
       </c>
       <c r="F184" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country President)</t>
+          <t>Executive (Supply/Quality)</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr"/>
       <c r="I184" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>Joaquin Duato</t>
+          <t>Lasse Holm Clausen</t>
         </is>
       </c>
       <c r="B185" s="14" t="inlineStr">
         <is>
-          <t>Chairman &amp; CEO</t>
+          <t>Head of Process Management, AI &amp; IT Quality</t>
         </is>
       </c>
       <c r="C185" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
-        </is>
-      </c>
-      <c r="D185" s="17" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="D185" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F185" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Process Management / IT Quality</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr"/>
       <c r="I185" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>John Reed, MD, PhD</t>
+          <t>Marie Czogalla</t>
         </is>
       </c>
       <c r="B186" s="14" t="inlineStr">
         <is>
-          <t>EVP, Innovative Medicine R&amp;D</t>
+          <t>Partnering System Change Specialist Sterile Filling</t>
         </is>
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
-        </is>
-      </c>
-      <c r="D186" s="17" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F186" s="13" t="inlineStr">
         <is>
-          <t>Executive (R&amp;D)</t>
+          <t>Process / Sterile Filling</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
-        </is>
-      </c>
-      <c r="H186" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H186" s="13" t="inlineStr"/>
       <c r="I186" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>M. Martinez Climent</t>
+          <t>Azita Saleki-Gerhardt, PhD</t>
         </is>
       </c>
       <c r="B187" s="14" t="inlineStr">
         <is>
-          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
+          <t>EVP, Chief Operations Officer</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="D187" s="17" t="inlineStr">
@@ -9851,17 +9843,17 @@
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Global (mfg/eng/quality/supply) (US)</t>
         </is>
       </c>
       <c r="F187" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country DG)</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H187" s="13" t="inlineStr"/>
@@ -9874,17 +9866,17 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>Namal Nawana</t>
+          <t>Edgardo Hernandez</t>
         </is>
       </c>
       <c r="B188" s="14" t="inlineStr">
         <is>
-          <t>Worldwide President, DePuy Synthes</t>
+          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D188" s="17" t="inlineStr">
@@ -9894,17 +9886,17 @@
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Orthopedics manufacturing network (Global)</t>
+          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
         </is>
       </c>
       <c r="F188" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (Manufacturing)</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr"/>
@@ -9917,17 +9909,17 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>Nauman Shah</t>
+          <t>Syed Abbas Yar-Khan</t>
         </is>
       </c>
       <c r="B189" s="14" t="inlineStr">
         <is>
-          <t>Global Head of Business Development</t>
+          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D189" s="17" t="inlineStr">
@@ -9942,17 +9934,17 @@
       </c>
       <c r="F189" s="13" t="inlineStr">
         <is>
-          <t>Executive (Business Development)</t>
+          <t>Manufacturing (Parenteral / Devices)</t>
         </is>
       </c>
       <c r="G189" s="13" t="inlineStr">
         <is>
-          <t>Public research (J&amp;J)</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
         <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
         </is>
       </c>
       <c r="I189" s="14" t="inlineStr">
@@ -9964,12 +9956,12 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>Tim Schmid</t>
+          <t>Delphine Caron</t>
         </is>
       </c>
       <c r="B190" s="14" t="inlineStr">
         <is>
-          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
+          <t>President, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
@@ -9984,12 +9976,12 @@
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="F190" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (Country President)</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
@@ -10007,12 +9999,12 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>Tom Heyman</t>
+          <t>Joaquin Duato</t>
         </is>
       </c>
       <c r="B191" s="14" t="inlineStr">
         <is>
-          <t>CEO, Janssen Pharmaceutica (Belgium)</t>
+          <t>Chairman &amp; CEO</t>
         </is>
       </c>
       <c r="C191" s="13" t="inlineStr">
@@ -10027,12 +10019,12 @@
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Geel, Belgium (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F191" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country CEO)</t>
+          <t>Executive (CEO)</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
@@ -10050,17 +10042,17 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>James Weirich</t>
+          <t>John Reed, MD, PhD</t>
         </is>
       </c>
       <c r="B192" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Cell &amp; Gene Therapy Head</t>
+          <t>EVP, Innovative Medicine R&amp;D</t>
         </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D192" s="17" t="inlineStr">
@@ -10070,20 +10062,24 @@
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F192" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
+          <t>Executive (R&amp;D)</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H192" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="I192" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -10093,17 +10089,17 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>Steffen Lang, PhD</t>
+          <t>M. Martinez Climent</t>
         </is>
       </c>
       <c r="B193" s="14" t="inlineStr">
         <is>
-          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
+          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
         </is>
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D193" s="17" t="inlineStr">
@@ -10113,17 +10109,17 @@
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Durham, NC / Kundl, AT)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="F193" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>Executive (Country DG)</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr"/>
@@ -10136,17 +10132,17 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>Ann Lee</t>
+          <t>Namal Nawana</t>
         </is>
       </c>
       <c r="B194" s="14" t="inlineStr">
         <is>
-          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
+          <t>Worldwide President, DePuy Synthes</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D194" s="17" t="inlineStr">
@@ -10156,17 +10152,17 @@
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>South San Francisco, CA (US)</t>
+          <t>Orthopedics manufacturing network (Global)</t>
         </is>
       </c>
       <c r="F194" s="13" t="inlineStr">
         <is>
-          <t>Technical Development / Manufacturing Science</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr"/>
@@ -10179,17 +10175,17 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>Ashley Magargee</t>
+          <t>Nauman Shah</t>
         </is>
       </c>
       <c r="B195" s="14" t="inlineStr">
         <is>
-          <t>CEO, Genentech</t>
+          <t>Global Head of Business Development</t>
         </is>
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="D195" s="17" t="inlineStr">
@@ -10199,20 +10195,24 @@
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Holly Springs, NC (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F195" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Executive (Business Development)</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H195" s="13" t="inlineStr"/>
+          <t>Public research (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="H195" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="I195" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -10222,98 +10222,98 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>Dana Kendall</t>
+          <t>Tim Schmid</t>
         </is>
       </c>
       <c r="B196" s="14" t="inlineStr">
         <is>
-          <t>General Manager, AbbVie Ireland</t>
+          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
         </is>
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
-        </is>
-      </c>
-      <c r="D196" s="18" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D196" s="17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Dublin (Citywest), Ireland (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country GM)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr"/>
       <c r="I196" s="14" t="inlineStr">
         <is>
-          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>Guy Oliver</t>
+          <t>Tom Heyman</t>
         </is>
       </c>
       <c r="B197" s="14" t="inlineStr">
         <is>
-          <t>General Manager, UK &amp; Ireland</t>
+          <t>CEO, Janssen Pharmaceutica (Belgium)</t>
         </is>
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D197" s="18" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D197" s="17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>UK &amp; Ireland (Europe)</t>
+          <t>Geel, Belgium (Europe)</t>
         </is>
       </c>
       <c r="F197" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country GM)</t>
+          <t>Executive (Country CEO)</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>Public research (J&amp;J)</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr"/>
       <c r="I197" s="14" t="inlineStr">
         <is>
-          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>Maria T.</t>
+          <t>James Weirich</t>
         </is>
       </c>
       <c r="B198" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Medical Science Liaison - Immunology CART</t>
+          <t>Vice President, Cell &amp; Gene Therapy Head</t>
         </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
@@ -10321,42 +10321,42 @@
           <t>Novartis</t>
         </is>
       </c>
-      <c r="D198" s="18" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+      <c r="D198" s="17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
         </is>
       </c>
       <c r="F198" s="13" t="inlineStr">
         <is>
-          <t>Medical Affairs</t>
+          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr"/>
       <c r="I198" s="14" t="inlineStr">
         <is>
-          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>Thierry Diagana</t>
+          <t>Steffen Lang, PhD</t>
         </is>
       </c>
       <c r="B199" s="14" t="inlineStr">
         <is>
-          <t>California Sites Head, Novartis Biomedical Research</t>
+          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
         </is>
       </c>
       <c r="C199" s="13" t="inlineStr">
@@ -10364,19 +10364,19 @@
           <t>Novartis</t>
         </is>
       </c>
-      <c r="D199" s="18" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+      <c r="D199" s="17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>San Diego / Emeryville, CA (US)</t>
+          <t>Global (incl. Durham, NC / Kundl, AT)</t>
         </is>
       </c>
       <c r="F199" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D / Research Site Leadership</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
@@ -10387,59 +10387,317 @@
       <c r="H199" s="13" t="inlineStr"/>
       <c r="I199" s="14" t="inlineStr">
         <is>
-          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
+          <t>Ann Lee</t>
+        </is>
+      </c>
+      <c r="B200" s="14" t="inlineStr">
+        <is>
+          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
+        </is>
+      </c>
+      <c r="C200" s="13" t="inlineStr">
+        <is>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D200" s="17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="E200" s="13" t="inlineStr">
+        <is>
+          <t>South San Francisco, CA (US)</t>
+        </is>
+      </c>
+      <c r="F200" s="13" t="inlineStr">
+        <is>
+          <t>Technical Development / Manufacturing Science</t>
+        </is>
+      </c>
+      <c r="G200" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H200" s="13" t="inlineStr"/>
+      <c r="I200" s="14" t="inlineStr">
+        <is>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="13" t="inlineStr">
+        <is>
+          <t>Ashley Magargee</t>
+        </is>
+      </c>
+      <c r="B201" s="14" t="inlineStr">
+        <is>
+          <t>CEO, Genentech</t>
+        </is>
+      </c>
+      <c r="C201" s="13" t="inlineStr">
+        <is>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D201" s="17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="E201" s="13" t="inlineStr">
+        <is>
+          <t>Holly Springs, NC (US)</t>
+        </is>
+      </c>
+      <c r="F201" s="13" t="inlineStr">
+        <is>
+          <t>Executive (CEO)</t>
+        </is>
+      </c>
+      <c r="G201" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H201" s="13" t="inlineStr"/>
+      <c r="I201" s="14" t="inlineStr">
+        <is>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="13" t="inlineStr">
+        <is>
+          <t>Dana Kendall</t>
+        </is>
+      </c>
+      <c r="B202" s="14" t="inlineStr">
+        <is>
+          <t>General Manager, AbbVie Ireland</t>
+        </is>
+      </c>
+      <c r="C202" s="13" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="D202" s="18" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="E202" s="13" t="inlineStr">
+        <is>
+          <t>Dublin (Citywest), Ireland (Europe)</t>
+        </is>
+      </c>
+      <c r="F202" s="13" t="inlineStr">
+        <is>
+          <t>Executive (Country GM)</t>
+        </is>
+      </c>
+      <c r="G202" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H202" s="13" t="inlineStr"/>
+      <c r="I202" s="14" t="inlineStr">
+        <is>
+          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="13" t="inlineStr">
+        <is>
+          <t>Guy Oliver</t>
+        </is>
+      </c>
+      <c r="B203" s="14" t="inlineStr">
+        <is>
+          <t>General Manager, UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="C203" s="13" t="inlineStr">
+        <is>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D203" s="18" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="E203" s="13" t="inlineStr">
+        <is>
+          <t>UK &amp; Ireland (Europe)</t>
+        </is>
+      </c>
+      <c r="F203" s="13" t="inlineStr">
+        <is>
+          <t>Executive (Country GM)</t>
+        </is>
+      </c>
+      <c r="G203" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H203" s="13" t="inlineStr"/>
+      <c r="I203" s="14" t="inlineStr">
+        <is>
+          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="13" t="inlineStr">
+        <is>
+          <t>Maria T.</t>
+        </is>
+      </c>
+      <c r="B204" s="14" t="inlineStr">
+        <is>
+          <t>Associate Director, Medical Science Liaison - Immunology CART</t>
+        </is>
+      </c>
+      <c r="C204" s="13" t="inlineStr">
+        <is>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D204" s="18" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="E204" s="13" t="inlineStr">
+        <is>
+          <t>United States (US)</t>
+        </is>
+      </c>
+      <c r="F204" s="13" t="inlineStr">
+        <is>
+          <t>Medical Affairs</t>
+        </is>
+      </c>
+      <c r="G204" s="13" t="inlineStr">
+        <is>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H204" s="13" t="inlineStr"/>
+      <c r="I204" s="14" t="inlineStr">
+        <is>
+          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="13" t="inlineStr">
+        <is>
+          <t>Thierry Diagana</t>
+        </is>
+      </c>
+      <c r="B205" s="14" t="inlineStr">
+        <is>
+          <t>California Sites Head, Novartis Biomedical Research</t>
+        </is>
+      </c>
+      <c r="C205" s="13" t="inlineStr">
+        <is>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D205" s="18" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="E205" s="13" t="inlineStr">
+        <is>
+          <t>San Diego / Emeryville, CA (US)</t>
+        </is>
+      </c>
+      <c r="F205" s="13" t="inlineStr">
+        <is>
+          <t>R&amp;D / Research Site Leadership</t>
+        </is>
+      </c>
+      <c r="G205" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H205" s="13" t="inlineStr"/>
+      <c r="I205" s="14" t="inlineStr">
+        <is>
+          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="13" t="inlineStr">
+        <is>
           <t>Franck Bure</t>
         </is>
       </c>
-      <c r="B200" s="14" t="inlineStr">
+      <c r="B206" s="14" t="inlineStr">
         <is>
           <t>(title not stated in source)</t>
         </is>
       </c>
-      <c r="C200" s="13" t="inlineStr">
+      <c r="C206" s="13" t="inlineStr">
         <is>
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D200" s="18" t="inlineStr">
+      <c r="D206" s="18" t="inlineStr">
         <is>
           <t>De-prioritise</t>
         </is>
       </c>
-      <c r="E200" s="13" t="inlineStr">
+      <c r="E206" s="13" t="inlineStr">
         <is>
           <t>Not specified in source (Global)</t>
         </is>
       </c>
-      <c r="F200" s="13" t="inlineStr">
+      <c r="F206" s="13" t="inlineStr">
         <is>
           <t>Unknown (conference speaker)</t>
         </is>
       </c>
-      <c r="G200" s="13" t="inlineStr">
+      <c r="G206" s="13" t="inlineStr">
         <is>
           <t>Public research</t>
         </is>
       </c>
-      <c r="H200" s="13" t="inlineStr">
+      <c r="H206" s="13" t="inlineStr">
         <is>
           <t>ISPE Aseptic Conference 2026</t>
         </is>
       </c>
-      <c r="I200" s="14" t="inlineStr">
+      <c r="I206" s="14" t="inlineStr">
         <is>
           <t>Conference-confirmed contact but role/title unknown — verify function before ranking.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I200"/>
+  <autoFilter ref="A1:I206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10450,7 +10708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10987,12 +11245,12 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Columba McGarvey</t>
+          <t>Elvir J.</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Site Director, AbbVie Ballytivnan (Sligo)</t>
+          <t>Category Manager, Capital Projects (Pharmaceutical)</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -11007,35 +11265,35 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Sligo, Ireland (Europe)</t>
+          <t>Niles, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Procurement (Capital Projects)</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr"/>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Darren Egan</t>
+          <t>Columba McGarvey</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Site Director, AbbVie Manorhamilton Road (Sligo)</t>
+          <t>Site Director, AbbVie Ballytivnan (Sligo)</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -11073,12 +11331,12 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Emilie Leonard</t>
+          <t>Darren Egan</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Head of MSAT</t>
+          <t>Site Director, AbbVie Manorhamilton Road (Sligo)</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -11093,35 +11351,35 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Talence, Nouvelle-Aquitaine, France (Europe)</t>
+          <t>Sligo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr"/>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Christopher Wright</t>
+          <t>Emilie Leonard</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Head of MSAT</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -11136,12 +11394,12 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Talence, Nouvelle-Aquitaine, France (Europe)</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -11152,19 +11410,19 @@
       <c r="H16" s="13" t="inlineStr"/>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Xiaobei Zeng</t>
+          <t>Christopher Wright</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Director, MSAT</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -11184,7 +11442,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -11195,19 +11453,19 @@
       <c r="H17" s="13" t="inlineStr"/>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Azita Saleki-Gerhardt, PhD</t>
+          <t>Xiaobei Zeng</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Operations Officer</t>
+          <t>Director, MSAT</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -11215,42 +11473,42 @@
           <t>AbbVie</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Global (mfg/eng/quality/supply) (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr"/>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Dana Kendall</t>
+          <t>Azita Saleki-Gerhardt, PhD</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>General Manager, AbbVie Ireland</t>
+          <t>EVP, Chief Operations Officer</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -11258,19 +11516,19 @@
           <t>AbbVie</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Dublin (Citywest), Ireland (Europe)</t>
+          <t>Global (mfg/eng/quality/supply) (US)</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country GM)</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -11281,12 +11539,55 @@
       <c r="H19" s="13" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Dana Kendall</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>General Manager, AbbVie Ireland</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Dublin (Citywest), Ireland (Europe)</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Executive (Country GM)</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
           <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I19"/>
+  <autoFilter ref="A1:I20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11800,7 +12101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12380,12 +12681,12 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Rémy Pereira</t>
+          <t>Rachel Miles</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Senior IT Manufacturing Engineer C&amp;Q</t>
+          <t>Director of Capital Projects</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -12400,12 +12701,12 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Marin-Epagnier, Neuchâtel, Switzerland (Europe)</t>
+          <t>Manteno, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (IT)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -12416,19 +12717,19 @@
       <c r="H14" s="13" t="inlineStr"/>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Felix Butkevich</t>
+          <t>Rémy Pereira</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, CQV</t>
+          <t>Senior IT Manufacturing Engineer C&amp;Q</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -12443,12 +12744,12 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Marin-Epagnier, Neuchâtel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering / C&amp;Q (IT)</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -12466,12 +12767,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Roe Hau</t>
+          <t>Eoin Howard</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Director, MSAT Process Engineering</t>
+          <t>CQV Lead (Formulation &amp; Component Prep)</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -12486,12 +12787,12 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Navan, County Meath, Ireland (Europe)</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -12502,19 +12803,19 @@
       <c r="H16" s="13" t="inlineStr"/>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Melissa I. Jiménez</t>
+          <t>Felix Butkevich</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Buyer: Capital Projects and Compliance</t>
+          <t>Associate Director, CQV</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -12529,12 +12830,12 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -12545,19 +12846,19 @@
       <c r="H17" s="13" t="inlineStr"/>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Fabio Lastrucci</t>
+          <t>Mahesh S.</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -12572,7 +12873,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Solothurn, Switzerland (Europe)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -12595,12 +12896,12 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Lisa Martins</t>
+          <t>Roe Hau</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Senior Manager, Capital Projects</t>
+          <t>Director, MSAT Process Engineering</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -12615,12 +12916,12 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Upton, Massachusetts, United States</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>MSAT / Process Engineering</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -12631,19 +12932,19 @@
       <c r="H19" s="13" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Troy M</t>
+          <t>Melissa I. Jiménez</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Manager, Maintenance</t>
+          <t>Buyer: Capital Projects and Compliance</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -12658,12 +12959,12 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Westminster, Massachusetts, United States</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
@@ -12674,19 +12975,19 @@
       <c r="H20" s="13" t="inlineStr"/>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Chris Chumsae, PhD</t>
+          <t>Fabio Lastrucci</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Process Development Analytics</t>
+          <t>CQV Lead</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -12694,46 +12995,42 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>Solothurn, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Process Development / Analytics</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>The Bioprocessing Summit 2026 (Aug 10-13, Boston, MA)</t>
-        </is>
-      </c>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr"/>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Richard Martel</t>
+          <t>Lisa Martins</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Upstream Manager, Single-Use Facility</t>
+          <t>Senior Manager, Capital Projects</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -12741,42 +13038,42 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>Upton, Massachusetts, United States</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Upstream / Single-Use)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Karin Shanahan</t>
+          <t>Troy M</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
+          <t>Manager, Maintenance</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -12784,42 +13081,42 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
+          <t>Westminster, Massachusetts, United States</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Ops)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr"/>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>L. Andrew R.</t>
+          <t>Chris Chumsae, PhD</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
+          <t>Associate Director, Process Development Analytics</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -12834,35 +13131,39 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, New Jersey, United States (US)</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing IT / Operations</t>
+          <t>Process Development / Analytics</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr"/>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>The Bioprocessing Summit 2026 (Aug 10-13, Boston, MA)</t>
+        </is>
+      </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Sean Tonzi</t>
+          <t>Richard Martel</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, CMC Strategy</t>
+          <t>Upstream Manager, Single-Use Facility</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -12877,35 +13178,35 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Syracuse, New York, United States</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>CMC / Process Development</t>
+          <t>Manufacturing (Upstream / Single-Use)</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr"/>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Guy Oliver</t>
+          <t>Karin Shanahan</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>General Manager, UK &amp; Ireland</t>
+          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -12913,19 +13214,19 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>UK &amp; Ireland (Europe)</t>
+          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country GM)</t>
+          <t>Executive (Supply/Ops)</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -12936,12 +13237,141 @@
       <c r="H26" s="13" t="inlineStr"/>
       <c r="I26" s="14" t="inlineStr">
         <is>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>L. Andrew R.</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Lebanon, New Jersey, United States (US)</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Manufacturing IT / Operations</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Sean Tonzi</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Associate Director, CMC Strategy</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Syracuse, New York, United States</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>CMC / Process Development</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Guy Oliver</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>General Manager, UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>UK &amp; Ireland (Europe)</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Executive (Country GM)</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
           <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17629,7 +18059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18389,12 +18819,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Dermot Farnan</t>
+          <t>Dev R.</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>CQV Consultant</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -18409,12 +18839,12 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Greater Boston (US)</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -18432,12 +18862,12 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Jesper Kløve</t>
+          <t>Dermot Farnan</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>CEO, NNE (Novo Nordisk Engineering)</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -18452,17 +18882,17 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Kalundborg, DK / Clayton, NC (NNE-delivered) (Global)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Engineering (EPCM — capital delivery)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr"/>
@@ -18475,12 +18905,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Bettina Jakobsen</t>
+          <t>Jesper Kløve</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Senior Manager API QA MSAT &amp; Support</t>
+          <t>CEO, NNE (Novo Nordisk Engineering)</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -18495,35 +18925,35 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
+          <t>Kalundborg, DK / Clayton, NC (NNE-delivered) (Global)</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QA</t>
+          <t>Engineering (EPCM — capital delivery)</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>LinkedIn Navigator</t>
+          <t>Public research</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr"/>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Camilla Ulrich Hassager</t>
+          <t>Bettina Jakobsen</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Scientific Director, API Quality IT &amp; MSAT</t>
+          <t>Senior Manager API QA MSAT &amp; Support</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -18543,7 +18973,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>MSAT / API Quality</t>
+          <t>MSAT / QA</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -18561,12 +18991,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Trent Rogers</t>
+          <t>Camilla Ulrich Hassager</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Scientific Director, API Quality IT &amp; MSAT</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -18581,12 +19011,12 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Kinston, North Carolina, United States (US)</t>
+          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT / API Quality</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -18597,19 +19027,19 @@
       <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Henrik Wulff</t>
+          <t>Trent Rogers</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>EVP, Product Supply, Quality &amp; IT</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -18617,42 +19047,42 @@
           <t>Novo Nordisk</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC / Kalundborg, DK (Global)</t>
+          <t>Kinston, North Carolina, United States (US)</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Quality)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>Public research</t>
+          <t>LinkedIn Navigator</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr"/>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Lasse Holm Clausen</t>
+          <t>Oleksandr Malenko</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Head of Process Management, AI &amp; IT Quality</t>
+          <t>CQV Project Manager - Fill Finish Expansion</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -18660,19 +19090,19 @@
           <t>Novo Nordisk</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Process Management / IT Quality</t>
+          <t>Engineering / C&amp;Q (Fill-Finish Expansion)</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -18683,19 +19113,19 @@
       <c r="H24" s="13" t="inlineStr"/>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Erik Lorin Rasmussen</t>
+          <t>Henrik Wulff</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Supply, Aseptic Manufacturing</t>
+          <t>EVP, Product Supply, Quality &amp; IT</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -18710,12 +19140,12 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Hillerod, Denmark (Europe)</t>
+          <t>Clayton, NC / Kalundborg, DK (Global)</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Aseptic)</t>
+          <t>Executive (Supply/Quality)</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -18726,12 +19156,98 @@
       <c r="H25" s="13" t="inlineStr"/>
       <c r="I25" s="14" t="inlineStr">
         <is>
+          <t>QA / validation — influences equipment qualification and change control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Lasse Holm Clausen</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Head of Process Management, AI &amp; IT Quality</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Copenhagen, Denmark (Europe)</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Process Management / IT Quality</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>LinkedIn Navigator</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr"/>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>QA / validation — influences equipment qualification and change control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Erik Lorin Rasmussen</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>SVP, Product Supply, Aseptic Manufacturing</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Hillerod, Denmark (Europe)</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Manufacturing (Aseptic)</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Public research</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
           <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/networkmap/data/contacts_all.xlsx
+++ b/networkmap/data/contacts_all.xlsx
@@ -20,9 +20,9 @@
     <sheet name="Roche-Genentech" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision-Makers'!$A$1:$K$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Contacts'!$A$1:$K$508</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AbbVie'!$A$1:$K$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision-Makers'!$A$1:$K$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Contacts'!$A$1:$K$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AbbVie'!$A$1:$K$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AstraZeneca'!$A$1:$K$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BMS'!$A$1:$K$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Eli Lilly'!$A$1:$K$132</definedName>
@@ -597,7 +597,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>507 named contacts across 8 accounts. Tiers = influence over valve spec/procurement/lifecycle. Generated 2026-07-17.</t>
+          <t>508 named contacts across 8 accounts. Tiers = influence over valve spec/procurement/lifecycle. Generated 2026-07-17.</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6520,42 +6520,42 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Pam Cheng</t>
+          <t>John Casey</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>EVP, Global Operations &amp; IT, Chief Sustainability Officer</t>
+          <t>Senior Director, Biologics Contract Manufacturing</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Global (UK/US)</t>
+          <t>Worcester, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>External / Contract Manufacturing</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
@@ -6566,19 +6566,19 @@
       <c r="J11" s="13" t="inlineStr"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Linzell Harris</t>
+          <t>Pam Cheng</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>SVP, Global Supply Chain and Strategy</t>
+          <t>EVP, Global Operations &amp; IT, Chief Sustainability Officer</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -6596,19 +6596,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global (UK/US)</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply Chain)</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -6619,19 +6619,19 @@
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Simon Goldfarb</t>
+          <t>Linzell Harris</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Head of Capital Projects</t>
+          <t>SVP, Global Supply Chain and Strategy</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -6639,52 +6639,52 @@
           <t>AstraZeneca</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Emsworth, England, United Kingdom (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Executive (Supply Chain)</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr"/>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Patrik Ruderer</t>
+          <t>Simon Goldfarb</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Projects - Sweden Biologics Center</t>
+          <t>Head of Capital Projects</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -6697,9 +6697,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Södertälje, Sweden (Europe)</t>
+          <t>Emsworth, England, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -6732,12 +6732,12 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Thomas A. Harris</t>
+          <t>Patrik Ruderer</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Engineering Director, Biologics Manufacturing</t>
+          <t>Director, Capital Projects - Sweden Biologics Center</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -6762,39 +6762,35 @@
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Frederick, Maryland, United States (US)</t>
+          <t>Södertälje, Sweden (Europe)</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Asset Reliability &amp; Maintenance</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Chris Leman</t>
+          <t>Thomas A. Harris</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Global C&amp;Q Director</t>
+          <t>Engineering Director, Biologics Manufacturing</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -6819,35 +6815,39 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom (Europe)</t>
+          <t>Frederick, Maryland, United States (US)</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Global)</t>
+          <t>Asset Reliability &amp; Maintenance</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual</t>
+        </is>
+      </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Ciby Abraham</t>
+          <t>Chris Leman</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Senior Director &amp; Group Manager, Project &amp; Product Leadership</t>
+          <t>Global C&amp;Q Director</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -6865,46 +6865,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>Project &amp; Product Leadership</t>
+          <t>Engineering / C&amp;Q (Global)</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr"/>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Clayton Aguiar</t>
+          <t>Ciby Abraham</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Capital Projects</t>
+          <t>Senior Director &amp; Group Manager, Project &amp; Product Leadership</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -6922,42 +6918,46 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Stockholm, Sweden (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Project &amp; Product Leadership</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual</t>
+        </is>
+      </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Mark Benesch</t>
+          <t>Clayton Aguiar</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Capital Projects Portfolio - Americas</t>
+          <t>Senior Director, Capital Projects</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Catonsville, Maryland, United States (US)</t>
+          <t>Stockholm, Sweden (Europe)</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -7005,12 +7005,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Dan Horner</t>
+          <t>Mark Benesch</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, PT&amp;D Capital Projects</t>
+          <t>Senior Director, Capital Projects Portfolio - Americas</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth Metroplex (US)</t>
+          <t>Catonsville, Maryland, United States (US)</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -7058,65 +7058,65 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Karin Shanahan</t>
+          <t>Dan Horner</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
+          <t>Senior Director, PT&amp;D Capital Projects</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
+          <t>Dallas-Fort Worth Metroplex (US)</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Ops)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr"/>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Catalina Vargas</t>
+          <t>Karin Shanahan</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>SVP, Global Supply Chain</t>
+          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain (Executive)</t>
+          <t>Executive (Supply/Ops)</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
@@ -7154,11 +7154,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit</t>
-        </is>
-      </c>
+      <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="14" t="inlineStr">
         <is>
           <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
@@ -7168,12 +7164,12 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Manisha Desai</t>
+          <t>Catalina Vargas</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Development (Global Product Dev &amp; Supply)</t>
+          <t>SVP, Global Supply Chain</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -7203,7 +7199,7 @@
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>Product Development (Executive)</t>
+          <t>Supply Chain (Executive)</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
@@ -7225,12 +7221,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Odile Smith</t>
+          <t>Manisha Desai</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Vice President &amp; Devens Campus Lead</t>
+          <t>SVP, Product Development (Global Product Dev &amp; Supply)</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -7248,19 +7244,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Product Development (Executive)</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
@@ -7268,22 +7264,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>Pharma Manufacturing World Summit</t>
+        </is>
+      </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Padraig Keane</t>
+          <t>Odile Smith</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Vice President &amp; General Manager, Cruiserath Biologics Campus</t>
+          <t>Vice President &amp; Devens Campus Lead</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Cruiserath (Dublin), Ireland (Europe)</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -7331,12 +7331,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Guy Oliver</t>
+          <t>Padraig Keane</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>General Manager, UK &amp; Ireland</t>
+          <t>Vice President &amp; General Manager, Cruiserath Biologics Campus</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -7344,29 +7344,29 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>UK &amp; Ireland (Europe)</t>
+          <t>Cruiserath (Dublin), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country GM)</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -7377,19 +7377,19 @@
       <c r="J26" s="13" t="inlineStr"/>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Kevin Rosenthal</t>
+          <t>Guy Oliver</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>VP, Site Head Indianapolis</t>
+          <t>General Manager, UK &amp; Ireland</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -7407,19 +7407,19 @@
           <t>Site / Function Head</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>Indianapolis, Indiana, United States (US)</t>
+          <t>UK &amp; Ireland (Europe)</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Executive (Country GM)</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
@@ -7427,26 +7427,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J27" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future</t>
-        </is>
-      </c>
+      <c r="J27" s="13" t="inlineStr"/>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Rachel Miles</t>
+          <t>Kevin Rosenthal</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Director of Capital Projects</t>
+          <t>VP, Site Head Indianapolis</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -7459,9 +7455,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -7471,35 +7467,39 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Manteno, Illinois, United States (US)</t>
+          <t>Indianapolis, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future</t>
+        </is>
+      </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>Anthony Haskell</t>
+          <t>Rachel Miles</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Project Engineering</t>
+          <t>Director of Capital Projects</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Europe (BMS)</t>
+          <t>Manteno, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -7534,14 +7534,10 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr"/>
       <c r="K29" s="14" t="inlineStr">
         <is>
           <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
@@ -7551,12 +7547,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>L. Andrew R.</t>
+          <t>Anthony Haskell</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
+          <t>Director, Capital Project Engineering</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -7574,42 +7570,46 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, New Jersey, United States (US)</t>
+          <t>Europe (BMS)</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing IT / Operations</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe Annual</t>
+        </is>
+      </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Carole Bertola</t>
+          <t>L. Andrew R.</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Director, Global Strategic Sourcing &amp; Procurement</t>
+          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -7634,35 +7634,35 @@
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (global) (Europe)</t>
+          <t>Lebanon, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>Strategic Sourcing / Procurement</t>
+          <t>Manufacturing IT / Operations</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J31" s="13" t="inlineStr"/>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>Roe Hau</t>
+          <t>Carole Bertola</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Director, MSAT Process Engineering</t>
+          <t>Director, Global Strategic Sourcing &amp; Procurement</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -7680,42 +7680,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Switzerland (global) (Europe)</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Engineering</t>
+          <t>Strategic Sourcing / Procurement</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr"/>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Justin McGrath</t>
+          <t>Roe Hau</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Director, Procurement Capital Services &amp; Solutions - Major Projects</t>
+          <t>Director, MSAT Process Engineering</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts, United States</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Procurement (Capital Projects)</t>
+          <t>MSAT / Process Engineering</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -7756,19 +7756,19 @@
       <c r="J33" s="13" t="inlineStr"/>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>Michael Andretich</t>
+          <t>Justin McGrath</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Director, Project Engineering &amp; CQV</t>
+          <t>Director, Procurement Capital Services &amp; Solutions - Major Projects</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>Lancaster, Massachusetts, United States</t>
+          <t>Boston, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Procurement (Capital Projects)</t>
         </is>
       </c>
       <c r="I34" s="13" t="inlineStr">
@@ -7816,12 +7816,12 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>William Gantz</t>
+          <t>Michael Andretich</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Global Technical Service</t>
+          <t>Director, Project Engineering &amp; CQV</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -7846,39 +7846,35 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Lancaster, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Service</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr"/>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Nidhi Shah</t>
+          <t>William Gantz</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Value Stream CAR-T Manufacturing Operations</t>
+          <t>Senior Director, Global Technical Service</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -7896,9 +7892,9 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
@@ -7908,7 +7904,7 @@
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t>Sterile / CAR-T Operations</t>
+          <t>MSAT / Technical Service</t>
         </is>
       </c>
       <c r="I36" s="13" t="inlineStr">
@@ -7918,54 +7914,54 @@
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>ISPE Aseptic Conference</t>
+          <t>ISPE Facilities of the Future</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>Edgardo Hernandez</t>
+          <t>Nidhi Shah</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
+          <t>Senior Director, Value Stream CAR-T Manufacturing Operations</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>Executive (Manufacturing)</t>
+          <t>Sterile / CAR-T Operations</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -7973,22 +7969,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J37" s="13" t="inlineStr"/>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Aseptic Conference</t>
+        </is>
+      </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Melissa Seymour</t>
+          <t>Edgardo Hernandez</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>EVP, Global Quality</t>
+          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -8006,19 +8006,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Global (Indianapolis) (US)</t>
+          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>Executive (Quality)</t>
+          <t>Executive (Manufacturing)</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
@@ -8029,19 +8029,19 @@
       <c r="J38" s="13" t="inlineStr"/>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Syed Abbas Yar-Khan</t>
+          <t>Melissa Seymour</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
+          <t>EVP, Global Quality</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -8059,19 +8059,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global (Indianapolis) (US)</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Parenteral / Devices)</t>
+          <t>Executive (Quality)</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
@@ -8079,26 +8079,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+      <c r="J39" s="13" t="inlineStr"/>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>Tara Tibbs</t>
+          <t>Syed Abbas Yar-Khan</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>SVP &amp; Site Head, Lilly Kinsale</t>
+          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
@@ -8116,19 +8112,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Kinsale (Cork), Ireland (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Manufacturing (Parenteral / Devices)</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
@@ -8136,22 +8132,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J40" s="13" t="inlineStr"/>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
+        </is>
+      </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Victor Cruz</t>
+          <t>Tara Tibbs</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>SVP, Corporate Engineering &amp; Global Health, Safety &amp; Environmental</t>
+          <t>SVP &amp; Site Head, Lilly Kinsale</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Global (Indianapolis) (US)</t>
+          <t>Kinsale (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Corporate)</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
@@ -8189,26 +8189,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J41" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+      <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>Dave Riordan</t>
+          <t>Victor Cruz</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; Site Head, Lilly Limerick</t>
+          <t>SVP, Corporate Engineering &amp; Global Health, Safety &amp; Environmental</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -8233,12 +8229,12 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Limerick, Ireland (Europe)</t>
+          <t>Global (Indianapolis) (US)</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership (Capital Project)</t>
+          <t>Engineering (Corporate)</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
@@ -8246,22 +8242,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J42" s="13" t="inlineStr"/>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Matthew von Zirkelbach</t>
+          <t>Dave Riordan</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Vice President &amp; Site Head, Lilly Medicine Foundry (Lebanon)</t>
+          <t>VP &amp; Site Head, Lilly Limerick</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, IN (US)</t>
+          <t>Limerick, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -8309,12 +8309,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>F.R. Casal</t>
+          <t>Matthew von Zirkelbach</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Assistant Director</t>
+          <t>Vice President &amp; Site Head, Lilly Medicine Foundry (Lebanon)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -8322,52 +8322,52 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="F44" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Lebanon, IN (US)</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Assistant Director)</t>
+          <t>Site Leadership (Capital Project)</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr"/>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Molly Wagner</t>
+          <t>F.R. Casal</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Procurement</t>
+          <t>Assistant Director</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -8392,35 +8392,35 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>Strategic Sourcing / Procurement</t>
+          <t>Manufacturing (Assistant Director)</t>
         </is>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Bill Cook</t>
+          <t>Molly Wagner</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Lean Manufacturing / Operational Excellence - Director</t>
+          <t>Director, Capital Procurement</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -8445,35 +8445,35 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Clinton, Indiana, United States (US)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>Operational Excellence / Lean</t>
+          <t>Strategic Sourcing / Procurement</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J46" s="13" t="inlineStr"/>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Robert O'Keeffe</t>
+          <t>Bill Cook</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Engineering Tech Centre</t>
+          <t>Lean Manufacturing / Operational Excellence - Director</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -8491,46 +8491,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Limerick NGB) (Europe)</t>
+          <t>Clinton, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Operational Excellence / Lean</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr"/>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Massimiliano Ammannito</t>
+          <t>Robert O'Keeffe</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Sr Director - Facilities, Utilities &amp; Capital Projects</t>
+          <t>Senior Director, Engineering Tech Centre</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -8555,12 +8551,12 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Italy (Europe)</t>
+          <t>Ireland (Limerick NGB) (Europe)</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>Utilities / Capital Projects</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -8570,24 +8566,24 @@
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>ISPE Aseptic Conference; ISPE Europe</t>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Kenneth Swank</t>
+          <t>Massimiliano Ammannito</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Sr. Director - Major Capital Projects</t>
+          <t>Sr Director - Facilities, Utilities &amp; Capital Projects</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
@@ -8612,88 +8608,92 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Greenwood, Indiana, United States (US)</t>
+          <t>Italy (Europe)</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Utilities / Capital Projects</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Aseptic Conference; ISPE Europe</t>
+        </is>
+      </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Joaquin Duato</t>
+          <t>Kenneth Swank</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Chairman &amp; CEO</t>
+          <t>Sr. Director - Major Capital Projects</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Greenwood, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr"/>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Kathryn E. Wengel</t>
+          <t>Joaquin Duato</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Technical Operations &amp; Risk Officer</t>
+          <t>Chairman &amp; CEO</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -8711,19 +8711,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F51" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Enterprise-wide (Global) (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Quality/Supply Chain (Executive)</t>
+          <t>Executive (CEO)</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
@@ -8734,19 +8734,19 @@
       <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>John Reed, MD, PhD</t>
+          <t>Kathryn E. Wengel</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>EVP, Innovative Medicine R&amp;D</t>
+          <t>EVP, Chief Technical Operations &amp; Risk Officer</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -8764,19 +8764,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Enterprise-wide (Global) (US)</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>Executive (R&amp;D)</t>
+          <t>Engineering/Quality/Supply Chain (Executive)</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -8784,26 +8784,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J52" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J52" s="13" t="inlineStr"/>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Tim Schmid</t>
+          <t>John Reed, MD, PhD</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
+          <t>EVP, Innovative Medicine R&amp;D</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -8833,7 +8829,7 @@
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (R&amp;D)</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
@@ -8841,7 +8837,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J53" s="13" t="inlineStr"/>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -8851,12 +8851,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Dana Daneshvari</t>
+          <t>Tim Schmid</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>General Manager &amp; VP Manufacturing, Large Molecule Site</t>
+          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -8874,19 +8874,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Manufacturing (Site GM)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -8897,19 +8897,19 @@
       <c r="J54" s="13" t="inlineStr"/>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>Delphine Caron</t>
+          <t>Dana Daneshvari</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>President, Janssen-Cilag (France)</t>
+          <t>General Manager &amp; VP Manufacturing, Large Molecule Site</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -8927,19 +8927,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country President)</t>
+          <t>Engineering/Manufacturing (Site GM)</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr">
@@ -8950,19 +8950,19 @@
       <c r="J55" s="13" t="inlineStr"/>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Robin Kumoluyi</t>
+          <t>Delphine Caron</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
+          <t>President, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -8980,19 +8980,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F56" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>Quality (Executive)</t>
+          <t>Executive (Country President)</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
@@ -9000,26 +9000,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J56" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit</t>
-        </is>
-      </c>
+      <c r="J56" s="13" t="inlineStr"/>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>Leila Schwery-Bou-Diab</t>
+          <t>Robin Kumoluyi</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>VP Manufacturing &amp; Technical Operations</t>
+          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -9044,12 +9040,12 @@
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Technical Operations</t>
+          <t>Quality (Executive)</t>
         </is>
       </c>
       <c r="I57" s="13" t="inlineStr">
@@ -9057,22 +9053,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J57" s="13" t="inlineStr"/>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>Pharma Manufacturing World Summit</t>
+        </is>
+      </c>
       <c r="K57" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Namal Nawana</t>
+          <t>Leila Schwery-Bou-Diab</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Worldwide President, DePuy Synthes</t>
+          <t>VP Manufacturing &amp; Technical Operations</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -9090,19 +9090,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>Orthopedics manufacturing network (Global)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Manufacturing/Technical Operations</t>
         </is>
       </c>
       <c r="I58" s="13" t="inlineStr">
@@ -9113,19 +9113,19 @@
       <c r="J58" s="13" t="inlineStr"/>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>Stephanie Striegler</t>
+          <t>Namal Nawana</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>General Manager, Janssen Schaffhausen</t>
+          <t>Worldwide President, DePuy Synthes</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -9133,29 +9133,29 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>Schaffhausen, Switzerland (Europe)</t>
+          <t>Orthopedics manufacturing network (Global)</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>Executive (Site GM)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr">
@@ -9166,19 +9166,19 @@
       <c r="J59" s="13" t="inlineStr"/>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Nauman Shah</t>
+          <t>Stephanie Striegler</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Global Head of Business Development</t>
+          <t>General Manager, Janssen Schaffhausen</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -9196,19 +9196,19 @@
           <t>Site / Function Head</t>
         </is>
       </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Schaffhausen, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>Executive (Business Development)</t>
+          <t>Executive (Site GM)</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
@@ -9216,26 +9216,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J60" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J60" s="13" t="inlineStr"/>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>Mary Houchin</t>
+          <t>Nauman Shah</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>MSAT Site Director</t>
+          <t>Global Head of Business Development</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -9253,42 +9249,46 @@
           <t>Site / Function Head</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Site Director)</t>
+          <t>Executive (Business Development)</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J61" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>Armelle Santelli</t>
+          <t>Mary Houchin</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
+          <t>MSAT Site Director</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -9301,47 +9301,47 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E62" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="F62" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>Quality/Regulatory</t>
+          <t>MSAT (Site Director)</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J62" s="13" t="inlineStr"/>
       <c r="K62" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Goeran Crucius</t>
+          <t>Armelle Santelli</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Director MSAT Cross Platform Engineering</t>
+          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -9359,42 +9359,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>Schaffhausen, Switzerland (Europe)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Engineering</t>
+          <t>Quality/Regulatory</t>
         </is>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J63" s="13" t="inlineStr"/>
       <c r="K63" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>Scott Foell</t>
+          <t>Goeran Crucius</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Projects</t>
+          <t>Director MSAT Cross Platform Engineering</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>Vacaville, California, United States (US)</t>
+          <t>Schaffhausen, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>MSAT / Engineering</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr">
@@ -9435,19 +9435,19 @@
       <c r="J64" s="13" t="inlineStr"/>
       <c r="K64" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>Thomas Kelly</t>
+          <t>Scott Foell</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Director, Cell Engineering &amp; Analytical Sciences</t>
+          <t>Director, Capital Projects</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -9472,39 +9472,35 @@
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (US)</t>
+          <t>Vacaville, California, United States (US)</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D/Manufacturing Science</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J65" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International 2026 (Sep 22-25, Boston, MA)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J65" s="13" t="inlineStr"/>
       <c r="K65" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Alan Bateman</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Director, Systems Architecture, Digital &amp; Execution</t>
+          <t>Director, Cell Engineering &amp; Analytical Sciences</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -9522,19 +9518,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F66" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Not specified in source (US)</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>Advanced Mfg / Digital</t>
+          <t>R&amp;D/Manufacturing Science</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
@@ -9544,24 +9540,24 @@
       </c>
       <c r="J66" s="13" t="inlineStr">
         <is>
-          <t>ISPE</t>
+          <t>BioProcess International 2026 (Sep 22-25, Boston, MA)</t>
         </is>
       </c>
       <c r="K66" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Dan Usas</t>
+          <t>Alan Bateman</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Director, Technical Operations</t>
+          <t>Director, Systems Architecture, Digital &amp; Execution</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
@@ -9579,19 +9575,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Service</t>
+          <t>Advanced Mfg / Digital</t>
         </is>
       </c>
       <c r="I67" s="13" t="inlineStr">
@@ -9599,22 +9595,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J67" s="13" t="inlineStr"/>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>ISPE</t>
+        </is>
+      </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>M. Martinez Climent</t>
+          <t>Dan Usas</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
+          <t>Director, Technical Operations</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -9632,19 +9632,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country DG)</t>
+          <t>MSAT / Technical Service</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -9655,19 +9655,19 @@
       <c r="J68" s="13" t="inlineStr"/>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>Peter Millili</t>
+          <t>M. Martinez Climent</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Manufacturing Science &amp; Technology</t>
+          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -9685,19 +9685,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F69" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Service</t>
+          <t>Executive (Country DG)</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
@@ -9705,26 +9705,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J69" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual</t>
-        </is>
-      </c>
+      <c r="J69" s="13" t="inlineStr"/>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Peter Millili, PhD</t>
+          <t>Peter Millili</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Manufacturing Science and Technology (MSAT), Advanced Therapies</t>
+          <t>Senior Director, Manufacturing Science &amp; Technology</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -9749,12 +9745,12 @@
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Philadelphia / Spring House, PA</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>MSAT / Technical Service</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
@@ -9764,7 +9760,7 @@
       </c>
       <c r="J70" s="13" t="inlineStr">
         <is>
-          <t>ISPE Annual Meeting &amp; Expo 2026 (Oct 18-21, National Harbor, MD)</t>
+          <t>ISPE Annual</t>
         </is>
       </c>
       <c r="K70" s="14" t="inlineStr">
@@ -9776,12 +9772,12 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Donald Powers</t>
+          <t>Peter Millili, PhD</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Sr Director Advanced Therapies MSAT</t>
+          <t>Senior Director, Manufacturing Science and Technology (MSAT), Advanced Therapies</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -9806,7 +9802,7 @@
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Greater Philadelphia (US)</t>
+          <t>Philadelphia / Spring House, PA</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -9816,10 +9812,14 @@
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J71" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual Meeting &amp; Expo 2026 (Oct 18-21, National Harbor, MD)</t>
+        </is>
+      </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
           <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
@@ -9829,65 +9829,65 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>Steffen Lang, PhD</t>
+          <t>Donald Powers</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
+          <t>Sr Director Advanced Therapies MSAT</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E72" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E72" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Durham, NC / Kundl, AT)</t>
+          <t>Greater Philadelphia (US)</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J72" s="13" t="inlineStr"/>
       <c r="K72" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>James Weirich</t>
+          <t>Steffen Lang, PhD</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Cell &amp; Gene Therapy Head</t>
+          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
+          <t>Global (incl. Durham, NC / Kundl, AT)</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="I73" s="13" t="inlineStr">
@@ -9935,12 +9935,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>Nicholas J. Casale</t>
+          <t>James Weirich</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Head of Strategy &amp; Operational Excellence, Cell &amp; Gene Tech Dev &amp; Mfg</t>
+          <t>Vice President, Cell &amp; Gene Therapy Head</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -9948,29 +9948,29 @@
           <t>Novartis</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F74" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>Morris Plains, New Jersey, United States (US)</t>
+          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering / Op-Ex</t>
+          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
@@ -9978,26 +9978,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J74" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual; ISPE Aseptic</t>
-        </is>
-      </c>
+      <c r="J74" s="13" t="inlineStr"/>
       <c r="K74" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Soma shekara</t>
+          <t>Nicholas J. Casale</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>Director - Global Project Engineering</t>
+          <t>Head of Strategy &amp; Operational Excellence, Cell &amp; Gene Tech Dev &amp; Mfg</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -10010,9 +10006,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E75" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -10022,20 +10018,24 @@
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Morris Plains, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Global Project Engineering)</t>
+          <t>Manufacturing Engineering / Op-Ex</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J75" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual; ISPE Aseptic</t>
+        </is>
+      </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
           <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
@@ -10045,27 +10045,27 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>Lone Charlotte Larsen</t>
+          <t>Soma shekara</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>Corporate Vice President, Novo Nordisk Production Chartres</t>
+          <t>Director - Global Project Engineering</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E76" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E76" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
@@ -10075,35 +10075,35 @@
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>Chartres, France (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership (Capital Project)</t>
+          <t>Engineering (Global Project Engineering)</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J76" s="13" t="inlineStr"/>
       <c r="K76" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Henrik Wulff</t>
+          <t>Lone Charlotte Larsen</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>EVP, Product Supply, Quality &amp; IT</t>
+          <t>Corporate Vice President, Novo Nordisk Production Chartres</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -10121,19 +10121,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F77" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC / Kalundborg, DK (Global)</t>
+          <t>Chartres, France (Europe)</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Quality)</t>
+          <t>Site Leadership (Capital Project)</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
@@ -10144,19 +10144,19 @@
       <c r="J77" s="13" t="inlineStr"/>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>Jay Kuykendall</t>
+          <t>Henrik Wulff</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Project Vice President, Clayton (NC) Expansion</t>
+          <t>EVP, Product Supply, Quality &amp; IT</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -10174,19 +10174,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F78" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F78" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC (US)</t>
+          <t>Clayton, NC / Kalundborg, DK (Global)</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Capital Project</t>
+          <t>Executive (Supply/Quality)</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -10197,19 +10197,19 @@
       <c r="J78" s="13" t="inlineStr"/>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>Flemming Dahl</t>
+          <t>Jay Kuykendall</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>SVP, Head of Product Supply Fill &amp; Finish Expansions</t>
+          <t>Project Vice President, Clayton (NC) Expansion</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>Global (Denmark) (Europe)</t>
+          <t>Clayton, NC (US)</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>Engineering / Capital Project (Fill-Finish Expansions)</t>
+          <t>Engineering/Capital Project</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr">
@@ -10257,12 +10257,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>Erik Lorin Rasmussen</t>
+          <t>Flemming Dahl</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Supply, Aseptic Manufacturing</t>
+          <t>SVP, Head of Product Supply Fill &amp; Finish Expansions</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -10280,19 +10280,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F80" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>Hillerod, Denmark (Europe)</t>
+          <t>Global (Denmark) (Europe)</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Aseptic)</t>
+          <t>Engineering / Capital Project (Fill-Finish Expansions)</t>
         </is>
       </c>
       <c r="I80" s="13" t="inlineStr">
@@ -10303,19 +10303,19 @@
       <c r="J80" s="13" t="inlineStr"/>
       <c r="K80" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>Peter C. Luke</t>
+          <t>Erik Lorin Rasmussen</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Capital Projects - Drug Substance</t>
+          <t>SVP, Product Supply, Aseptic Manufacturing</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -10333,42 +10333,42 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Hillerod, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Manufacturing (Aseptic)</t>
         </is>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J81" s="13" t="inlineStr"/>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>Lasse Holm Clausen</t>
+          <t>Peter C. Luke</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Head of Process Management, AI &amp; IT Quality</t>
+          <t>Vice President, Capital Projects - Drug Substance</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -10376,19 +10376,19 @@
           <t>Novo Nordisk</t>
         </is>
       </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F82" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>Process Management / IT Quality</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I82" s="13" t="inlineStr">
@@ -10409,19 +10409,19 @@
       <c r="J82" s="13" t="inlineStr"/>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>Jason Trussell</t>
+          <t>Lasse Holm Clausen</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Director - Bioteam, MSAT and QC</t>
+          <t>Head of Process Management, AI &amp; IT Quality</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -10434,24 +10434,24 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E83" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="F83" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
+        </is>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>Grantham, New Hampshire, United States (US)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QC</t>
+          <t>Process Management / IT Quality</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -10462,19 +10462,19 @@
       <c r="J83" s="13" t="inlineStr"/>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>Mads Overgaard</t>
+          <t>Jason Trussell</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Director - PS API MSAT Technology &amp; Process Facilities</t>
+          <t>Director - Bioteam, MSAT and QC</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Grantham, New Hampshire, United States (US)</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Facilities</t>
+          <t>MSAT / QC</t>
         </is>
       </c>
       <c r="I84" s="13" t="inlineStr">
@@ -10522,12 +10522,12 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>Anne-Sophie Eriksen</t>
+          <t>Mads Overgaard</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Director Life Cycle Management, MSAT &amp; QC</t>
+          <t>Director - PS API MSAT Technology &amp; Process Facilities</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -10552,12 +10552,12 @@
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>Farum, Capital Region of Denmark, Denmark (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QC</t>
+          <t>MSAT / Process Facilities</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -10575,12 +10575,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>Søren Thuesen Pedersen</t>
+          <t>Anne-Sophie Eriksen</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Director, CMC Manufacturing Development</t>
+          <t>Director Life Cycle Management, MSAT &amp; QC</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -10598,46 +10598,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F86" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G86" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Farum, Capital Region of Denmark, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
-          <t>Process Development / CMC</t>
+          <t>MSAT / QC</t>
         </is>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J86" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe; ISPE Nordic</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J86" s="13" t="inlineStr"/>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>Søren Rønsted</t>
+          <t>Søren Thuesen Pedersen</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>Director, Finished Product Manufacturing and Science (MSAT)</t>
+          <t>Director, CMC Manufacturing Development</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -10655,42 +10651,46 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F87" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Finished Product)</t>
+          <t>Process Development / CMC</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J87" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J87" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe; ISPE Nordic</t>
+        </is>
+      </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>Hao Jiang</t>
+          <t>Søren Rønsted</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>Director, Synthetic API MSAT</t>
+          <t>Director, Finished Product Manufacturing and Science (MSAT)</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Synthetic API)</t>
+          <t>MSAT (Finished Product)</t>
         </is>
       </c>
       <c r="I88" s="13" t="inlineStr">
@@ -10738,12 +10738,12 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>Larry Lane</t>
+          <t>Hao Jiang</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>Project Director, Construction &amp; Engineering (Clayton Expansion)</t>
+          <t>Director, Synthetic API MSAT</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -10768,39 +10768,35 @@
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC (US)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Construction / Capital Project)</t>
+          <t>MSAT (Synthetic API)</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J89" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J89" s="13" t="inlineStr"/>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>Jørgen Falkbøll</t>
+          <t>Larry Lane</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>Project Director, Diabetes API (US project)</t>
+          <t>Project Director, Construction &amp; Engineering (Clayton Expansion)</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -10825,12 +10821,12 @@
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>Denmark / United States (Europe)</t>
+          <t>Clayton, NC (US)</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Construction / Capital Project)</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
@@ -10840,7 +10836,7 @@
       </c>
       <c r="J90" s="13" t="inlineStr">
         <is>
-          <t>ISPE Europe; ISPE Nordic</t>
+          <t>ISPE Facilities of the Future 2026</t>
         </is>
       </c>
       <c r="K90" s="14" t="inlineStr">
@@ -10852,12 +10848,12 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>Camilla Ulrich Hassager</t>
+          <t>Jørgen Falkbøll</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>Scientific Director, API Quality IT &amp; MSAT</t>
+          <t>Project Director, Diabetes API (US project)</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -10882,50 +10878,54 @@
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
+          <t>Denmark / United States (Europe)</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>MSAT / API Quality</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J91" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J91" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe; ISPE Nordic</t>
+        </is>
+      </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>Georg Singewald</t>
+          <t>Camilla Ulrich Hassager</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>SVP, Head of Global Engineering, MSAT &amp; Sustainability</t>
+          <t>Scientific Director, API Quality IT &amp; MSAT</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E92" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -10935,24 +10935,20 @@
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (global) (Europe)</t>
+          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t>Global Engineering (Executive)</t>
+          <t>MSAT / API Quality</t>
         </is>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J92" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe; ISPE Facilities of the Future</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J92" s="13" t="inlineStr"/>
       <c r="K92" s="14" t="inlineStr">
         <is>
           <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
@@ -10962,12 +10958,12 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>Ann Lee</t>
+          <t>Georg Singewald</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
+          <t>SVP, Head of Global Engineering, MSAT &amp; Sustainability</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -10985,19 +10981,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F93" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>South San Francisco, CA (US)</t>
+          <t>Basel, Switzerland (global) (Europe)</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>Technical Development / Manufacturing Science</t>
+          <t>Global Engineering (Executive)</t>
         </is>
       </c>
       <c r="I93" s="13" t="inlineStr">
@@ -11005,22 +11001,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J93" s="13" t="inlineStr"/>
+      <c r="J93" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe; ISPE Facilities of the Future</t>
+        </is>
+      </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>Nazeli Dertsakian</t>
+          <t>Ann Lee</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; GM Genentech Oceanside / VP, Global Head Clinical Supply Operations</t>
+          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -11038,19 +11038,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F94" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>Oceanside, CA (US)</t>
+          <t>South San Francisco, CA (US)</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Technical Development / Manufacturing Science</t>
         </is>
       </c>
       <c r="I94" s="13" t="inlineStr">
@@ -11058,26 +11058,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J94" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+      <c r="J94" s="13" t="inlineStr"/>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>Michael Greening</t>
+          <t>Nazeli Dertsakian</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>Executive Director, Head of Project Delivery (US)</t>
+          <t>VP &amp; GM Genentech Oceanside / VP, Global Head Clinical Supply Operations</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -11085,14 +11081,14 @@
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D95" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
@@ -11102,12 +11098,12 @@
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Oceanside, CA (US)</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="I95" s="13" t="inlineStr">
@@ -11117,24 +11113,24 @@
       </c>
       <c r="J95" s="13" t="inlineStr">
         <is>
-          <t>ISPE Facilities of the Future; ISPE Annual</t>
+          <t>ISPE Facilities of the Future 2026</t>
         </is>
       </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>Eric Fallon</t>
+          <t>Michael Greening</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Head of Global Biologics MSAT, Drug Substance</t>
+          <t>Executive Director, Head of Project Delivery (US)</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -11164,7 +11160,7 @@
       </c>
       <c r="H96" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Service</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I96" s="13" t="inlineStr">
@@ -11174,24 +11170,24 @@
       </c>
       <c r="J96" s="13" t="inlineStr">
         <is>
-          <t>ISPE Biotechnology; ISPE Annual</t>
+          <t>ISPE Facilities of the Future; ISPE Annual</t>
         </is>
       </c>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>Mark Nolden</t>
+          <t>Eric Fallon</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Head of Global MSAT Drug Substance Process Stewards</t>
+          <t>Head of Global Biologics MSAT, Drug Substance</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -11216,20 +11212,24 @@
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>Iffeldorf, Bavaria, Germany (Global)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Drug Substance)</t>
+          <t>MSAT / Technical Service</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J97" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J97" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Biotechnology; ISPE Annual</t>
+        </is>
+      </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
           <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
@@ -11239,12 +11239,12 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>Christian Rutz</t>
+          <t>Mark Nolden</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Head of Global PTT Engineering &amp; Technology, Global MSAT/Engineering/Sustainability</t>
+          <t>Head of Global MSAT Drug Substance Process Stewards</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>Mannheim, Baden-Württemberg, Germany (Global)</t>
+          <t>Iffeldorf, Bavaria, Germany (Global)</t>
         </is>
       </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
-          <t>Engineering / MSAT (Global)</t>
+          <t>MSAT (Drug Substance)</t>
         </is>
       </c>
       <c r="I98" s="13" t="inlineStr">
@@ -11292,12 +11292,12 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>Christian Hakemeyer</t>
+          <t>Christian Rutz</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>Head of MSAT</t>
+          <t>Head of Global PTT Engineering &amp; Technology, Global MSAT/Engineering/Sustainability</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>Ilvesheim, Baden-Württemberg, Germany (Europe)</t>
+          <t>Mannheim, Baden-Württemberg, Germany (Global)</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Engineering / MSAT (Global)</t>
         </is>
       </c>
       <c r="I99" s="13" t="inlineStr">
@@ -11345,7 +11345,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>Marco Wetzstein</t>
+          <t>Christian Hakemeyer</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>Ilvesheim, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
@@ -11398,7 +11398,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>Qianting Ou</t>
+          <t>Marco Wetzstein</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>China (Asia)</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -11451,12 +11451,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>Ethan Wang</t>
+          <t>Qianting Ou</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>Head of Maintenance</t>
+          <t>Head of MSAT</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>Shanghai, China (Asia)</t>
+          <t>China (Asia)</t>
         </is>
       </c>
       <c r="H102" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="I102" s="13" t="inlineStr">
@@ -11497,19 +11497,19 @@
       <c r="J102" s="13" t="inlineStr"/>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>Maurice Lambrecht</t>
+          <t>Ethan Wang</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>Head of Maintenance F&amp;E und SHE</t>
+          <t>Head of Maintenance</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Mannheim, Baden-Württemberg, Germany (Europe)</t>
+          <t>Shanghai, China (Asia)</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
@@ -11557,12 +11557,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>Pascal Ruf</t>
+          <t>Maurice Lambrecht</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>Head of Site Infrastructure Engineering</t>
+          <t>Head of Maintenance F&amp;E und SHE</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (Europe)</t>
+          <t>Mannheim, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="H104" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Utilities / Site Infrastructure)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="I104" s="13" t="inlineStr">
@@ -11603,19 +11603,19 @@
       <c r="J104" s="13" t="inlineStr"/>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>Troy Farris</t>
+          <t>Pascal Ruf</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Projects</t>
+          <t>Head of Site Infrastructure Engineering</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -11628,9 +11628,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E105" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Basel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Utilities / Site Infrastructure)</t>
         </is>
       </c>
       <c r="I105" s="13" t="inlineStr">
@@ -11656,12 +11656,65 @@
       <c r="J105" s="13" t="inlineStr"/>
       <c r="K105" s="14" t="inlineStr">
         <is>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>Troy Farris</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>Director, Capital Projects</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E106" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F106" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>Greater Indianapolis (US)</t>
+        </is>
+      </c>
+      <c r="H106" s="13" t="inlineStr">
+        <is>
+          <t>Engineering (Capital Projects)</t>
+        </is>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J106" s="13" t="inlineStr"/>
+      <c r="K106" s="14" t="inlineStr">
+        <is>
           <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K105"/>
+  <autoFilter ref="A1:K106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11672,7 +11725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K508"/>
+  <dimension ref="A1:K509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -35433,12 +35486,12 @@
     <row r="447">
       <c r="A447" s="13" t="inlineStr">
         <is>
-          <t>Luis M González</t>
+          <t>John Casey</t>
         </is>
       </c>
       <c r="B447" s="14" t="inlineStr">
         <is>
-          <t>Supply Chain QA Project Manager</t>
+          <t>Senior Director, Biologics Contract Manufacturing</t>
         </is>
       </c>
       <c r="C447" s="13" t="inlineStr">
@@ -35446,14 +35499,14 @@
           <t>AbbVie</t>
         </is>
       </c>
-      <c r="D447" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E447" s="16" t="inlineStr">
-        <is>
-          <t>Manager / Lead</t>
+      <c r="D447" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E447" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F447" s="22" t="inlineStr">
@@ -35463,50 +35516,50 @@
       </c>
       <c r="G447" s="13" t="inlineStr">
         <is>
-          <t>Highland Park, Illinois, United States (US)</t>
+          <t>Worcester, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H447" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain / QA</t>
+          <t>External / Contract Manufacturing</t>
         </is>
       </c>
       <c r="I447" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J447" s="13" t="inlineStr"/>
       <c r="K447" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="13" t="inlineStr">
         <is>
-          <t>Arun Krishnan</t>
+          <t>Luis M González</t>
         </is>
       </c>
       <c r="B448" s="14" t="inlineStr">
         <is>
-          <t>VP, Global Network Planning (Global Supply Chain &amp; Strategy)</t>
+          <t>Supply Chain QA Project Manager</t>
         </is>
       </c>
       <c r="C448" s="13" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
-        </is>
-      </c>
-      <c r="D448" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E448" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="D448" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E448" s="16" t="inlineStr">
+        <is>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F448" s="22" t="inlineStr">
@@ -35516,35 +35569,35 @@
       </c>
       <c r="G448" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Highland Park, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H448" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply Chain)</t>
+          <t>Supply Chain / QA</t>
         </is>
       </c>
       <c r="I448" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J448" s="13" t="inlineStr"/>
       <c r="K448" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="13" t="inlineStr">
         <is>
-          <t>Ciby Abraham</t>
+          <t>Arun Krishnan</t>
         </is>
       </c>
       <c r="B449" s="14" t="inlineStr">
         <is>
-          <t>Senior Director &amp; Group Manager, Project &amp; Product Leadership</t>
+          <t>VP, Global Network Planning (Global Supply Chain &amp; Strategy)</t>
         </is>
       </c>
       <c r="C449" s="13" t="inlineStr">
@@ -35557,9 +35610,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E449" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E449" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F449" s="22" t="inlineStr">
@@ -35569,12 +35622,12 @@
       </c>
       <c r="G449" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H449" s="13" t="inlineStr">
         <is>
-          <t>Project &amp; Product Leadership</t>
+          <t>Executive (Supply Chain)</t>
         </is>
       </c>
       <c r="I449" s="13" t="inlineStr">
@@ -35582,26 +35635,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J449" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual</t>
-        </is>
-      </c>
+      <c r="J449" s="13" t="inlineStr"/>
       <c r="K449" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="13" t="inlineStr">
         <is>
-          <t>Linzell Harris</t>
+          <t>Ciby Abraham</t>
         </is>
       </c>
       <c r="B450" s="14" t="inlineStr">
         <is>
-          <t>SVP, Global Supply Chain and Strategy</t>
+          <t>Senior Director &amp; Group Manager, Project &amp; Product Leadership</t>
         </is>
       </c>
       <c r="C450" s="13" t="inlineStr">
@@ -35609,14 +35658,14 @@
           <t>AstraZeneca</t>
         </is>
       </c>
-      <c r="D450" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E450" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D450" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E450" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F450" s="22" t="inlineStr">
@@ -35626,12 +35675,12 @@
       </c>
       <c r="G450" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H450" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply Chain)</t>
+          <t>Project &amp; Product Leadership</t>
         </is>
       </c>
       <c r="I450" s="13" t="inlineStr">
@@ -35639,37 +35688,41 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J450" s="13" t="inlineStr"/>
+      <c r="J450" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual</t>
+        </is>
+      </c>
       <c r="K450" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="13" t="inlineStr">
         <is>
-          <t>Brian Whitlock</t>
+          <t>Linzell Harris</t>
         </is>
       </c>
       <c r="B451" s="14" t="inlineStr">
         <is>
-          <t>VP, Strategic Sourcing &amp; Procurement (R&amp;D)</t>
+          <t>SVP, Global Supply Chain and Strategy</t>
         </is>
       </c>
       <c r="C451" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
-        </is>
-      </c>
-      <c r="D451" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E451" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="D451" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E451" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F451" s="22" t="inlineStr">
@@ -35679,12 +35732,12 @@
       </c>
       <c r="G451" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H451" s="13" t="inlineStr">
         <is>
-          <t>Strategic Sourcing / Procurement</t>
+          <t>Executive (Supply Chain)</t>
         </is>
       </c>
       <c r="I451" s="13" t="inlineStr">
@@ -35702,12 +35755,12 @@
     <row r="452">
       <c r="A452" s="13" t="inlineStr">
         <is>
-          <t>Carole Bertola</t>
+          <t>Brian Whitlock</t>
         </is>
       </c>
       <c r="B452" s="14" t="inlineStr">
         <is>
-          <t>Director, Global Strategic Sourcing &amp; Procurement</t>
+          <t>VP, Strategic Sourcing &amp; Procurement (R&amp;D)</t>
         </is>
       </c>
       <c r="C452" s="13" t="inlineStr">
@@ -35715,14 +35768,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D452" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E452" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="D452" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E452" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F452" s="22" t="inlineStr">
@@ -35732,7 +35785,7 @@
       </c>
       <c r="G452" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (global) (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H452" s="13" t="inlineStr">
@@ -35755,12 +35808,12 @@
     <row r="453">
       <c r="A453" s="13" t="inlineStr">
         <is>
-          <t>Catalina Vargas</t>
+          <t>Carole Bertola</t>
         </is>
       </c>
       <c r="B453" s="14" t="inlineStr">
         <is>
-          <t>SVP, Global Supply Chain</t>
+          <t>Director, Global Strategic Sourcing &amp; Procurement</t>
         </is>
       </c>
       <c r="C453" s="13" t="inlineStr">
@@ -35768,14 +35821,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D453" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E453" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D453" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E453" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F453" s="22" t="inlineStr">
@@ -35785,12 +35838,12 @@
       </c>
       <c r="G453" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Switzerland (global) (Europe)</t>
         </is>
       </c>
       <c r="H453" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain (Executive)</t>
+          <t>Strategic Sourcing / Procurement</t>
         </is>
       </c>
       <c r="I453" s="13" t="inlineStr">
@@ -35798,11 +35851,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J453" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit</t>
-        </is>
-      </c>
+      <c r="J453" s="13" t="inlineStr"/>
       <c r="K453" s="14" t="inlineStr">
         <is>
           <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
@@ -35812,12 +35861,12 @@
     <row r="454">
       <c r="A454" s="13" t="inlineStr">
         <is>
-          <t>Chris Chumsae, PhD</t>
+          <t>Catalina Vargas</t>
         </is>
       </c>
       <c r="B454" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Process Development Analytics</t>
+          <t>SVP, Global Supply Chain</t>
         </is>
       </c>
       <c r="C454" s="13" t="inlineStr">
@@ -35825,14 +35874,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D454" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E454" s="16" t="inlineStr">
-        <is>
-          <t>Assoc Director</t>
+      <c r="D454" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E454" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F454" s="22" t="inlineStr">
@@ -35842,12 +35891,12 @@
       </c>
       <c r="G454" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H454" s="13" t="inlineStr">
         <is>
-          <t>Process Development / Analytics</t>
+          <t>Supply Chain (Executive)</t>
         </is>
       </c>
       <c r="I454" s="13" t="inlineStr">
@@ -35857,24 +35906,24 @@
       </c>
       <c r="J454" s="13" t="inlineStr">
         <is>
-          <t>The Bioprocessing Summit 2026 (Aug 10-13, Boston, MA)</t>
+          <t>Pharma Manufacturing World Summit</t>
         </is>
       </c>
       <c r="K454" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="13" t="inlineStr">
         <is>
-          <t>Karin Shanahan</t>
+          <t>Chris Chumsae, PhD</t>
         </is>
       </c>
       <c r="B455" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
+          <t>Associate Director, Process Development Analytics</t>
         </is>
       </c>
       <c r="C455" s="13" t="inlineStr">
@@ -35882,14 +35931,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D455" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E455" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D455" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E455" s="16" t="inlineStr">
+        <is>
+          <t>Assoc Director</t>
         </is>
       </c>
       <c r="F455" s="22" t="inlineStr">
@@ -35899,12 +35948,12 @@
       </c>
       <c r="G455" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="H455" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Ops)</t>
+          <t>Process Development / Analytics</t>
         </is>
       </c>
       <c r="I455" s="13" t="inlineStr">
@@ -35912,22 +35961,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J455" s="13" t="inlineStr"/>
+      <c r="J455" s="13" t="inlineStr">
+        <is>
+          <t>The Bioprocessing Summit 2026 (Aug 10-13, Boston, MA)</t>
+        </is>
+      </c>
       <c r="K455" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="13" t="inlineStr">
         <is>
-          <t>L. Andrew R.</t>
+          <t>Karin Shanahan</t>
         </is>
       </c>
       <c r="B456" s="14" t="inlineStr">
         <is>
-          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
+          <t>EVP, Chief Supply Chain &amp; Operations Officer</t>
         </is>
       </c>
       <c r="C456" s="13" t="inlineStr">
@@ -35935,14 +35988,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D456" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E456" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="D456" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E456" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F456" s="22" t="inlineStr">
@@ -35952,35 +36005,35 @@
       </c>
       <c r="G456" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, New Jersey, United States (US)</t>
+          <t>Global (incl. Cruiserath, IE / Devens, MA) (US)</t>
         </is>
       </c>
       <c r="H456" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing IT / Operations</t>
+          <t>Executive (Supply/Ops)</t>
         </is>
       </c>
       <c r="I456" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J456" s="13" t="inlineStr"/>
       <c r="K456" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="13" t="inlineStr">
         <is>
-          <t>Manisha Desai</t>
+          <t>L. Andrew R.</t>
         </is>
       </c>
       <c r="B457" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Development (Global Product Dev &amp; Supply)</t>
+          <t>Director, Commercial Mfg GMP IT Systems – Operations Functional Lead</t>
         </is>
       </c>
       <c r="C457" s="13" t="inlineStr">
@@ -35988,14 +36041,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D457" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E457" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D457" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E457" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F457" s="22" t="inlineStr">
@@ -36005,39 +36058,35 @@
       </c>
       <c r="G457" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Lebanon, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="H457" s="13" t="inlineStr">
         <is>
-          <t>Product Development (Executive)</t>
+          <t>Manufacturing IT / Operations</t>
         </is>
       </c>
       <c r="I457" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J457" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J457" s="13" t="inlineStr"/>
       <c r="K457" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="13" t="inlineStr">
         <is>
-          <t>Nidhi Shah</t>
+          <t>Manisha Desai</t>
         </is>
       </c>
       <c r="B458" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Value Stream CAR-T Manufacturing Operations</t>
+          <t>SVP, Product Development (Global Product Dev &amp; Supply)</t>
         </is>
       </c>
       <c r="C458" s="13" t="inlineStr">
@@ -36045,14 +36094,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D458" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E458" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="D458" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E458" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F458" s="22" t="inlineStr">
@@ -36067,7 +36116,7 @@
       </c>
       <c r="H458" s="13" t="inlineStr">
         <is>
-          <t>Sterile / CAR-T Operations</t>
+          <t>Product Development (Executive)</t>
         </is>
       </c>
       <c r="I458" s="13" t="inlineStr">
@@ -36077,24 +36126,24 @@
       </c>
       <c r="J458" s="13" t="inlineStr">
         <is>
-          <t>ISPE Aseptic Conference</t>
+          <t>Pharma Manufacturing World Summit</t>
         </is>
       </c>
       <c r="K458" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="13" t="inlineStr">
         <is>
-          <t>Richard Martel</t>
+          <t>Nidhi Shah</t>
         </is>
       </c>
       <c r="B459" s="14" t="inlineStr">
         <is>
-          <t>Upstream Manager, Single-Use Facility</t>
+          <t>Senior Director, Value Stream CAR-T Manufacturing Operations</t>
         </is>
       </c>
       <c r="C459" s="13" t="inlineStr">
@@ -36102,14 +36151,14 @@
           <t>Bristol Myers Squibb</t>
         </is>
       </c>
-      <c r="D459" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E459" s="16" t="inlineStr">
-        <is>
-          <t>Manager / Lead</t>
+      <c r="D459" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E459" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F459" s="22" t="inlineStr">
@@ -36119,12 +36168,12 @@
       </c>
       <c r="G459" s="13" t="inlineStr">
         <is>
-          <t>Devens, MA (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H459" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Upstream / Single-Use)</t>
+          <t>Sterile / CAR-T Operations</t>
         </is>
       </c>
       <c r="I459" s="13" t="inlineStr">
@@ -36132,7 +36181,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J459" s="13" t="inlineStr"/>
+      <c r="J459" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Aseptic Conference</t>
+        </is>
+      </c>
       <c r="K459" s="14" t="inlineStr">
         <is>
           <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
@@ -36142,12 +36195,12 @@
     <row r="460">
       <c r="A460" s="13" t="inlineStr">
         <is>
-          <t>Sean Tonzi</t>
+          <t>Richard Martel</t>
         </is>
       </c>
       <c r="B460" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, CMC Strategy</t>
+          <t>Upstream Manager, Single-Use Facility</t>
         </is>
       </c>
       <c r="C460" s="13" t="inlineStr">
@@ -36162,7 +36215,7 @@
       </c>
       <c r="E460" s="16" t="inlineStr">
         <is>
-          <t>Assoc Director</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F460" s="22" t="inlineStr">
@@ -36172,50 +36225,50 @@
       </c>
       <c r="G460" s="13" t="inlineStr">
         <is>
-          <t>Syracuse, New York, United States</t>
+          <t>Devens, MA (US)</t>
         </is>
       </c>
       <c r="H460" s="13" t="inlineStr">
         <is>
-          <t>CMC / Process Development</t>
+          <t>Manufacturing (Upstream / Single-Use)</t>
         </is>
       </c>
       <c r="I460" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J460" s="13" t="inlineStr"/>
       <c r="K460" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="13" t="inlineStr">
         <is>
-          <t>Ainhoa Nieto</t>
+          <t>Sean Tonzi</t>
         </is>
       </c>
       <c r="B461" s="14" t="inlineStr">
         <is>
-          <t>Associate VP, Manufacturing</t>
+          <t>Associate Director, CMC Strategy</t>
         </is>
       </c>
       <c r="C461" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="D461" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E461" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D461" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E461" s="16" t="inlineStr">
+        <is>
+          <t>Assoc Director</t>
         </is>
       </c>
       <c r="F461" s="22" t="inlineStr">
@@ -36225,39 +36278,35 @@
       </c>
       <c r="G461" s="13" t="inlineStr">
         <is>
-          <t>Japan (Global)</t>
+          <t>Syracuse, New York, United States</t>
         </is>
       </c>
       <c r="H461" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>CMC / Process Development</t>
         </is>
       </c>
       <c r="I461" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J461" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J461" s="13" t="inlineStr"/>
       <c r="K461" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="13" t="inlineStr">
         <is>
-          <t>Bill Cook</t>
+          <t>Ainhoa Nieto</t>
         </is>
       </c>
       <c r="B462" s="14" t="inlineStr">
         <is>
-          <t>Lean Manufacturing / Operational Excellence - Director</t>
+          <t>Associate VP, Manufacturing</t>
         </is>
       </c>
       <c r="C462" s="13" t="inlineStr">
@@ -36270,9 +36319,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E462" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E462" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F462" s="22" t="inlineStr">
@@ -36282,20 +36331,24 @@
       </c>
       <c r="G462" s="13" t="inlineStr">
         <is>
-          <t>Clinton, Indiana, United States (US)</t>
+          <t>Japan (Global)</t>
         </is>
       </c>
       <c r="H462" s="13" t="inlineStr">
         <is>
-          <t>Operational Excellence / Lean</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="I462" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J462" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J462" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="K462" s="14" t="inlineStr">
         <is>
           <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
@@ -36305,12 +36358,12 @@
     <row r="463">
       <c r="A463" s="13" t="inlineStr">
         <is>
-          <t>F.R. Casal</t>
+          <t>Bill Cook</t>
         </is>
       </c>
       <c r="B463" s="14" t="inlineStr">
         <is>
-          <t>Assistant Director</t>
+          <t>Lean Manufacturing / Operational Excellence - Director</t>
         </is>
       </c>
       <c r="C463" s="13" t="inlineStr">
@@ -36335,12 +36388,12 @@
       </c>
       <c r="G463" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Clinton, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H463" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Assistant Director)</t>
+          <t>Operational Excellence / Lean</t>
         </is>
       </c>
       <c r="I463" s="13" t="inlineStr">
@@ -36358,12 +36411,12 @@
     <row r="464">
       <c r="A464" s="13" t="inlineStr">
         <is>
-          <t>Melissa Seymour</t>
+          <t>F.R. Casal</t>
         </is>
       </c>
       <c r="B464" s="14" t="inlineStr">
         <is>
-          <t>EVP, Global Quality</t>
+          <t>Assistant Director</t>
         </is>
       </c>
       <c r="C464" s="13" t="inlineStr">
@@ -36371,14 +36424,14 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D464" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E464" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D464" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E464" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F464" s="22" t="inlineStr">
@@ -36388,35 +36441,35 @@
       </c>
       <c r="G464" s="13" t="inlineStr">
         <is>
-          <t>Global (Indianapolis) (US)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="H464" s="13" t="inlineStr">
         <is>
-          <t>Executive (Quality)</t>
+          <t>Manufacturing (Assistant Director)</t>
         </is>
       </c>
       <c r="I464" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J464" s="13" t="inlineStr"/>
       <c r="K464" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="13" t="inlineStr">
         <is>
-          <t>Molly Wagner</t>
+          <t>Melissa Seymour</t>
         </is>
       </c>
       <c r="B465" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Procurement</t>
+          <t>EVP, Global Quality</t>
         </is>
       </c>
       <c r="C465" s="13" t="inlineStr">
@@ -36424,14 +36477,14 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D465" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E465" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="D465" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E465" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F465" s="22" t="inlineStr">
@@ -36441,12 +36494,12 @@
       </c>
       <c r="G465" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Global (Indianapolis) (US)</t>
         </is>
       </c>
       <c r="H465" s="13" t="inlineStr">
         <is>
-          <t>Strategic Sourcing / Procurement</t>
+          <t>Executive (Quality)</t>
         </is>
       </c>
       <c r="I465" s="13" t="inlineStr">
@@ -36457,24 +36510,24 @@
       <c r="J465" s="13" t="inlineStr"/>
       <c r="K465" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="13" t="inlineStr">
         <is>
-          <t>Alan Bateman</t>
+          <t>Molly Wagner</t>
         </is>
       </c>
       <c r="B466" s="14" t="inlineStr">
         <is>
-          <t>Director, Systems Architecture, Digital &amp; Execution</t>
+          <t>Director, Capital Procurement</t>
         </is>
       </c>
       <c r="C466" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D466" s="17" t="inlineStr">
@@ -36494,12 +36547,12 @@
       </c>
       <c r="G466" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="H466" s="13" t="inlineStr">
         <is>
-          <t>Advanced Mfg / Digital</t>
+          <t>Strategic Sourcing / Procurement</t>
         </is>
       </c>
       <c r="I466" s="13" t="inlineStr">
@@ -36507,26 +36560,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J466" s="13" t="inlineStr">
-        <is>
-          <t>ISPE</t>
-        </is>
-      </c>
+      <c r="J466" s="13" t="inlineStr"/>
       <c r="K466" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="13" t="inlineStr">
         <is>
-          <t>Armelle Santelli</t>
+          <t>Alan Bateman</t>
         </is>
       </c>
       <c r="B467" s="14" t="inlineStr">
         <is>
-          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
+          <t>Director, Systems Architecture, Digital &amp; Execution</t>
         </is>
       </c>
       <c r="C467" s="13" t="inlineStr">
@@ -36551,12 +36600,12 @@
       </c>
       <c r="G467" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H467" s="13" t="inlineStr">
         <is>
-          <t>Quality/Regulatory</t>
+          <t>Advanced Mfg / Digital</t>
         </is>
       </c>
       <c r="I467" s="13" t="inlineStr">
@@ -36564,22 +36613,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J467" s="13" t="inlineStr"/>
+      <c r="J467" s="13" t="inlineStr">
+        <is>
+          <t>ISPE</t>
+        </is>
+      </c>
       <c r="K467" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="13" t="inlineStr">
         <is>
-          <t>Carlos Arbelaez, PhD</t>
+          <t>Armelle Santelli</t>
         </is>
       </c>
       <c r="B468" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Cell Therapy Process Development</t>
+          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C468" s="13" t="inlineStr">
@@ -36587,14 +36640,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D468" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E468" s="16" t="inlineStr">
-        <is>
-          <t>Assoc Director</t>
+      <c r="D468" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E468" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F468" s="22" t="inlineStr">
@@ -36604,12 +36657,12 @@
       </c>
       <c r="G468" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (US)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H468" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Process Development</t>
+          <t>Quality/Regulatory</t>
         </is>
       </c>
       <c r="I468" s="13" t="inlineStr">
@@ -36617,26 +36670,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J468" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International US West 2026 (Mar 9-11, San Diego, CA) — session confirmed Mar 10, 2:30pm</t>
-        </is>
-      </c>
+      <c r="J468" s="13" t="inlineStr"/>
       <c r="K468" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="13" t="inlineStr">
         <is>
-          <t>Dapo Ajayi</t>
+          <t>Carlos Arbelaez, PhD</t>
         </is>
       </c>
       <c r="B469" s="14" t="inlineStr">
         <is>
-          <t>VP, Innovative Medicine Supply Chain</t>
+          <t>Associate Director, Cell Therapy Process Development</t>
         </is>
       </c>
       <c r="C469" s="13" t="inlineStr">
@@ -36649,9 +36698,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E469" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="E469" s="16" t="inlineStr">
+        <is>
+          <t>Assoc Director</t>
         </is>
       </c>
       <c r="F469" s="22" t="inlineStr">
@@ -36661,12 +36710,12 @@
       </c>
       <c r="G469" s="13" t="inlineStr">
         <is>
-          <t>Wilson, NC (US)</t>
+          <t>Not specified in source (US)</t>
         </is>
       </c>
       <c r="H469" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Manufacturing/Process Development</t>
         </is>
       </c>
       <c r="I469" s="13" t="inlineStr">
@@ -36674,22 +36723,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J469" s="13" t="inlineStr"/>
+      <c r="J469" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International US West 2026 (Mar 9-11, San Diego, CA) — session confirmed Mar 10, 2:30pm</t>
+        </is>
+      </c>
       <c r="K469" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="13" t="inlineStr">
         <is>
-          <t>David Estape</t>
+          <t>Dapo Ajayi</t>
         </is>
       </c>
       <c r="B470" s="14" t="inlineStr">
         <is>
-          <t>Technology Manager, Biotechnology</t>
+          <t>VP, Innovative Medicine Supply Chain</t>
         </is>
       </c>
       <c r="C470" s="13" t="inlineStr">
@@ -36702,9 +36755,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E470" s="16" t="inlineStr">
-        <is>
-          <t>Manager / Lead</t>
+      <c r="E470" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F470" s="22" t="inlineStr">
@@ -36714,12 +36767,12 @@
       </c>
       <c r="G470" s="13" t="inlineStr">
         <is>
-          <t>Europe (J&amp;J)</t>
+          <t>Wilson, NC (US)</t>
         </is>
       </c>
       <c r="H470" s="13" t="inlineStr">
         <is>
-          <t>Process Development / Advanced Mfg</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="I470" s="13" t="inlineStr">
@@ -36727,26 +36780,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J470" s="13" t="inlineStr">
-        <is>
-          <t>ISPE</t>
-        </is>
-      </c>
+      <c r="J470" s="13" t="inlineStr"/>
       <c r="K470" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="13" t="inlineStr">
         <is>
-          <t>Johan Van Hoof, MD</t>
+          <t>David Estape</t>
         </is>
       </c>
       <c r="B471" s="14" t="inlineStr">
         <is>
-          <t>Global Therapeutic Area Head IDV, Vaccines</t>
+          <t>Technology Manager, Biotechnology</t>
         </is>
       </c>
       <c r="C471" s="13" t="inlineStr">
@@ -36754,14 +36803,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D471" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E471" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="D471" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E471" s="16" t="inlineStr">
+        <is>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F471" s="22" t="inlineStr">
@@ -36771,12 +36820,12 @@
       </c>
       <c r="G471" s="13" t="inlineStr">
         <is>
-          <t>Leiden, Netherlands (Europe)</t>
+          <t>Europe (J&amp;J)</t>
         </is>
       </c>
       <c r="H471" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D/Vaccines</t>
+          <t>Process Development / Advanced Mfg</t>
         </is>
       </c>
       <c r="I471" s="13" t="inlineStr">
@@ -36784,22 +36833,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J471" s="13" t="inlineStr"/>
+      <c r="J471" s="13" t="inlineStr">
+        <is>
+          <t>ISPE</t>
+        </is>
+      </c>
       <c r="K471" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="13" t="inlineStr">
         <is>
-          <t>Julian Hooks</t>
+          <t>Johan Van Hoof, MD</t>
         </is>
       </c>
       <c r="B472" s="14" t="inlineStr">
         <is>
-          <t>VP, Global Services Operations &amp; Procurement</t>
+          <t>Global Therapeutic Area Head IDV, Vaccines</t>
         </is>
       </c>
       <c r="C472" s="13" t="inlineStr">
@@ -36824,12 +36877,12 @@
       </c>
       <c r="G472" s="13" t="inlineStr">
         <is>
-          <t>Enterprise-wide (Global) (US)</t>
+          <t>Leiden, Netherlands (Europe)</t>
         </is>
       </c>
       <c r="H472" s="13" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>R&amp;D/Vaccines</t>
         </is>
       </c>
       <c r="I472" s="13" t="inlineStr">
@@ -36840,19 +36893,19 @@
       <c r="J472" s="13" t="inlineStr"/>
       <c r="K472" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="13" t="inlineStr">
         <is>
-          <t>Kimberly Lounds Foster</t>
+          <t>Julian Hooks</t>
         </is>
       </c>
       <c r="B473" s="14" t="inlineStr">
         <is>
-          <t>Global Head, Advanced Therapies Supply Chain</t>
+          <t>VP, Global Services Operations &amp; Procurement</t>
         </is>
       </c>
       <c r="C473" s="13" t="inlineStr">
@@ -36877,12 +36930,12 @@
       </c>
       <c r="G473" s="13" t="inlineStr">
         <is>
-          <t>Advanced therapies manufacturing network (US)</t>
+          <t>Enterprise-wide (Global) (US)</t>
         </is>
       </c>
       <c r="H473" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="I473" s="13" t="inlineStr">
@@ -36900,12 +36953,12 @@
     <row r="474">
       <c r="A474" s="13" t="inlineStr">
         <is>
-          <t>Leila Schwery-Bou-Diab</t>
+          <t>Kimberly Lounds Foster</t>
         </is>
       </c>
       <c r="B474" s="14" t="inlineStr">
         <is>
-          <t>VP Manufacturing &amp; Technical Operations</t>
+          <t>Global Head, Advanced Therapies Supply Chain</t>
         </is>
       </c>
       <c r="C474" s="13" t="inlineStr">
@@ -36913,14 +36966,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D474" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E474" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D474" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E474" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F474" s="22" t="inlineStr">
@@ -36930,12 +36983,12 @@
       </c>
       <c r="G474" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>Advanced therapies manufacturing network (US)</t>
         </is>
       </c>
       <c r="H474" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Technical Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="I474" s="13" t="inlineStr">
@@ -36946,19 +36999,19 @@
       <c r="J474" s="13" t="inlineStr"/>
       <c r="K474" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="13" t="inlineStr">
         <is>
-          <t>Marius Muller</t>
+          <t>Leila Schwery-Bou-Diab</t>
         </is>
       </c>
       <c r="B475" s="14" t="inlineStr">
         <is>
-          <t>Scientific Senior Manager, TDS Biologics AD</t>
+          <t>VP Manufacturing &amp; Technical Operations</t>
         </is>
       </c>
       <c r="C475" s="13" t="inlineStr">
@@ -36966,14 +37019,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D475" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E475" s="16" t="inlineStr">
-        <is>
-          <t>Sr Manager / Principal</t>
+      <c r="D475" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E475" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F475" s="22" t="inlineStr">
@@ -36983,12 +37036,12 @@
       </c>
       <c r="G475" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (Europe)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H475" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing Science/Technical Development</t>
+          <t>Manufacturing/Technical Operations</t>
         </is>
       </c>
       <c r="I475" s="13" t="inlineStr">
@@ -36996,11 +37049,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J475" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
-        </is>
-      </c>
+      <c r="J475" s="13" t="inlineStr"/>
       <c r="K475" s="14" t="inlineStr">
         <is>
           <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
@@ -37010,12 +37059,12 @@
     <row r="476">
       <c r="A476" s="13" t="inlineStr">
         <is>
-          <t>Maxime Bergman</t>
+          <t>Marius Muller</t>
         </is>
       </c>
       <c r="B476" s="14" t="inlineStr">
         <is>
-          <t>Senior Scientist, Process II, Global Process Development, TDS, Drug Product Development &amp; Delivery</t>
+          <t>Scientific Senior Manager, TDS Biologics AD</t>
         </is>
       </c>
       <c r="C476" s="13" t="inlineStr">
@@ -37023,14 +37072,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D476" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E476" s="13" t="inlineStr">
-        <is>
-          <t>Senior IC</t>
+      <c r="D476" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E476" s="16" t="inlineStr">
+        <is>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F476" s="22" t="inlineStr">
@@ -37040,12 +37089,12 @@
       </c>
       <c r="G476" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (Europe)</t>
+          <t>Basel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H476" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Process Development</t>
+          <t>Manufacturing Science/Technical Development</t>
         </is>
       </c>
       <c r="I476" s="13" t="inlineStr">
@@ -37060,19 +37109,19 @@
       </c>
       <c r="K476" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="13" t="inlineStr">
         <is>
-          <t>Robin Kumoluyi</t>
+          <t>Maxime Bergman</t>
         </is>
       </c>
       <c r="B477" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
+          <t>Senior Scientist, Process II, Global Process Development, TDS, Drug Product Development &amp; Delivery</t>
         </is>
       </c>
       <c r="C477" s="13" t="inlineStr">
@@ -37080,14 +37129,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D477" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E477" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D477" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E477" s="13" t="inlineStr">
+        <is>
+          <t>Senior IC</t>
         </is>
       </c>
       <c r="F477" s="22" t="inlineStr">
@@ -37097,12 +37146,12 @@
       </c>
       <c r="G477" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Not specified in source (Europe)</t>
         </is>
       </c>
       <c r="H477" s="13" t="inlineStr">
         <is>
-          <t>Quality (Executive)</t>
+          <t>Manufacturing/Process Development</t>
         </is>
       </c>
       <c r="I477" s="13" t="inlineStr">
@@ -37112,39 +37161,39 @@
       </c>
       <c r="J477" s="13" t="inlineStr">
         <is>
-          <t>Pharma Manufacturing World Summit</t>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
         </is>
       </c>
       <c r="K477" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="13" t="inlineStr">
         <is>
-          <t>Roderick Freeman</t>
+          <t>Robin Kumoluyi</t>
         </is>
       </c>
       <c r="B478" s="14" t="inlineStr">
         <is>
-          <t>Site Quality Head, Novartis RLT (Radioligand Therapy)</t>
+          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
         </is>
       </c>
       <c r="C478" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D478" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E478" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D478" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E478" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F478" s="22" t="inlineStr">
@@ -37154,12 +37203,12 @@
       </c>
       <c r="G478" s="13" t="inlineStr">
         <is>
-          <t>US (RLT site)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H478" s="13" t="inlineStr">
         <is>
-          <t>Quality (Site)</t>
+          <t>Quality (Executive)</t>
         </is>
       </c>
       <c r="I478" s="13" t="inlineStr">
@@ -37169,7 +37218,7 @@
       </c>
       <c r="J478" s="13" t="inlineStr">
         <is>
-          <t>ISPE Facilities of the Future 2026</t>
+          <t>Pharma Manufacturing World Summit</t>
         </is>
       </c>
       <c r="K478" s="14" t="inlineStr">
@@ -37181,12 +37230,12 @@
     <row r="479">
       <c r="A479" s="13" t="inlineStr">
         <is>
-          <t>Roland Gander</t>
+          <t>Roderick Freeman</t>
         </is>
       </c>
       <c r="B479" s="14" t="inlineStr">
         <is>
-          <t>Global Head Large Molecules / Cell &amp; Gene Therapies; MD, Novartis Pharmaceutical GmbH (Kundl)</t>
+          <t>Site Quality Head, Novartis RLT (Radioligand Therapy)</t>
         </is>
       </c>
       <c r="C479" s="13" t="inlineStr">
@@ -37194,9 +37243,9 @@
           <t>Novartis</t>
         </is>
       </c>
-      <c r="D479" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
+      <c r="D479" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
         </is>
       </c>
       <c r="E479" s="13" t="inlineStr">
@@ -37211,12 +37260,12 @@
       </c>
       <c r="G479" s="13" t="inlineStr">
         <is>
-          <t>Kundl, Austria (Europe)</t>
+          <t>US (RLT site)</t>
         </is>
       </c>
       <c r="H479" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Large Molecules / CGT)</t>
+          <t>Quality (Site)</t>
         </is>
       </c>
       <c r="I479" s="13" t="inlineStr">
@@ -37224,37 +37273,41 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J479" s="13" t="inlineStr"/>
+      <c r="J479" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="K479" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="13" t="inlineStr">
         <is>
-          <t>Erik Lorin Rasmussen</t>
+          <t>Roland Gander</t>
         </is>
       </c>
       <c r="B480" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Supply, Aseptic Manufacturing</t>
+          <t>Global Head Large Molecules / Cell &amp; Gene Therapies; MD, Novartis Pharmaceutical GmbH (Kundl)</t>
         </is>
       </c>
       <c r="C480" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
-        </is>
-      </c>
-      <c r="D480" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E480" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D480" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E480" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F480" s="22" t="inlineStr">
@@ -37264,12 +37317,12 @@
       </c>
       <c r="G480" s="13" t="inlineStr">
         <is>
-          <t>Hillerod, Denmark (Europe)</t>
+          <t>Kundl, Austria (Europe)</t>
         </is>
       </c>
       <c r="H480" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Aseptic)</t>
+          <t>Manufacturing (Large Molecules / CGT)</t>
         </is>
       </c>
       <c r="I480" s="13" t="inlineStr">
@@ -37280,19 +37333,19 @@
       <c r="J480" s="13" t="inlineStr"/>
       <c r="K480" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="13" t="inlineStr">
         <is>
-          <t>Henrik Wulff</t>
+          <t>Erik Lorin Rasmussen</t>
         </is>
       </c>
       <c r="B481" s="14" t="inlineStr">
         <is>
-          <t>EVP, Product Supply, Quality &amp; IT</t>
+          <t>SVP, Product Supply, Aseptic Manufacturing</t>
         </is>
       </c>
       <c r="C481" s="13" t="inlineStr">
@@ -37317,12 +37370,12 @@
       </c>
       <c r="G481" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC / Kalundborg, DK (Global)</t>
+          <t>Hillerod, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H481" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Quality)</t>
+          <t>Manufacturing (Aseptic)</t>
         </is>
       </c>
       <c r="I481" s="13" t="inlineStr">
@@ -37333,19 +37386,19 @@
       <c r="J481" s="13" t="inlineStr"/>
       <c r="K481" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="13" t="inlineStr">
         <is>
-          <t>Lasse Holm Clausen</t>
+          <t>Henrik Wulff</t>
         </is>
       </c>
       <c r="B482" s="14" t="inlineStr">
         <is>
-          <t>Head of Process Management, AI &amp; IT Quality</t>
+          <t>EVP, Product Supply, Quality &amp; IT</t>
         </is>
       </c>
       <c r="C482" s="13" t="inlineStr">
@@ -37353,14 +37406,14 @@
           <t>Novo Nordisk</t>
         </is>
       </c>
-      <c r="D482" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E482" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
+      <c r="D482" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E482" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F482" s="22" t="inlineStr">
@@ -37370,17 +37423,17 @@
       </c>
       <c r="G482" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Clayton, NC / Kalundborg, DK (Global)</t>
         </is>
       </c>
       <c r="H482" s="13" t="inlineStr">
         <is>
-          <t>Process Management / IT Quality</t>
+          <t>Executive (Supply/Quality)</t>
         </is>
       </c>
       <c r="I482" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J482" s="13" t="inlineStr"/>
@@ -37393,12 +37446,12 @@
     <row r="483">
       <c r="A483" s="13" t="inlineStr">
         <is>
-          <t>Søren Thuesen Pedersen</t>
+          <t>Lasse Holm Clausen</t>
         </is>
       </c>
       <c r="B483" s="14" t="inlineStr">
         <is>
-          <t>Director, CMC Manufacturing Development</t>
+          <t>Head of Process Management, AI &amp; IT Quality</t>
         </is>
       </c>
       <c r="C483" s="13" t="inlineStr">
@@ -37411,9 +37464,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E483" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E483" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F483" s="22" t="inlineStr">
@@ -37423,44 +37476,40 @@
       </c>
       <c r="G483" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H483" s="13" t="inlineStr">
         <is>
-          <t>Process Development / CMC</t>
+          <t>Process Management / IT Quality</t>
         </is>
       </c>
       <c r="I483" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J483" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe; ISPE Nordic</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J483" s="13" t="inlineStr"/>
       <c r="K483" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="13" t="inlineStr">
         <is>
-          <t>Bob Iser</t>
+          <t>Søren Thuesen Pedersen</t>
         </is>
       </c>
       <c r="B484" s="14" t="inlineStr">
         <is>
-          <t>Global Head, Quality Policy &amp; Advocacy</t>
+          <t>Director, CMC Manufacturing Development</t>
         </is>
       </c>
       <c r="C484" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D484" s="17" t="inlineStr">
@@ -37468,9 +37517,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E484" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="E484" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F484" s="22" t="inlineStr">
@@ -37480,12 +37529,12 @@
       </c>
       <c r="G484" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="H484" s="13" t="inlineStr">
         <is>
-          <t>Quality Policy</t>
+          <t>Process Development / CMC</t>
         </is>
       </c>
       <c r="I484" s="13" t="inlineStr">
@@ -37495,24 +37544,24 @@
       </c>
       <c r="J484" s="13" t="inlineStr">
         <is>
-          <t>ISPE Facilities of the Future</t>
+          <t>ISPE Europe; ISPE Nordic</t>
         </is>
       </c>
       <c r="K484" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="13" t="inlineStr">
         <is>
-          <t>Marie Czogalla</t>
+          <t>Bob Iser</t>
         </is>
       </c>
       <c r="B485" s="14" t="inlineStr">
         <is>
-          <t>Partnering System Change Specialist Sterile Filling</t>
+          <t>Global Head, Quality Policy &amp; Advocacy</t>
         </is>
       </c>
       <c r="C485" s="13" t="inlineStr">
@@ -37520,14 +37569,14 @@
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D485" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
+      <c r="D485" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
         </is>
       </c>
       <c r="E485" s="13" t="inlineStr">
         <is>
-          <t>Senior IC</t>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F485" s="22" t="inlineStr">
@@ -37537,35 +37586,39 @@
       </c>
       <c r="G485" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H485" s="13" t="inlineStr">
         <is>
-          <t>Process / Sterile Filling</t>
+          <t>Quality Policy</t>
         </is>
       </c>
       <c r="I485" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J485" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J485" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future</t>
+        </is>
+      </c>
       <c r="K485" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="13" t="inlineStr">
         <is>
-          <t>Tobias Gerbracht</t>
+          <t>Marie Czogalla</t>
         </is>
       </c>
       <c r="B486" s="14" t="inlineStr">
         <is>
-          <t>Technology Scientific Expert</t>
+          <t>Partnering System Change Specialist Sterile Filling</t>
         </is>
       </c>
       <c r="C486" s="13" t="inlineStr">
@@ -37580,7 +37633,7 @@
       </c>
       <c r="E486" s="13" t="inlineStr">
         <is>
-          <t>Engineer / IC</t>
+          <t>Senior IC</t>
         </is>
       </c>
       <c r="F486" s="22" t="inlineStr">
@@ -37590,12 +37643,12 @@
       </c>
       <c r="G486" s="13" t="inlineStr">
         <is>
-          <t>Grenzach-Wyhlen, Germany (Europe)</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H486" s="13" t="inlineStr">
         <is>
-          <t>Process Development</t>
+          <t>Process / Sterile Filling</t>
         </is>
       </c>
       <c r="I486" s="13" t="inlineStr">
@@ -37606,77 +37659,77 @@
       <c r="J486" s="13" t="inlineStr"/>
       <c r="K486" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="13" t="inlineStr">
         <is>
-          <t>Azita Saleki-Gerhardt, PhD</t>
+          <t>Tobias Gerbracht</t>
         </is>
       </c>
       <c r="B487" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Operations Officer</t>
+          <t>Technology Scientific Expert</t>
         </is>
       </c>
       <c r="C487" s="13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
-        </is>
-      </c>
-      <c r="D487" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E487" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F487" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D487" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E487" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F487" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G487" s="13" t="inlineStr">
         <is>
-          <t>Global (mfg/eng/quality/supply) (US)</t>
+          <t>Grenzach-Wyhlen, Germany (Europe)</t>
         </is>
       </c>
       <c r="H487" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>Process Development</t>
         </is>
       </c>
       <c r="I487" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J487" s="13" t="inlineStr"/>
       <c r="K487" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="13" t="inlineStr">
         <is>
-          <t>Pam Cheng</t>
+          <t>Azita Saleki-Gerhardt, PhD</t>
         </is>
       </c>
       <c r="B488" s="14" t="inlineStr">
         <is>
-          <t>EVP, Global Operations &amp; IT, Chief Sustainability Officer</t>
+          <t>EVP, Chief Operations Officer</t>
         </is>
       </c>
       <c r="C488" s="13" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="D488" s="15" t="inlineStr">
@@ -37696,7 +37749,7 @@
       </c>
       <c r="G488" s="13" t="inlineStr">
         <is>
-          <t>Global (UK/US)</t>
+          <t>Global (mfg/eng/quality/supply) (US)</t>
         </is>
       </c>
       <c r="H488" s="13" t="inlineStr">
@@ -37719,27 +37772,27 @@
     <row r="489">
       <c r="A489" s="13" t="inlineStr">
         <is>
-          <t>Eamonn Warren</t>
+          <t>Pam Cheng</t>
         </is>
       </c>
       <c r="B489" s="14" t="inlineStr">
         <is>
-          <t>Group VP, API &amp; Dry Products Manufacturing</t>
+          <t>EVP, Global Operations &amp; IT, Chief Sustainability Officer</t>
         </is>
       </c>
       <c r="C489" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="D489" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E489" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="D489" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E489" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F489" s="16" t="inlineStr">
@@ -37749,12 +37802,12 @@
       </c>
       <c r="G489" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Global (UK/US)</t>
         </is>
       </c>
       <c r="H489" s="13" t="inlineStr">
         <is>
-          <t>API Manufacturing (Executive)</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="I489" s="13" t="inlineStr">
@@ -37762,11 +37815,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J489" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit; ISPE Annual</t>
-        </is>
-      </c>
+      <c r="J489" s="13" t="inlineStr"/>
       <c r="K489" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -37776,12 +37825,12 @@
     <row r="490">
       <c r="A490" s="13" t="inlineStr">
         <is>
-          <t>Edgardo Hernandez</t>
+          <t>Eamonn Warren</t>
         </is>
       </c>
       <c r="B490" s="14" t="inlineStr">
         <is>
-          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
+          <t>Group VP, API &amp; Dry Products Manufacturing</t>
         </is>
       </c>
       <c r="C490" s="13" t="inlineStr">
@@ -37789,14 +37838,14 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D490" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E490" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D490" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E490" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F490" s="16" t="inlineStr">
@@ -37806,12 +37855,12 @@
       </c>
       <c r="G490" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H490" s="13" t="inlineStr">
         <is>
-          <t>Executive (Manufacturing)</t>
+          <t>API Manufacturing (Executive)</t>
         </is>
       </c>
       <c r="I490" s="13" t="inlineStr">
@@ -37819,7 +37868,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J490" s="13" t="inlineStr"/>
+      <c r="J490" s="13" t="inlineStr">
+        <is>
+          <t>Pharma Manufacturing World Summit; ISPE Annual</t>
+        </is>
+      </c>
       <c r="K490" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -37829,12 +37882,12 @@
     <row r="491">
       <c r="A491" s="13" t="inlineStr">
         <is>
-          <t>Syed Abbas Yar-Khan</t>
+          <t>Edgardo Hernandez</t>
         </is>
       </c>
       <c r="B491" s="14" t="inlineStr">
         <is>
-          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
+          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
         </is>
       </c>
       <c r="C491" s="13" t="inlineStr">
@@ -37859,12 +37912,12 @@
       </c>
       <c r="G491" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
         </is>
       </c>
       <c r="H491" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Parenteral / Devices)</t>
+          <t>Executive (Manufacturing)</t>
         </is>
       </c>
       <c r="I491" s="13" t="inlineStr">
@@ -37872,11 +37925,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J491" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+      <c r="J491" s="13" t="inlineStr"/>
       <c r="K491" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -37886,17 +37935,17 @@
     <row r="492">
       <c r="A492" s="13" t="inlineStr">
         <is>
-          <t>Delphine Caron</t>
+          <t>Syed Abbas Yar-Khan</t>
         </is>
       </c>
       <c r="B492" s="14" t="inlineStr">
         <is>
-          <t>President, Janssen-Cilag (France)</t>
+          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
         </is>
       </c>
       <c r="C492" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D492" s="15" t="inlineStr">
@@ -37916,12 +37965,12 @@
       </c>
       <c r="G492" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H492" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country President)</t>
+          <t>Manufacturing (Parenteral / Devices)</t>
         </is>
       </c>
       <c r="I492" s="13" t="inlineStr">
@@ -37929,7 +37978,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J492" s="13" t="inlineStr"/>
+      <c r="J492" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
+        </is>
+      </c>
       <c r="K492" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -37939,12 +37992,12 @@
     <row r="493">
       <c r="A493" s="13" t="inlineStr">
         <is>
-          <t>Joaquin Duato</t>
+          <t>Delphine Caron</t>
         </is>
       </c>
       <c r="B493" s="14" t="inlineStr">
         <is>
-          <t>Chairman &amp; CEO</t>
+          <t>President, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C493" s="13" t="inlineStr">
@@ -37969,12 +38022,12 @@
       </c>
       <c r="G493" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H493" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Executive (Country President)</t>
         </is>
       </c>
       <c r="I493" s="13" t="inlineStr">
@@ -37992,12 +38045,12 @@
     <row r="494">
       <c r="A494" s="13" t="inlineStr">
         <is>
-          <t>John Reed, MD, PhD</t>
+          <t>Joaquin Duato</t>
         </is>
       </c>
       <c r="B494" s="14" t="inlineStr">
         <is>
-          <t>EVP, Innovative Medicine R&amp;D</t>
+          <t>Chairman &amp; CEO</t>
         </is>
       </c>
       <c r="C494" s="13" t="inlineStr">
@@ -38027,7 +38080,7 @@
       </c>
       <c r="H494" s="13" t="inlineStr">
         <is>
-          <t>Executive (R&amp;D)</t>
+          <t>Executive (CEO)</t>
         </is>
       </c>
       <c r="I494" s="13" t="inlineStr">
@@ -38035,11 +38088,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J494" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J494" s="13" t="inlineStr"/>
       <c r="K494" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38049,12 +38098,12 @@
     <row r="495">
       <c r="A495" s="13" t="inlineStr">
         <is>
-          <t>M. Martinez Climent</t>
+          <t>John Reed, MD, PhD</t>
         </is>
       </c>
       <c r="B495" s="14" t="inlineStr">
         <is>
-          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
+          <t>EVP, Innovative Medicine R&amp;D</t>
         </is>
       </c>
       <c r="C495" s="13" t="inlineStr">
@@ -38062,14 +38111,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D495" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E495" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="D495" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E495" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F495" s="16" t="inlineStr">
@@ -38079,12 +38128,12 @@
       </c>
       <c r="G495" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H495" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country DG)</t>
+          <t>Executive (R&amp;D)</t>
         </is>
       </c>
       <c r="I495" s="13" t="inlineStr">
@@ -38092,7 +38141,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J495" s="13" t="inlineStr"/>
+      <c r="J495" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K495" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38102,12 +38155,12 @@
     <row r="496">
       <c r="A496" s="13" t="inlineStr">
         <is>
-          <t>Namal Nawana</t>
+          <t>M. Martinez Climent</t>
         </is>
       </c>
       <c r="B496" s="14" t="inlineStr">
         <is>
-          <t>Worldwide President, DePuy Synthes</t>
+          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
         </is>
       </c>
       <c r="C496" s="13" t="inlineStr">
@@ -38115,14 +38168,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D496" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E496" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D496" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E496" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F496" s="16" t="inlineStr">
@@ -38132,12 +38185,12 @@
       </c>
       <c r="G496" s="13" t="inlineStr">
         <is>
-          <t>Orthopedics manufacturing network (Global)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H496" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (Country DG)</t>
         </is>
       </c>
       <c r="I496" s="13" t="inlineStr">
@@ -38155,12 +38208,12 @@
     <row r="497">
       <c r="A497" s="13" t="inlineStr">
         <is>
-          <t>Nauman Shah</t>
+          <t>Namal Nawana</t>
         </is>
       </c>
       <c r="B497" s="14" t="inlineStr">
         <is>
-          <t>Global Head of Business Development</t>
+          <t>Worldwide President, DePuy Synthes</t>
         </is>
       </c>
       <c r="C497" s="13" t="inlineStr">
@@ -38168,14 +38221,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D497" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E497" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
+      <c r="D497" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E497" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F497" s="16" t="inlineStr">
@@ -38185,12 +38238,12 @@
       </c>
       <c r="G497" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Orthopedics manufacturing network (Global)</t>
         </is>
       </c>
       <c r="H497" s="13" t="inlineStr">
         <is>
-          <t>Executive (Business Development)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I497" s="13" t="inlineStr">
@@ -38198,11 +38251,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J497" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J497" s="13" t="inlineStr"/>
       <c r="K497" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38212,12 +38261,12 @@
     <row r="498">
       <c r="A498" s="13" t="inlineStr">
         <is>
-          <t>Tim Schmid</t>
+          <t>Nauman Shah</t>
         </is>
       </c>
       <c r="B498" s="14" t="inlineStr">
         <is>
-          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
+          <t>Global Head of Business Development</t>
         </is>
       </c>
       <c r="C498" s="13" t="inlineStr">
@@ -38225,14 +38274,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D498" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E498" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D498" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E498" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F498" s="16" t="inlineStr">
@@ -38247,7 +38296,7 @@
       </c>
       <c r="H498" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (Business Development)</t>
         </is>
       </c>
       <c r="I498" s="13" t="inlineStr">
@@ -38255,7 +38304,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J498" s="13" t="inlineStr"/>
+      <c r="J498" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K498" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38265,12 +38318,12 @@
     <row r="499">
       <c r="A499" s="13" t="inlineStr">
         <is>
-          <t>Tom Heyman</t>
+          <t>Tim Schmid</t>
         </is>
       </c>
       <c r="B499" s="14" t="inlineStr">
         <is>
-          <t>CEO, Janssen Pharmaceutica (Belgium)</t>
+          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
         </is>
       </c>
       <c r="C499" s="13" t="inlineStr">
@@ -38278,14 +38331,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D499" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E499" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="D499" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E499" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F499" s="16" t="inlineStr">
@@ -38295,12 +38348,12 @@
       </c>
       <c r="G499" s="13" t="inlineStr">
         <is>
-          <t>Geel, Belgium (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H499" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country CEO)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I499" s="13" t="inlineStr">
@@ -38318,27 +38371,27 @@
     <row r="500">
       <c r="A500" s="13" t="inlineStr">
         <is>
-          <t>James Weirich</t>
+          <t>Tom Heyman</t>
         </is>
       </c>
       <c r="B500" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Cell &amp; Gene Therapy Head</t>
+          <t>CEO, Janssen Pharmaceutica (Belgium)</t>
         </is>
       </c>
       <c r="C500" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D500" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E500" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D500" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E500" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F500" s="16" t="inlineStr">
@@ -38348,12 +38401,12 @@
       </c>
       <c r="G500" s="13" t="inlineStr">
         <is>
-          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
+          <t>Geel, Belgium (Europe)</t>
         </is>
       </c>
       <c r="H500" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
+          <t>Executive (Country CEO)</t>
         </is>
       </c>
       <c r="I500" s="13" t="inlineStr">
@@ -38371,12 +38424,12 @@
     <row r="501">
       <c r="A501" s="13" t="inlineStr">
         <is>
-          <t>Steffen Lang, PhD</t>
+          <t>James Weirich</t>
         </is>
       </c>
       <c r="B501" s="14" t="inlineStr">
         <is>
-          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
+          <t>Vice President, Cell &amp; Gene Therapy Head</t>
         </is>
       </c>
       <c r="C501" s="13" t="inlineStr">
@@ -38401,12 +38454,12 @@
       </c>
       <c r="G501" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Durham, NC / Kundl, AT)</t>
+          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
         </is>
       </c>
       <c r="H501" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
         </is>
       </c>
       <c r="I501" s="13" t="inlineStr">
@@ -38424,17 +38477,17 @@
     <row r="502">
       <c r="A502" s="13" t="inlineStr">
         <is>
-          <t>Ann Lee</t>
+          <t>Steffen Lang, PhD</t>
         </is>
       </c>
       <c r="B502" s="14" t="inlineStr">
         <is>
-          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
+          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
         </is>
       </c>
       <c r="C502" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D502" s="15" t="inlineStr">
@@ -38454,12 +38507,12 @@
       </c>
       <c r="G502" s="13" t="inlineStr">
         <is>
-          <t>South San Francisco, CA (US)</t>
+          <t>Global (incl. Durham, NC / Kundl, AT)</t>
         </is>
       </c>
       <c r="H502" s="13" t="inlineStr">
         <is>
-          <t>Technical Development / Manufacturing Science</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="I502" s="13" t="inlineStr">
@@ -38477,12 +38530,12 @@
     <row r="503">
       <c r="A503" s="13" t="inlineStr">
         <is>
-          <t>Ashley Magargee</t>
+          <t>Ann Lee</t>
         </is>
       </c>
       <c r="B503" s="14" t="inlineStr">
         <is>
-          <t>CEO, Genentech</t>
+          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
         </is>
       </c>
       <c r="C503" s="13" t="inlineStr">
@@ -38490,14 +38543,14 @@
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D503" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E503" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="D503" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E503" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F503" s="16" t="inlineStr">
@@ -38507,12 +38560,12 @@
       </c>
       <c r="G503" s="13" t="inlineStr">
         <is>
-          <t>Holly Springs, NC (US)</t>
+          <t>South San Francisco, CA (US)</t>
         </is>
       </c>
       <c r="H503" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Technical Development / Manufacturing Science</t>
         </is>
       </c>
       <c r="I503" s="13" t="inlineStr">
@@ -38530,42 +38583,42 @@
     <row r="504">
       <c r="A504" s="13" t="inlineStr">
         <is>
-          <t>Dana Kendall</t>
+          <t>Ashley Magargee</t>
         </is>
       </c>
       <c r="B504" s="14" t="inlineStr">
         <is>
-          <t>General Manager, AbbVie Ireland</t>
+          <t>CEO, Genentech</t>
         </is>
       </c>
       <c r="C504" s="13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
-        </is>
-      </c>
-      <c r="D504" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E504" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F504" s="19" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D504" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E504" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F504" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G504" s="13" t="inlineStr">
         <is>
-          <t>Dublin (Citywest), Ireland (Europe)</t>
+          <t>Holly Springs, NC (US)</t>
         </is>
       </c>
       <c r="H504" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country GM)</t>
+          <t>Executive (CEO)</t>
         </is>
       </c>
       <c r="I504" s="13" t="inlineStr">
@@ -38576,24 +38629,24 @@
       <c r="J504" s="13" t="inlineStr"/>
       <c r="K504" s="14" t="inlineStr">
         <is>
-          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="13" t="inlineStr">
         <is>
-          <t>Guy Oliver</t>
+          <t>Dana Kendall</t>
         </is>
       </c>
       <c r="B505" s="14" t="inlineStr">
         <is>
-          <t>General Manager, UK &amp; Ireland</t>
+          <t>General Manager, AbbVie Ireland</t>
         </is>
       </c>
       <c r="C505" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="D505" s="17" t="inlineStr">
@@ -38613,7 +38666,7 @@
       </c>
       <c r="G505" s="13" t="inlineStr">
         <is>
-          <t>UK &amp; Ireland (Europe)</t>
+          <t>Dublin (Citywest), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H505" s="13" t="inlineStr">
@@ -38636,27 +38689,27 @@
     <row r="506">
       <c r="A506" s="13" t="inlineStr">
         <is>
-          <t>Maria T.</t>
+          <t>Guy Oliver</t>
         </is>
       </c>
       <c r="B506" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Medical Science Liaison - Immunology CART</t>
+          <t>General Manager, UK &amp; Ireland</t>
         </is>
       </c>
       <c r="C506" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D506" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E506" s="16" t="inlineStr">
-        <is>
-          <t>Assoc Director</t>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D506" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E506" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F506" s="19" t="inlineStr">
@@ -38666,17 +38719,17 @@
       </c>
       <c r="G506" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>UK &amp; Ireland (Europe)</t>
         </is>
       </c>
       <c r="H506" s="13" t="inlineStr">
         <is>
-          <t>Medical Affairs</t>
+          <t>Executive (Country GM)</t>
         </is>
       </c>
       <c r="I506" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J506" s="13" t="inlineStr"/>
@@ -38689,12 +38742,12 @@
     <row r="507">
       <c r="A507" s="13" t="inlineStr">
         <is>
-          <t>Thierry Diagana</t>
+          <t>Maria T.</t>
         </is>
       </c>
       <c r="B507" s="14" t="inlineStr">
         <is>
-          <t>California Sites Head, Novartis Biomedical Research</t>
+          <t>Associate Director, Medical Science Liaison - Immunology CART</t>
         </is>
       </c>
       <c r="C507" s="13" t="inlineStr">
@@ -38707,9 +38760,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E507" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="E507" s="16" t="inlineStr">
+        <is>
+          <t>Assoc Director</t>
         </is>
       </c>
       <c r="F507" s="19" t="inlineStr">
@@ -38719,17 +38772,17 @@
       </c>
       <c r="G507" s="13" t="inlineStr">
         <is>
-          <t>San Diego / Emeryville, CA (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H507" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D / Research Site Leadership</t>
+          <t>Medical Affairs</t>
         </is>
       </c>
       <c r="I507" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J507" s="13" t="inlineStr"/>
@@ -38742,62 +38795,115 @@
     <row r="508">
       <c r="A508" s="13" t="inlineStr">
         <is>
+          <t>Thierry Diagana</t>
+        </is>
+      </c>
+      <c r="B508" s="14" t="inlineStr">
+        <is>
+          <t>California Sites Head, Novartis Biomedical Research</t>
+        </is>
+      </c>
+      <c r="C508" s="13" t="inlineStr">
+        <is>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D508" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E508" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F508" s="19" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="G508" s="13" t="inlineStr">
+        <is>
+          <t>San Diego / Emeryville, CA (US)</t>
+        </is>
+      </c>
+      <c r="H508" s="13" t="inlineStr">
+        <is>
+          <t>R&amp;D / Research Site Leadership</t>
+        </is>
+      </c>
+      <c r="I508" s="13" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J508" s="13" t="inlineStr"/>
+      <c r="K508" s="14" t="inlineStr">
+        <is>
+          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="13" t="inlineStr">
+        <is>
           <t>Franck Bure</t>
         </is>
       </c>
-      <c r="B508" s="14" t="inlineStr">
+      <c r="B509" s="14" t="inlineStr">
         <is>
           <t>(title not stated in source)</t>
         </is>
       </c>
-      <c r="C508" s="13" t="inlineStr">
+      <c r="C509" s="13" t="inlineStr">
         <is>
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D508" s="17" t="inlineStr">
+      <c r="D509" s="17" t="inlineStr">
         <is>
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E508" s="13" t="inlineStr">
+      <c r="E509" s="13" t="inlineStr">
         <is>
           <t>Engineer / IC</t>
         </is>
       </c>
-      <c r="F508" s="19" t="inlineStr">
+      <c r="F509" s="19" t="inlineStr">
         <is>
           <t>De-prioritise</t>
         </is>
       </c>
-      <c r="G508" s="13" t="inlineStr">
+      <c r="G509" s="13" t="inlineStr">
         <is>
           <t>Not specified in source (Global)</t>
         </is>
       </c>
-      <c r="H508" s="13" t="inlineStr">
+      <c r="H509" s="13" t="inlineStr">
         <is>
           <t>Unknown (conference speaker)</t>
         </is>
       </c>
-      <c r="I508" s="13" t="inlineStr">
+      <c r="I509" s="13" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
-      <c r="J508" s="13" t="inlineStr">
+      <c r="J509" s="13" t="inlineStr">
         <is>
           <t>ISPE Aseptic Conference 2026</t>
         </is>
       </c>
-      <c r="K508" s="14" t="inlineStr">
+      <c r="K509" s="14" t="inlineStr">
         <is>
           <t>Conference-confirmed contact but role/title unknown — verify function before ranking.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K508"/>
+  <autoFilter ref="A1:K509"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38808,7 +38914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -39361,12 +39467,12 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Helen Grealis</t>
+          <t>John Casey</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Manager, Global Engineering</t>
+          <t>Senior Director, Biologics Contract Manufacturing</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -39379,47 +39485,47 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>Manager / Lead</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>County Mayo, Ireland (Europe)</t>
+          <t>Worcester, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>External / Contract Manufacturing</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Richard Harrington</t>
+          <t>Helen Grealis</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Capital Projects Engineering Manager</t>
+          <t>C&amp;Q Manager, Global Engineering</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -39427,9 +39533,9 @@
           <t>AbbVie</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -39444,12 +39550,12 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Dublin 17, County Dublin, Ireland (Europe)</t>
+          <t>County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -39460,19 +39566,19 @@
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Joe Brodt</t>
+          <t>Richard Harrington</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Business Excellence</t>
+          <t>Capital Projects Engineering Manager</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -39487,7 +39593,7 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>Assoc Director</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -39497,12 +39603,12 @@
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Greater Chicago Area</t>
+          <t>Dublin 17, County Dublin, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
@@ -39513,19 +39619,19 @@
       <c r="J13" s="13" t="inlineStr"/>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Luis M González</t>
+          <t>Joe Brodt</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Supply Chain QA Project Manager</t>
+          <t>Associate Director, Business Excellence</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -39540,22 +39646,22 @@
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+          <t>Assoc Director</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Highland Park, Illinois, United States (US)</t>
+          <t>Greater Chicago Area</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain / QA</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -39566,19 +39672,19 @@
       <c r="J14" s="13" t="inlineStr"/>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Caroline Rocks</t>
+          <t>Luis M González</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Senior Program Manager (Process Engineer)</t>
+          <t>Supply Chain QA Project Manager</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -39596,42 +39702,42 @@
           <t>Manager / Lead</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Highland Park, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Engineering / Program Management</t>
+          <t>Supply Chain / QA</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>James Curley</t>
+          <t>Caroline Rocks</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Ocular Implants Engineering Manager</t>
+          <t>Senior Program Manager (Process Engineer)</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -39661,12 +39767,12 @@
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / Program Management</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr"/>
@@ -39679,12 +39785,12 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Rory Clarke</t>
+          <t>James Curley</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Ocular Implants Engineering Manager</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -39732,12 +39838,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Elvir J.</t>
+          <t>Rory Clarke</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Category Manager, Capital Projects (Pharmaceutical)</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -39762,12 +39868,12 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Niles, Illinois, United States (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>Procurement (Capital Projects)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
@@ -39778,19 +39884,19 @@
       <c r="J18" s="13" t="inlineStr"/>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Vladimir Mulina</t>
+          <t>Elvir J.</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Project Engineering Manager</t>
+          <t>Category Manager, Capital Projects (Pharmaceutical)</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -39815,12 +39921,12 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>San Diego Metropolitan Area (US)</t>
+          <t>Niles, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Procurement (Capital Projects)</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
@@ -39831,19 +39937,19 @@
       <c r="J19" s="13" t="inlineStr"/>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Paul Dennison</t>
+          <t>Vladimir Mulina</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Biologics Engineering Manager</t>
+          <t>Project Engineering Manager</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -39868,12 +39974,12 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Sligo, County Sligo, Ireland (Europe)</t>
+          <t>San Diego Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
@@ -39891,12 +39997,12 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Christopher Wright</t>
+          <t>Paul Dennison</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Biologics Engineering Manager</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -39921,12 +40027,12 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Sligo, County Sligo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -39937,19 +40043,19 @@
       <c r="J21" s="13" t="inlineStr"/>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Kevin Ohora</t>
+          <t>Christopher Wright</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -39974,12 +40080,12 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>Westport, County Mayo, Ireland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
@@ -39990,19 +40096,19 @@
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Jean Mayotte</t>
+          <t>Kevin Ohora</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Capital Validation Engineering Manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -40027,12 +40133,12 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>Worcester, Massachusetts, United States</t>
+          <t>Westport, County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
@@ -40050,12 +40156,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Kelvin Lau</t>
+          <t>Jean Mayotte</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Principal Engineer (Manager)</t>
+          <t>Capital Validation Engineering Manager</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -40070,7 +40176,7 @@
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -40085,7 +40191,7 @@
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
@@ -40096,19 +40202,19 @@
       <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Abigail Vasilevsky (Cabral)</t>
+          <t>Kelvin Lau</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Principal Engineer (Manager)</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -40121,9 +40227,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Senior IC</t>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -40133,12 +40239,12 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts, United States</t>
+          <t>Worcester, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -40149,14 +40255,14 @@
       <c r="J25" s="13" t="inlineStr"/>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Gerard McWalter</t>
+          <t>Abigail Vasilevsky (Cabral)</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -40186,7 +40292,7 @@
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>County Mayo, Ireland (Europe)</t>
+          <t>Boston, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -40209,12 +40315,12 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Khanh D.</t>
+          <t>Gerard McWalter</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Sr CQV Engineer - Capital Validation Engineering</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -40239,12 +40345,12 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston (US)</t>
+          <t>County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
@@ -40262,12 +40368,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Victor Lee</t>
+          <t>Khanh D.</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer, Global Packaging</t>
+          <t>Sr CQV Engineer - Capital Validation Engineering</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -40275,9 +40381,9 @@
           <t>AbbVie</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -40292,12 +40398,12 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Greater Chicago Area</t>
+          <t>Greater Boston (US)</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I28" s="13" t="inlineStr">
@@ -40315,12 +40421,12 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>Yi Ching Koe</t>
+          <t>Victor Lee</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer, API Pilot Plant</t>
+          <t>Senior Project Engineer, Global Packaging</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -40328,9 +40434,9 @@
           <t>AbbVie</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -40345,7 +40451,7 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Greater Chicago Area (US)</t>
+          <t>Greater Chicago Area</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -40368,12 +40474,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Mike Redmond</t>
+          <t>Yi Ching Koe</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Senior Project Engineer, API Pilot Plant</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -40398,7 +40504,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Greater Chicago Area (US)</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -40421,7 +40527,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Sean O Malley</t>
+          <t>Mike Redmond</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -40474,7 +40580,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>Titi Adeyemi</t>
+          <t>Sean O Malley</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -40504,12 +40610,12 @@
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Lincolnshire, Illinois, United States (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
@@ -40520,19 +40626,19 @@
       <c r="J32" s="13" t="inlineStr"/>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Mihir Patoliya</t>
+          <t>Titi Adeyemi</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Senior CQV / Quality Consultant</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -40557,12 +40663,12 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Lincolnshire, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -40573,19 +40679,19 @@
       <c r="J33" s="13" t="inlineStr"/>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>Reza H.</t>
+          <t>Mihir Patoliya</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Senior CQV / Quality Consultant</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -40615,7 +40721,7 @@
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I34" s="13" t="inlineStr">
@@ -40633,12 +40739,12 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>Brian Forte</t>
+          <t>Reza H.</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Senior Packaging Project Engineer</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -40663,7 +40769,7 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>Waco, Texas, United States (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -40686,12 +40792,12 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Charlie Acquista</t>
+          <t>Brian Forte</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Senior Packaging Project Engineer</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -40716,7 +40822,7 @@
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Worcester, Massachusetts, United States</t>
+          <t>Waco, Texas, United States (US)</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -40739,12 +40845,12 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>Dylan Golden</t>
+          <t>Charlie Acquista</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -40759,7 +40865,7 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Engineer / IC</t>
+          <t>Senior IC</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -40769,7 +40875,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Ballina, County Mayo, Ireland (Europe)</t>
+          <t>Worcester, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -40792,12 +40898,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Daniel Tiffany-Appleton</t>
+          <t>Dylan Golden</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Capital Project Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -40822,12 +40928,12 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts, United States</t>
+          <t>Ballina, County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
@@ -40838,19 +40944,19 @@
       <c r="J38" s="13" t="inlineStr"/>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Mark Gaughan</t>
+          <t>Daniel Tiffany-Appleton</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Capital Project Engineer</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -40875,12 +40981,12 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Castlebar, County Mayo, Ireland (Europe)</t>
+          <t>Boston, Massachusetts, United States</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
@@ -40891,14 +40997,14 @@
       <c r="J39" s="13" t="inlineStr"/>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>Riya Gyanmote</t>
+          <t>Mark Gaughan</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -40928,7 +41034,7 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, United States (US)</t>
+          <t>Castlebar, County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -40951,12 +41057,12 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Iris Kanakis</t>
+          <t>Riya Gyanmote</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer (Facilities)</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -40981,7 +41087,7 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>County Galway, Ireland (Europe)</t>
+          <t>Chicago, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -41004,12 +41110,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>John M.</t>
+          <t>Iris Kanakis</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Project Engineer (Facilities)</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -41034,7 +41140,7 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>County Mayo, Ireland (Europe)</t>
+          <t>County Galway, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -41057,7 +41163,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Jade Bradley</t>
+          <t>John M.</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -41087,7 +41193,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>County Sligo, Ireland (Europe)</t>
+          <t>County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -41110,7 +41216,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>Kevin Ee Zen Ooi</t>
+          <t>Jade Bradley</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -41140,7 +41246,7 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Evanston, Illinois, United States (US)</t>
+          <t>County Sligo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -41163,12 +41269,12 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Bertrand Mouton</t>
+          <t>Kevin Ee Zen Ooi</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Responsable de maintenance générale et infrastructures site</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -41193,12 +41299,12 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Greater Bordeaux Metropolitan Area (Europe)</t>
+          <t>Evanston, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Infrastructure</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I45" s="13" t="inlineStr">
@@ -41209,19 +41315,19 @@
       <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Jack Hua</t>
+          <t>Bertrand Mouton</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Engineering Project Engineer</t>
+          <t>Responsable de maintenance générale et infrastructures site</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -41246,12 +41352,12 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Greater Dublin (Europe)</t>
+          <t>Greater Bordeaux Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Maintenance / Infrastructure</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
@@ -41262,19 +41368,19 @@
       <c r="J46" s="13" t="inlineStr"/>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Adrian Padden</t>
+          <t>Jack Hua</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Automation Project Engineering</t>
+          <t>Engineering Project Engineer</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -41299,12 +41405,12 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Greater Dublin (Europe)</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Automation)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -41322,12 +41428,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Barry Commons</t>
+          <t>Adrian Padden</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Automation Project Engineering</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -41357,7 +41463,7 @@
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q (Automation)</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -41375,7 +41481,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Brendan Quinn</t>
+          <t>Barry Commons</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -41410,7 +41516,7 @@
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project / Controls)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
@@ -41428,7 +41534,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Brendan Quinn</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -41463,7 +41569,7 @@
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering (Project / Controls)</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
@@ -41481,7 +41587,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Stephen Anderson</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -41534,12 +41640,12 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Simon Kuehbauch</t>
+          <t>Stephen Anderson</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer Pilot Plants</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -41564,7 +41670,7 @@
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Ketsch, Baden-Württemberg, Germany (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -41587,12 +41693,12 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Declan Heneghan</t>
+          <t>Simon Kuehbauch</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Project Engineer Pilot Plants</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -41617,7 +41723,7 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Partry, County Mayo, Ireland (Europe)</t>
+          <t>Ketsch, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -41640,12 +41746,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Luz Medina</t>
+          <t>Declan Heneghan</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Validation Consultant</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -41670,12 +41776,12 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Partry, County Mayo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -41693,12 +41799,12 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>Leon Low</t>
+          <t>Luz Medina</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Process and Project Engineer</t>
+          <t>C&amp;Q Validation Consultant</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -41723,12 +41829,12 @@
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Singapore (Asia)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr">
@@ -41746,12 +41852,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Brendan Duggan</t>
+          <t>Leon Low</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Process and Project Engineer</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -41776,7 +41882,7 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Sligo, County Sligo, Ireland (Europe)</t>
+          <t>Singapore (Asia)</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -41799,7 +41905,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>David Lynch</t>
+          <t>Brendan Duggan</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -41852,12 +41958,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Soummya Kar</t>
+          <t>David Lynch</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Projects Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -41882,7 +41988,7 @@
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom (Europe)</t>
+          <t>Sligo, County Sligo, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -41902,8 +42008,61 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>Soummya Kar</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Projects Engineer</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>United Kingdom (Europe)</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Engineering (Project)</t>
+        </is>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J59" s="13" t="inlineStr"/>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K58"/>
+  <autoFilter ref="A1:K59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/networkmap/data/contacts_all.xlsx
+++ b/networkmap/data/contacts_all.xlsx
@@ -20,12 +20,12 @@
     <sheet name="Roche-Genentech" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision-Makers'!$A$1:$K$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Contacts'!$A$1:$K$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision-Makers'!$A$1:$K$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Contacts'!$A$1:$K$510</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AbbVie'!$A$1:$K$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AstraZeneca'!$A$1:$K$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BMS'!$A$1:$K$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Eli Lilly'!$A$1:$K$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Eli Lilly'!$A$1:$K$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Johnson &amp; Johnson'!$A$1:$K$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Novartis'!$A$1:$K$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Novo Nordisk'!$A$1:$K$61</definedName>
@@ -597,7 +597,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>508 named contacts across 8 accounts. Tiers = influence over valve spec/procurement/lifecycle. Generated 2026-07-17.</t>
+          <t>509 named contacts across 8 accounts. Tiers = influence over valve spec/procurement/lifecycle. Generated 2026-07-17.</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8415,12 +8415,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Molly Wagner</t>
+          <t>Coralie Richard</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Procurement</t>
+          <t>Director (Parenteral)</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>Strategic Sourcing / Procurement</t>
+          <t>Parenteral / Packaging</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
@@ -8458,22 +8458,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J46" s="13" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>PDA Parenteral Packaging; PDA Week</t>
+        </is>
+      </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Bill Cook</t>
+          <t>Molly Wagner</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Lean Manufacturing / Operational Excellence - Director</t>
+          <t>Director, Capital Procurement</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -8498,35 +8502,35 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Clinton, Indiana, United States (US)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>Operational Excellence / Lean</t>
+          <t>Strategic Sourcing / Procurement</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr"/>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Robert O'Keeffe</t>
+          <t>Bill Cook</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Engineering Tech Centre</t>
+          <t>Lean Manufacturing / Operational Excellence - Director</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -8544,46 +8548,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Limerick NGB) (Europe)</t>
+          <t>Clinton, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Operational Excellence / Lean</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr"/>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Massimiliano Ammannito</t>
+          <t>Robert O'Keeffe</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Sr Director - Facilities, Utilities &amp; Capital Projects</t>
+          <t>Senior Director, Engineering Tech Centre</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Italy (Europe)</t>
+          <t>Ireland (Limerick NGB) (Europe)</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Utilities / Capital Projects</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
@@ -8623,24 +8623,24 @@
       </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>ISPE Aseptic Conference; ISPE Europe</t>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Kenneth Swank</t>
+          <t>Massimiliano Ammannito</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Sr. Director - Major Capital Projects</t>
+          <t>Sr Director - Facilities, Utilities &amp; Capital Projects</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -8665,88 +8665,92 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Greenwood, Indiana, United States (US)</t>
+          <t>Italy (Europe)</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Utilities / Capital Projects</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Aseptic Conference; ISPE Europe</t>
+        </is>
+      </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Joaquin Duato</t>
+          <t>Kenneth Swank</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Chairman &amp; CEO</t>
+          <t>Sr. Director - Major Capital Projects</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Greenwood, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Kathryn E. Wengel</t>
+          <t>Joaquin Duato</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Technical Operations &amp; Risk Officer</t>
+          <t>Chairman &amp; CEO</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -8764,19 +8768,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Enterprise-wide (Global) (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Quality/Supply Chain (Executive)</t>
+          <t>Executive (CEO)</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -8787,19 +8791,19 @@
       <c r="J52" s="13" t="inlineStr"/>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>John Reed, MD, PhD</t>
+          <t>Kathryn E. Wengel</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>EVP, Innovative Medicine R&amp;D</t>
+          <t>EVP, Chief Technical Operations &amp; Risk Officer</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -8817,19 +8821,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Enterprise-wide (Global) (US)</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>Executive (R&amp;D)</t>
+          <t>Engineering/Quality/Supply Chain (Executive)</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
@@ -8837,26 +8841,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J53" s="13" t="inlineStr"/>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Tim Schmid</t>
+          <t>John Reed, MD, PhD</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
+          <t>EVP, Innovative Medicine R&amp;D</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (R&amp;D)</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -8894,7 +8894,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -8904,12 +8908,12 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>Dana Daneshvari</t>
+          <t>Tim Schmid</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>General Manager &amp; VP Manufacturing, Large Molecule Site</t>
+          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -8927,19 +8931,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Manufacturing (Site GM)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr">
@@ -8950,19 +8954,19 @@
       <c r="J55" s="13" t="inlineStr"/>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Delphine Caron</t>
+          <t>Dana Daneshvari</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>President, Janssen-Cilag (France)</t>
+          <t>General Manager &amp; VP Manufacturing, Large Molecule Site</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -8980,19 +8984,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country President)</t>
+          <t>Engineering/Manufacturing (Site GM)</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
@@ -9003,19 +9007,19 @@
       <c r="J56" s="13" t="inlineStr"/>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>Robin Kumoluyi</t>
+          <t>Delphine Caron</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
+          <t>President, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -9033,19 +9037,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>Quality (Executive)</t>
+          <t>Executive (Country President)</t>
         </is>
       </c>
       <c r="I57" s="13" t="inlineStr">
@@ -9053,26 +9057,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J57" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit</t>
-        </is>
-      </c>
+      <c r="J57" s="13" t="inlineStr"/>
       <c r="K57" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Leila Schwery-Bou-Diab</t>
+          <t>Robin Kumoluyi</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>VP Manufacturing &amp; Technical Operations</t>
+          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Technical Operations</t>
+          <t>Quality (Executive)</t>
         </is>
       </c>
       <c r="I58" s="13" t="inlineStr">
@@ -9110,22 +9110,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J58" s="13" t="inlineStr"/>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>Pharma Manufacturing World Summit</t>
+        </is>
+      </c>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>Namal Nawana</t>
+          <t>Leila Schwery-Bou-Diab</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Worldwide President, DePuy Synthes</t>
+          <t>VP Manufacturing &amp; Technical Operations</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -9143,19 +9147,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>Orthopedics manufacturing network (Global)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Manufacturing/Technical Operations</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr">
@@ -9166,19 +9170,19 @@
       <c r="J59" s="13" t="inlineStr"/>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Stephanie Striegler</t>
+          <t>Namal Nawana</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>General Manager, Janssen Schaffhausen</t>
+          <t>Worldwide President, DePuy Synthes</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -9186,29 +9190,29 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F60" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>Schaffhausen, Switzerland (Europe)</t>
+          <t>Orthopedics manufacturing network (Global)</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>Executive (Site GM)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
@@ -9219,19 +9223,19 @@
       <c r="J60" s="13" t="inlineStr"/>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>Nauman Shah</t>
+          <t>Stephanie Striegler</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>Global Head of Business Development</t>
+          <t>General Manager, Janssen Schaffhausen</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -9249,19 +9253,19 @@
           <t>Site / Function Head</t>
         </is>
       </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Schaffhausen, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>Executive (Business Development)</t>
+          <t>Executive (Site GM)</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
@@ -9269,26 +9273,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J61" s="13" t="inlineStr"/>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>Mary Houchin</t>
+          <t>Nauman Shah</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>MSAT Site Director</t>
+          <t>Global Head of Business Development</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -9306,42 +9306,46 @@
           <t>Site / Function Head</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Site Director)</t>
+          <t>Executive (Business Development)</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J62" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K62" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Armelle Santelli</t>
+          <t>Mary Houchin</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
+          <t>MSAT Site Director</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -9354,47 +9358,47 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E63" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="F63" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Raleigh-Durham-Chapel Hill Area (US)</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>Quality/Regulatory</t>
+          <t>MSAT (Site Director)</t>
         </is>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J63" s="13" t="inlineStr"/>
       <c r="K63" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>Goeran Crucius</t>
+          <t>Armelle Santelli</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Director MSAT Cross Platform Engineering</t>
+          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -9412,42 +9416,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>Schaffhausen, Switzerland (Europe)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Engineering</t>
+          <t>Quality/Regulatory</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J64" s="13" t="inlineStr"/>
       <c r="K64" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>Scott Foell</t>
+          <t>Goeran Crucius</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Projects</t>
+          <t>Director MSAT Cross Platform Engineering</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -9472,12 +9476,12 @@
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>Vacaville, California, United States (US)</t>
+          <t>Schaffhausen, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>MSAT / Engineering</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr">
@@ -9488,19 +9492,19 @@
       <c r="J65" s="13" t="inlineStr"/>
       <c r="K65" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Thomas Kelly</t>
+          <t>Scott Foell</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Director, Cell Engineering &amp; Analytical Sciences</t>
+          <t>Director, Capital Projects</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -9525,39 +9529,35 @@
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (US)</t>
+          <t>Vacaville, California, United States (US)</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D/Manufacturing Science</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J66" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International 2026 (Sep 22-25, Boston, MA)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J66" s="13" t="inlineStr"/>
       <c r="K66" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Alan Bateman</t>
+          <t>Thomas Kelly</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Director, Systems Architecture, Digital &amp; Execution</t>
+          <t>Director, Cell Engineering &amp; Analytical Sciences</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
@@ -9575,19 +9575,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F67" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Not specified in source (US)</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>Advanced Mfg / Digital</t>
+          <t>R&amp;D/Manufacturing Science</t>
         </is>
       </c>
       <c r="I67" s="13" t="inlineStr">
@@ -9597,24 +9597,24 @@
       </c>
       <c r="J67" s="13" t="inlineStr">
         <is>
-          <t>ISPE</t>
+          <t>BioProcess International 2026 (Sep 22-25, Boston, MA)</t>
         </is>
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>Dan Usas</t>
+          <t>Alan Bateman</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Director, Technical Operations</t>
+          <t>Director, Systems Architecture, Digital &amp; Execution</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -9632,19 +9632,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F68" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Service</t>
+          <t>Advanced Mfg / Digital</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -9652,22 +9652,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J68" s="13" t="inlineStr"/>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>ISPE</t>
+        </is>
+      </c>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>M. Martinez Climent</t>
+          <t>Dan Usas</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
+          <t>Director, Technical Operations</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -9685,19 +9689,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country DG)</t>
+          <t>MSAT / Technical Service</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
@@ -9708,19 +9712,19 @@
       <c r="J69" s="13" t="inlineStr"/>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Peter Millili</t>
+          <t>M. Martinez Climent</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Manufacturing Science &amp; Technology</t>
+          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -9738,19 +9742,19 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F70" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Service</t>
+          <t>Executive (Country DG)</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
@@ -9758,26 +9762,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J70" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual</t>
-        </is>
-      </c>
+      <c r="J70" s="13" t="inlineStr"/>
       <c r="K70" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Peter Millili, PhD</t>
+          <t>Peter Millili</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Manufacturing Science and Technology (MSAT), Advanced Therapies</t>
+          <t>Senior Director, Manufacturing Science &amp; Technology</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Philadelphia / Spring House, PA</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>MSAT / Technical Service</t>
         </is>
       </c>
       <c r="I71" s="13" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="J71" s="13" t="inlineStr">
         <is>
-          <t>ISPE Annual Meeting &amp; Expo 2026 (Oct 18-21, National Harbor, MD)</t>
+          <t>ISPE Annual</t>
         </is>
       </c>
       <c r="K71" s="14" t="inlineStr">
@@ -9829,12 +9829,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>Donald Powers</t>
+          <t>Peter Millili, PhD</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Sr Director Advanced Therapies MSAT</t>
+          <t>Senior Director, Manufacturing Science and Technology (MSAT), Advanced Therapies</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>Greater Philadelphia (US)</t>
+          <t>Philadelphia / Spring House, PA</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -9869,10 +9869,14 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J72" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J72" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual Meeting &amp; Expo 2026 (Oct 18-21, National Harbor, MD)</t>
+        </is>
+      </c>
       <c r="K72" s="14" t="inlineStr">
         <is>
           <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
@@ -9882,65 +9886,65 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Steffen Lang, PhD</t>
+          <t>Donald Powers</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
+          <t>Sr Director Advanced Therapies MSAT</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E73" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E73" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Durham, NC / Kundl, AT)</t>
+          <t>Greater Philadelphia (US)</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J73" s="13" t="inlineStr"/>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>James Weirich</t>
+          <t>Steffen Lang, PhD</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Cell &amp; Gene Therapy Head</t>
+          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -9965,12 +9969,12 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
+          <t>Global (incl. Durham, NC / Kundl, AT)</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
@@ -9988,12 +9992,12 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Nicholas J. Casale</t>
+          <t>James Weirich</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>Head of Strategy &amp; Operational Excellence, Cell &amp; Gene Tech Dev &amp; Mfg</t>
+          <t>Vice President, Cell &amp; Gene Therapy Head</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -10001,29 +10005,29 @@
           <t>Novartis</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F75" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>Morris Plains, New Jersey, United States (US)</t>
+          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering / Op-Ex</t>
+          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
@@ -10031,26 +10035,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J75" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Annual; ISPE Aseptic</t>
-        </is>
-      </c>
+      <c r="J75" s="13" t="inlineStr"/>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>Soma shekara</t>
+          <t>Nicholas J. Casale</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>Director - Global Project Engineering</t>
+          <t>Head of Strategy &amp; Operational Excellence, Cell &amp; Gene Tech Dev &amp; Mfg</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -10063,9 +10063,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E76" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
@@ -10075,20 +10075,24 @@
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Morris Plains, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Global Project Engineering)</t>
+          <t>Manufacturing Engineering / Op-Ex</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J76" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J76" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Annual; ISPE Aseptic</t>
+        </is>
+      </c>
       <c r="K76" s="14" t="inlineStr">
         <is>
           <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
@@ -10098,27 +10102,27 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Lone Charlotte Larsen</t>
+          <t>Soma shekara</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Corporate Vice President, Novo Nordisk Production Chartres</t>
+          <t>Director - Global Project Engineering</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E77" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E77" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
@@ -10128,35 +10132,35 @@
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>Chartres, France (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership (Capital Project)</t>
+          <t>Engineering (Global Project Engineering)</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J77" s="13" t="inlineStr"/>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>Henrik Wulff</t>
+          <t>Lone Charlotte Larsen</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>EVP, Product Supply, Quality &amp; IT</t>
+          <t>Corporate Vice President, Novo Nordisk Production Chartres</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -10174,19 +10178,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F78" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC / Kalundborg, DK (Global)</t>
+          <t>Chartres, France (Europe)</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Quality)</t>
+          <t>Site Leadership (Capital Project)</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -10197,19 +10201,19 @@
       <c r="J78" s="13" t="inlineStr"/>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>Jay Kuykendall</t>
+          <t>Henrik Wulff</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Project Vice President, Clayton (NC) Expansion</t>
+          <t>EVP, Product Supply, Quality &amp; IT</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -10227,19 +10231,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F79" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC (US)</t>
+          <t>Clayton, NC / Kalundborg, DK (Global)</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>Engineering/Capital Project</t>
+          <t>Executive (Supply/Quality)</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr">
@@ -10250,19 +10254,19 @@
       <c r="J79" s="13" t="inlineStr"/>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>Flemming Dahl</t>
+          <t>Jay Kuykendall</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>SVP, Head of Product Supply Fill &amp; Finish Expansions</t>
+          <t>Project Vice President, Clayton (NC) Expansion</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -10287,12 +10291,12 @@
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>Global (Denmark) (Europe)</t>
+          <t>Clayton, NC (US)</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t>Engineering / Capital Project (Fill-Finish Expansions)</t>
+          <t>Engineering/Capital Project</t>
         </is>
       </c>
       <c r="I80" s="13" t="inlineStr">
@@ -10310,12 +10314,12 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>Erik Lorin Rasmussen</t>
+          <t>Flemming Dahl</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Supply, Aseptic Manufacturing</t>
+          <t>SVP, Head of Product Supply Fill &amp; Finish Expansions</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -10333,19 +10337,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F81" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F81" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>Hillerod, Denmark (Europe)</t>
+          <t>Global (Denmark) (Europe)</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Aseptic)</t>
+          <t>Engineering / Capital Project (Fill-Finish Expansions)</t>
         </is>
       </c>
       <c r="I81" s="13" t="inlineStr">
@@ -10356,19 +10360,19 @@
       <c r="J81" s="13" t="inlineStr"/>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>Peter C. Luke</t>
+          <t>Erik Lorin Rasmussen</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Capital Projects - Drug Substance</t>
+          <t>SVP, Product Supply, Aseptic Manufacturing</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -10386,42 +10390,42 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F82" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Hillerod, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Manufacturing (Aseptic)</t>
         </is>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J82" s="13" t="inlineStr"/>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>Lasse Holm Clausen</t>
+          <t>Peter C. Luke</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Head of Process Management, AI &amp; IT Quality</t>
+          <t>Vice President, Capital Projects - Drug Substance</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -10429,19 +10433,19 @@
           <t>Novo Nordisk</t>
         </is>
       </c>
-      <c r="D83" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F83" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
+        </is>
+      </c>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
@@ -10451,7 +10455,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>Process Management / IT Quality</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -10462,19 +10466,19 @@
       <c r="J83" s="13" t="inlineStr"/>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>Jason Trussell</t>
+          <t>Lasse Holm Clausen</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Director - Bioteam, MSAT and QC</t>
+          <t>Head of Process Management, AI &amp; IT Quality</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -10487,24 +10491,24 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="F84" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
+        </is>
+      </c>
+      <c r="F84" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>Grantham, New Hampshire, United States (US)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QC</t>
+          <t>Process Management / IT Quality</t>
         </is>
       </c>
       <c r="I84" s="13" t="inlineStr">
@@ -10515,19 +10519,19 @@
       <c r="J84" s="13" t="inlineStr"/>
       <c r="K84" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>Mads Overgaard</t>
+          <t>Jason Trussell</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Director - PS API MSAT Technology &amp; Process Facilities</t>
+          <t>Director - Bioteam, MSAT and QC</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -10552,12 +10556,12 @@
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Grantham, New Hampshire, United States (US)</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Facilities</t>
+          <t>MSAT / QC</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -10575,12 +10579,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>Anne-Sophie Eriksen</t>
+          <t>Mads Overgaard</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Director Life Cycle Management, MSAT &amp; QC</t>
+          <t>Director - PS API MSAT Technology &amp; Process Facilities</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -10605,12 +10609,12 @@
       </c>
       <c r="G86" s="13" t="inlineStr">
         <is>
-          <t>Farum, Capital Region of Denmark, Denmark (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
-          <t>MSAT / QC</t>
+          <t>MSAT / Process Facilities</t>
         </is>
       </c>
       <c r="I86" s="13" t="inlineStr">
@@ -10628,12 +10632,12 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>Søren Thuesen Pedersen</t>
+          <t>Anne-Sophie Eriksen</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>Director, CMC Manufacturing Development</t>
+          <t>Director Life Cycle Management, MSAT &amp; QC</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -10651,46 +10655,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F87" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F87" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Farum, Capital Region of Denmark, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>Process Development / CMC</t>
+          <t>MSAT / QC</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J87" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe; ISPE Nordic</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J87" s="13" t="inlineStr"/>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>Søren Rønsted</t>
+          <t>Søren Thuesen Pedersen</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>Director, Finished Product Manufacturing and Science (MSAT)</t>
+          <t>Director, CMC Manufacturing Development</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -10708,42 +10708,46 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F88" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F88" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Finished Product)</t>
+          <t>Process Development / CMC</t>
         </is>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J88" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J88" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe; ISPE Nordic</t>
+        </is>
+      </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>Hao Jiang</t>
+          <t>Søren Rønsted</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>Director, Synthetic API MSAT</t>
+          <t>Director, Finished Product Manufacturing and Science (MSAT)</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -10768,12 +10772,12 @@
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Synthetic API)</t>
+          <t>MSAT (Finished Product)</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -10791,12 +10795,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>Larry Lane</t>
+          <t>Hao Jiang</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>Project Director, Construction &amp; Engineering (Clayton Expansion)</t>
+          <t>Director, Synthetic API MSAT</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -10821,39 +10825,35 @@
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC (US)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Construction / Capital Project)</t>
+          <t>MSAT (Synthetic API)</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J90" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J90" s="13" t="inlineStr"/>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>Jørgen Falkbøll</t>
+          <t>Larry Lane</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>Project Director, Diabetes API (US project)</t>
+          <t>Project Director, Construction &amp; Engineering (Clayton Expansion)</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>Denmark / United States (Europe)</t>
+          <t>Clayton, NC (US)</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Construction / Capital Project)</t>
         </is>
       </c>
       <c r="I91" s="13" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="J91" s="13" t="inlineStr">
         <is>
-          <t>ISPE Europe; ISPE Nordic</t>
+          <t>ISPE Facilities of the Future 2026</t>
         </is>
       </c>
       <c r="K91" s="14" t="inlineStr">
@@ -10905,12 +10905,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>Camilla Ulrich Hassager</t>
+          <t>Jørgen Falkbøll</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Scientific Director, API Quality IT &amp; MSAT</t>
+          <t>Project Director, Diabetes API (US project)</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -10935,50 +10935,54 @@
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
+          <t>Denmark / United States (Europe)</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t>MSAT / API Quality</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J92" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J92" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe; ISPE Nordic</t>
+        </is>
+      </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>Georg Singewald</t>
+          <t>Camilla Ulrich Hassager</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>SVP, Head of Global Engineering, MSAT &amp; Sustainability</t>
+          <t>Scientific Director, API Quality IT &amp; MSAT</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E93" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -10988,24 +10992,20 @@
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (global) (Europe)</t>
+          <t>Kalundborg, Region Zealand, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>Global Engineering (Executive)</t>
+          <t>MSAT / API Quality</t>
         </is>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J93" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe; ISPE Facilities of the Future</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J93" s="13" t="inlineStr"/>
       <c r="K93" s="14" t="inlineStr">
         <is>
           <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
@@ -11015,12 +11015,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>Ann Lee</t>
+          <t>Georg Singewald</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
+          <t>SVP, Head of Global Engineering, MSAT &amp; Sustainability</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -11038,19 +11038,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F94" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F94" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>South San Francisco, CA (US)</t>
+          <t>Basel, Switzerland (global) (Europe)</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
         <is>
-          <t>Technical Development / Manufacturing Science</t>
+          <t>Global Engineering (Executive)</t>
         </is>
       </c>
       <c r="I94" s="13" t="inlineStr">
@@ -11058,22 +11058,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J94" s="13" t="inlineStr"/>
+      <c r="J94" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe; ISPE Facilities of the Future</t>
+        </is>
+      </c>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>Nazeli Dertsakian</t>
+          <t>Ann Lee</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; GM Genentech Oceanside / VP, Global Head Clinical Supply Operations</t>
+          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -11091,19 +11095,19 @@
           <t>Executive (VP+)</t>
         </is>
       </c>
-      <c r="F95" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>Oceanside, CA (US)</t>
+          <t>South San Francisco, CA (US)</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>Site Leadership</t>
+          <t>Technical Development / Manufacturing Science</t>
         </is>
       </c>
       <c r="I95" s="13" t="inlineStr">
@@ -11111,26 +11115,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J95" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+      <c r="J95" s="13" t="inlineStr"/>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>Michael Greening</t>
+          <t>Nazeli Dertsakian</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Executive Director, Head of Project Delivery (US)</t>
+          <t>VP &amp; GM Genentech Oceanside / VP, Global Head Clinical Supply Operations</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -11138,14 +11138,14 @@
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D96" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E96" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
@@ -11155,12 +11155,12 @@
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Oceanside, CA (US)</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Site Leadership</t>
         </is>
       </c>
       <c r="I96" s="13" t="inlineStr">
@@ -11170,24 +11170,24 @@
       </c>
       <c r="J96" s="13" t="inlineStr">
         <is>
-          <t>ISPE Facilities of the Future; ISPE Annual</t>
+          <t>ISPE Facilities of the Future 2026</t>
         </is>
       </c>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Site/plant leadership at a biologics/sterile site — owns local asset &amp; standardisation decisions.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>Eric Fallon</t>
+          <t>Michael Greening</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Head of Global Biologics MSAT, Drug Substance</t>
+          <t>Executive Director, Head of Project Delivery (US)</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Service</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
@@ -11227,24 +11227,24 @@
       </c>
       <c r="J97" s="13" t="inlineStr">
         <is>
-          <t>ISPE Biotechnology; ISPE Annual</t>
+          <t>ISPE Facilities of the Future; ISPE Annual</t>
         </is>
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>Mark Nolden</t>
+          <t>Eric Fallon</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Head of Global MSAT Drug Substance Process Stewards</t>
+          <t>Head of Global Biologics MSAT, Drug Substance</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -11269,20 +11269,24 @@
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>Iffeldorf, Bavaria, Germany (Global)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
-          <t>MSAT (Drug Substance)</t>
+          <t>MSAT / Technical Service</t>
         </is>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J98" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J98" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Biotechnology; ISPE Annual</t>
+        </is>
+      </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
           <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
@@ -11292,12 +11296,12 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>Christian Rutz</t>
+          <t>Mark Nolden</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>Head of Global PTT Engineering &amp; Technology, Global MSAT/Engineering/Sustainability</t>
+          <t>Head of Global MSAT Drug Substance Process Stewards</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -11322,12 +11326,12 @@
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>Mannheim, Baden-Württemberg, Germany (Global)</t>
+          <t>Iffeldorf, Bavaria, Germany (Global)</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>Engineering / MSAT (Global)</t>
+          <t>MSAT (Drug Substance)</t>
         </is>
       </c>
       <c r="I99" s="13" t="inlineStr">
@@ -11345,12 +11349,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>Christian Hakemeyer</t>
+          <t>Christian Rutz</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>Head of MSAT</t>
+          <t>Head of Global PTT Engineering &amp; Technology, Global MSAT/Engineering/Sustainability</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -11375,12 +11379,12 @@
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>Ilvesheim, Baden-Württemberg, Germany (Europe)</t>
+          <t>Mannheim, Baden-Württemberg, Germany (Global)</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t>MSAT</t>
+          <t>Engineering / MSAT (Global)</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr">
@@ -11398,7 +11402,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>Marco Wetzstein</t>
+          <t>Christian Hakemeyer</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
@@ -11428,7 +11432,7 @@
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>Ilvesheim, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -11451,7 +11455,7 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>Qianting Ou</t>
+          <t>Marco Wetzstein</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
@@ -11481,7 +11485,7 @@
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>China (Asia)</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H102" s="13" t="inlineStr">
@@ -11504,12 +11508,12 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>Ethan Wang</t>
+          <t>Qianting Ou</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>Head of Maintenance</t>
+          <t>Head of MSAT</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -11534,12 +11538,12 @@
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Shanghai, China (Asia)</t>
+          <t>China (Asia)</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>MSAT</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr">
@@ -11550,19 +11554,19 @@
       <c r="J103" s="13" t="inlineStr"/>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>MSAT / large-molecule tech ops — process ownership feeding valve &amp; equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>Maurice Lambrecht</t>
+          <t>Ethan Wang</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>Head of Maintenance F&amp;E und SHE</t>
+          <t>Head of Maintenance</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -11587,7 +11591,7 @@
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>Mannheim, Baden-Württemberg, Germany (Europe)</t>
+          <t>Shanghai, China (Asia)</t>
         </is>
       </c>
       <c r="H104" s="13" t="inlineStr">
@@ -11610,12 +11614,12 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>Pascal Ruf</t>
+          <t>Maurice Lambrecht</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Head of Site Infrastructure Engineering</t>
+          <t>Head of Maintenance F&amp;E und SHE</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -11640,12 +11644,12 @@
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (Europe)</t>
+          <t>Mannheim, Baden-Württemberg, Germany (Europe)</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Utilities / Site Infrastructure)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="I105" s="13" t="inlineStr">
@@ -11656,19 +11660,19 @@
       <c r="J105" s="13" t="inlineStr"/>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>Troy Farris</t>
+          <t>Pascal Ruf</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Projects</t>
+          <t>Head of Site Infrastructure Engineering</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -11681,9 +11685,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E106" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -11693,12 +11697,12 @@
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Basel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H106" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Utilities / Site Infrastructure)</t>
         </is>
       </c>
       <c r="I106" s="13" t="inlineStr">
@@ -11709,12 +11713,65 @@
       <c r="J106" s="13" t="inlineStr"/>
       <c r="K106" s="14" t="inlineStr">
         <is>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t>Troy Farris</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>Director, Capital Projects</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E107" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F107" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>Greater Indianapolis (US)</t>
+        </is>
+      </c>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Engineering (Capital Projects)</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J107" s="13" t="inlineStr"/>
+      <c r="K107" s="14" t="inlineStr">
+        <is>
           <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K106"/>
+  <autoFilter ref="A1:K107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11725,7 +11782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K509"/>
+  <dimension ref="A1:K510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -36411,12 +36468,12 @@
     <row r="464">
       <c r="A464" s="13" t="inlineStr">
         <is>
-          <t>F.R. Casal</t>
+          <t>Coralie Richard</t>
         </is>
       </c>
       <c r="B464" s="14" t="inlineStr">
         <is>
-          <t>Assistant Director</t>
+          <t>Director (Parenteral)</t>
         </is>
       </c>
       <c r="C464" s="13" t="inlineStr">
@@ -36441,20 +36498,24 @@
       </c>
       <c r="G464" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="H464" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Assistant Director)</t>
+          <t>Parenteral / Packaging</t>
         </is>
       </c>
       <c r="I464" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J464" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J464" s="13" t="inlineStr">
+        <is>
+          <t>PDA Parenteral Packaging; PDA Week</t>
+        </is>
+      </c>
       <c r="K464" s="14" t="inlineStr">
         <is>
           <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
@@ -36464,12 +36525,12 @@
     <row r="465">
       <c r="A465" s="13" t="inlineStr">
         <is>
-          <t>Melissa Seymour</t>
+          <t>F.R. Casal</t>
         </is>
       </c>
       <c r="B465" s="14" t="inlineStr">
         <is>
-          <t>EVP, Global Quality</t>
+          <t>Assistant Director</t>
         </is>
       </c>
       <c r="C465" s="13" t="inlineStr">
@@ -36477,14 +36538,14 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D465" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E465" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D465" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E465" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F465" s="22" t="inlineStr">
@@ -36494,35 +36555,35 @@
       </c>
       <c r="G465" s="13" t="inlineStr">
         <is>
-          <t>Global (Indianapolis) (US)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="H465" s="13" t="inlineStr">
         <is>
-          <t>Executive (Quality)</t>
+          <t>Manufacturing (Assistant Director)</t>
         </is>
       </c>
       <c r="I465" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J465" s="13" t="inlineStr"/>
       <c r="K465" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="13" t="inlineStr">
         <is>
-          <t>Molly Wagner</t>
+          <t>Melissa Seymour</t>
         </is>
       </c>
       <c r="B466" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Procurement</t>
+          <t>EVP, Global Quality</t>
         </is>
       </c>
       <c r="C466" s="13" t="inlineStr">
@@ -36530,14 +36591,14 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D466" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E466" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="D466" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E466" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F466" s="22" t="inlineStr">
@@ -36547,12 +36608,12 @@
       </c>
       <c r="G466" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Global (Indianapolis) (US)</t>
         </is>
       </c>
       <c r="H466" s="13" t="inlineStr">
         <is>
-          <t>Strategic Sourcing / Procurement</t>
+          <t>Executive (Quality)</t>
         </is>
       </c>
       <c r="I466" s="13" t="inlineStr">
@@ -36563,24 +36624,24 @@
       <c r="J466" s="13" t="inlineStr"/>
       <c r="K466" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="13" t="inlineStr">
         <is>
-          <t>Alan Bateman</t>
+          <t>Molly Wagner</t>
         </is>
       </c>
       <c r="B467" s="14" t="inlineStr">
         <is>
-          <t>Director, Systems Architecture, Digital &amp; Execution</t>
+          <t>Director, Capital Procurement</t>
         </is>
       </c>
       <c r="C467" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D467" s="17" t="inlineStr">
@@ -36600,12 +36661,12 @@
       </c>
       <c r="G467" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="H467" s="13" t="inlineStr">
         <is>
-          <t>Advanced Mfg / Digital</t>
+          <t>Strategic Sourcing / Procurement</t>
         </is>
       </c>
       <c r="I467" s="13" t="inlineStr">
@@ -36613,26 +36674,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J467" s="13" t="inlineStr">
-        <is>
-          <t>ISPE</t>
-        </is>
-      </c>
+      <c r="J467" s="13" t="inlineStr"/>
       <c r="K467" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="13" t="inlineStr">
         <is>
-          <t>Armelle Santelli</t>
+          <t>Alan Bateman</t>
         </is>
       </c>
       <c r="B468" s="14" t="inlineStr">
         <is>
-          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
+          <t>Director, Systems Architecture, Digital &amp; Execution</t>
         </is>
       </c>
       <c r="C468" s="13" t="inlineStr">
@@ -36657,12 +36714,12 @@
       </c>
       <c r="G468" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H468" s="13" t="inlineStr">
         <is>
-          <t>Quality/Regulatory</t>
+          <t>Advanced Mfg / Digital</t>
         </is>
       </c>
       <c r="I468" s="13" t="inlineStr">
@@ -36670,22 +36727,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J468" s="13" t="inlineStr"/>
+      <c r="J468" s="13" t="inlineStr">
+        <is>
+          <t>ISPE</t>
+        </is>
+      </c>
       <c r="K468" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="13" t="inlineStr">
         <is>
-          <t>Carlos Arbelaez, PhD</t>
+          <t>Armelle Santelli</t>
         </is>
       </c>
       <c r="B469" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Cell Therapy Process Development</t>
+          <t>Director General / Pharmacist, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C469" s="13" t="inlineStr">
@@ -36693,14 +36754,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D469" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E469" s="16" t="inlineStr">
-        <is>
-          <t>Assoc Director</t>
+      <c r="D469" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E469" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F469" s="22" t="inlineStr">
@@ -36710,12 +36771,12 @@
       </c>
       <c r="G469" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (US)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H469" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Process Development</t>
+          <t>Quality/Regulatory</t>
         </is>
       </c>
       <c r="I469" s="13" t="inlineStr">
@@ -36723,26 +36784,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J469" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International US West 2026 (Mar 9-11, San Diego, CA) — session confirmed Mar 10, 2:30pm</t>
-        </is>
-      </c>
+      <c r="J469" s="13" t="inlineStr"/>
       <c r="K469" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="13" t="inlineStr">
         <is>
-          <t>Dapo Ajayi</t>
+          <t>Carlos Arbelaez, PhD</t>
         </is>
       </c>
       <c r="B470" s="14" t="inlineStr">
         <is>
-          <t>VP, Innovative Medicine Supply Chain</t>
+          <t>Associate Director, Cell Therapy Process Development</t>
         </is>
       </c>
       <c r="C470" s="13" t="inlineStr">
@@ -36755,9 +36812,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E470" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="E470" s="16" t="inlineStr">
+        <is>
+          <t>Assoc Director</t>
         </is>
       </c>
       <c r="F470" s="22" t="inlineStr">
@@ -36767,12 +36824,12 @@
       </c>
       <c r="G470" s="13" t="inlineStr">
         <is>
-          <t>Wilson, NC (US)</t>
+          <t>Not specified in source (US)</t>
         </is>
       </c>
       <c r="H470" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Manufacturing/Process Development</t>
         </is>
       </c>
       <c r="I470" s="13" t="inlineStr">
@@ -36780,22 +36837,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J470" s="13" t="inlineStr"/>
+      <c r="J470" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International US West 2026 (Mar 9-11, San Diego, CA) — session confirmed Mar 10, 2:30pm</t>
+        </is>
+      </c>
       <c r="K470" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="13" t="inlineStr">
         <is>
-          <t>David Estape</t>
+          <t>Dapo Ajayi</t>
         </is>
       </c>
       <c r="B471" s="14" t="inlineStr">
         <is>
-          <t>Technology Manager, Biotechnology</t>
+          <t>VP, Innovative Medicine Supply Chain</t>
         </is>
       </c>
       <c r="C471" s="13" t="inlineStr">
@@ -36808,9 +36869,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E471" s="16" t="inlineStr">
-        <is>
-          <t>Manager / Lead</t>
+      <c r="E471" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F471" s="22" t="inlineStr">
@@ -36820,12 +36881,12 @@
       </c>
       <c r="G471" s="13" t="inlineStr">
         <is>
-          <t>Europe (J&amp;J)</t>
+          <t>Wilson, NC (US)</t>
         </is>
       </c>
       <c r="H471" s="13" t="inlineStr">
         <is>
-          <t>Process Development / Advanced Mfg</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="I471" s="13" t="inlineStr">
@@ -36833,26 +36894,22 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J471" s="13" t="inlineStr">
-        <is>
-          <t>ISPE</t>
-        </is>
-      </c>
+      <c r="J471" s="13" t="inlineStr"/>
       <c r="K471" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="13" t="inlineStr">
         <is>
-          <t>Johan Van Hoof, MD</t>
+          <t>David Estape</t>
         </is>
       </c>
       <c r="B472" s="14" t="inlineStr">
         <is>
-          <t>Global Therapeutic Area Head IDV, Vaccines</t>
+          <t>Technology Manager, Biotechnology</t>
         </is>
       </c>
       <c r="C472" s="13" t="inlineStr">
@@ -36860,14 +36917,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D472" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E472" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="D472" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E472" s="16" t="inlineStr">
+        <is>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F472" s="22" t="inlineStr">
@@ -36877,12 +36934,12 @@
       </c>
       <c r="G472" s="13" t="inlineStr">
         <is>
-          <t>Leiden, Netherlands (Europe)</t>
+          <t>Europe (J&amp;J)</t>
         </is>
       </c>
       <c r="H472" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D/Vaccines</t>
+          <t>Process Development / Advanced Mfg</t>
         </is>
       </c>
       <c r="I472" s="13" t="inlineStr">
@@ -36890,22 +36947,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J472" s="13" t="inlineStr"/>
+      <c r="J472" s="13" t="inlineStr">
+        <is>
+          <t>ISPE</t>
+        </is>
+      </c>
       <c r="K472" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="13" t="inlineStr">
         <is>
-          <t>Julian Hooks</t>
+          <t>Johan Van Hoof, MD</t>
         </is>
       </c>
       <c r="B473" s="14" t="inlineStr">
         <is>
-          <t>VP, Global Services Operations &amp; Procurement</t>
+          <t>Global Therapeutic Area Head IDV, Vaccines</t>
         </is>
       </c>
       <c r="C473" s="13" t="inlineStr">
@@ -36930,12 +36991,12 @@
       </c>
       <c r="G473" s="13" t="inlineStr">
         <is>
-          <t>Enterprise-wide (Global) (US)</t>
+          <t>Leiden, Netherlands (Europe)</t>
         </is>
       </c>
       <c r="H473" s="13" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>R&amp;D/Vaccines</t>
         </is>
       </c>
       <c r="I473" s="13" t="inlineStr">
@@ -36946,19 +37007,19 @@
       <c r="J473" s="13" t="inlineStr"/>
       <c r="K473" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="13" t="inlineStr">
         <is>
-          <t>Kimberly Lounds Foster</t>
+          <t>Julian Hooks</t>
         </is>
       </c>
       <c r="B474" s="14" t="inlineStr">
         <is>
-          <t>Global Head, Advanced Therapies Supply Chain</t>
+          <t>VP, Global Services Operations &amp; Procurement</t>
         </is>
       </c>
       <c r="C474" s="13" t="inlineStr">
@@ -36983,12 +37044,12 @@
       </c>
       <c r="G474" s="13" t="inlineStr">
         <is>
-          <t>Advanced therapies manufacturing network (US)</t>
+          <t>Enterprise-wide (Global) (US)</t>
         </is>
       </c>
       <c r="H474" s="13" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="I474" s="13" t="inlineStr">
@@ -37006,12 +37067,12 @@
     <row r="475">
       <c r="A475" s="13" t="inlineStr">
         <is>
-          <t>Leila Schwery-Bou-Diab</t>
+          <t>Kimberly Lounds Foster</t>
         </is>
       </c>
       <c r="B475" s="14" t="inlineStr">
         <is>
-          <t>VP Manufacturing &amp; Technical Operations</t>
+          <t>Global Head, Advanced Therapies Supply Chain</t>
         </is>
       </c>
       <c r="C475" s="13" t="inlineStr">
@@ -37019,14 +37080,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D475" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E475" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D475" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E475" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F475" s="22" t="inlineStr">
@@ -37036,12 +37097,12 @@
       </c>
       <c r="G475" s="13" t="inlineStr">
         <is>
-          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
+          <t>Advanced therapies manufacturing network (US)</t>
         </is>
       </c>
       <c r="H475" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Technical Operations</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="I475" s="13" t="inlineStr">
@@ -37052,19 +37113,19 @@
       <c r="J475" s="13" t="inlineStr"/>
       <c r="K475" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="13" t="inlineStr">
         <is>
-          <t>Marius Muller</t>
+          <t>Leila Schwery-Bou-Diab</t>
         </is>
       </c>
       <c r="B476" s="14" t="inlineStr">
         <is>
-          <t>Scientific Senior Manager, TDS Biologics AD</t>
+          <t>VP Manufacturing &amp; Technical Operations</t>
         </is>
       </c>
       <c r="C476" s="13" t="inlineStr">
@@ -37072,14 +37133,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D476" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E476" s="16" t="inlineStr">
-        <is>
-          <t>Sr Manager / Principal</t>
+      <c r="D476" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E476" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F476" s="22" t="inlineStr">
@@ -37089,12 +37150,12 @@
       </c>
       <c r="G476" s="13" t="inlineStr">
         <is>
-          <t>Basel, Switzerland (Europe)</t>
+          <t>Ringaskiddy (Cork), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H476" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing Science/Technical Development</t>
+          <t>Manufacturing/Technical Operations</t>
         </is>
       </c>
       <c r="I476" s="13" t="inlineStr">
@@ -37102,11 +37163,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J476" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
-        </is>
-      </c>
+      <c r="J476" s="13" t="inlineStr"/>
       <c r="K476" s="14" t="inlineStr">
         <is>
           <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
@@ -37116,12 +37173,12 @@
     <row r="477">
       <c r="A477" s="13" t="inlineStr">
         <is>
-          <t>Maxime Bergman</t>
+          <t>Marius Muller</t>
         </is>
       </c>
       <c r="B477" s="14" t="inlineStr">
         <is>
-          <t>Senior Scientist, Process II, Global Process Development, TDS, Drug Product Development &amp; Delivery</t>
+          <t>Scientific Senior Manager, TDS Biologics AD</t>
         </is>
       </c>
       <c r="C477" s="13" t="inlineStr">
@@ -37129,14 +37186,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D477" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E477" s="13" t="inlineStr">
-        <is>
-          <t>Senior IC</t>
+      <c r="D477" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E477" s="16" t="inlineStr">
+        <is>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F477" s="22" t="inlineStr">
@@ -37146,12 +37203,12 @@
       </c>
       <c r="G477" s="13" t="inlineStr">
         <is>
-          <t>Not specified in source (Europe)</t>
+          <t>Basel, Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H477" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing/Process Development</t>
+          <t>Manufacturing Science/Technical Development</t>
         </is>
       </c>
       <c r="I477" s="13" t="inlineStr">
@@ -37166,19 +37223,19 @@
       </c>
       <c r="K477" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="13" t="inlineStr">
         <is>
-          <t>Robin Kumoluyi</t>
+          <t>Maxime Bergman</t>
         </is>
       </c>
       <c r="B478" s="14" t="inlineStr">
         <is>
-          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
+          <t>Senior Scientist, Process II, Global Process Development, TDS, Drug Product Development &amp; Delivery</t>
         </is>
       </c>
       <c r="C478" s="13" t="inlineStr">
@@ -37186,14 +37243,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D478" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E478" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D478" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E478" s="13" t="inlineStr">
+        <is>
+          <t>Senior IC</t>
         </is>
       </c>
       <c r="F478" s="22" t="inlineStr">
@@ -37203,12 +37260,12 @@
       </c>
       <c r="G478" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Not specified in source (Europe)</t>
         </is>
       </c>
       <c r="H478" s="13" t="inlineStr">
         <is>
-          <t>Quality (Executive)</t>
+          <t>Manufacturing/Process Development</t>
         </is>
       </c>
       <c r="I478" s="13" t="inlineStr">
@@ -37218,39 +37275,39 @@
       </c>
       <c r="J478" s="13" t="inlineStr">
         <is>
-          <t>Pharma Manufacturing World Summit</t>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
         </is>
       </c>
       <c r="K478" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="13" t="inlineStr">
         <is>
-          <t>Roderick Freeman</t>
+          <t>Robin Kumoluyi</t>
         </is>
       </c>
       <c r="B479" s="14" t="inlineStr">
         <is>
-          <t>Site Quality Head, Novartis RLT (Radioligand Therapy)</t>
+          <t>VP &amp; Chief Quality Officer, Innovative Medicine</t>
         </is>
       </c>
       <c r="C479" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D479" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E479" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D479" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E479" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F479" s="22" t="inlineStr">
@@ -37260,12 +37317,12 @@
       </c>
       <c r="G479" s="13" t="inlineStr">
         <is>
-          <t>US (RLT site)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H479" s="13" t="inlineStr">
         <is>
-          <t>Quality (Site)</t>
+          <t>Quality (Executive)</t>
         </is>
       </c>
       <c r="I479" s="13" t="inlineStr">
@@ -37275,7 +37332,7 @@
       </c>
       <c r="J479" s="13" t="inlineStr">
         <is>
-          <t>ISPE Facilities of the Future 2026</t>
+          <t>Pharma Manufacturing World Summit</t>
         </is>
       </c>
       <c r="K479" s="14" t="inlineStr">
@@ -37287,12 +37344,12 @@
     <row r="480">
       <c r="A480" s="13" t="inlineStr">
         <is>
-          <t>Roland Gander</t>
+          <t>Roderick Freeman</t>
         </is>
       </c>
       <c r="B480" s="14" t="inlineStr">
         <is>
-          <t>Global Head Large Molecules / Cell &amp; Gene Therapies; MD, Novartis Pharmaceutical GmbH (Kundl)</t>
+          <t>Site Quality Head, Novartis RLT (Radioligand Therapy)</t>
         </is>
       </c>
       <c r="C480" s="13" t="inlineStr">
@@ -37300,9 +37357,9 @@
           <t>Novartis</t>
         </is>
       </c>
-      <c r="D480" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
+      <c r="D480" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
         </is>
       </c>
       <c r="E480" s="13" t="inlineStr">
@@ -37317,12 +37374,12 @@
       </c>
       <c r="G480" s="13" t="inlineStr">
         <is>
-          <t>Kundl, Austria (Europe)</t>
+          <t>US (RLT site)</t>
         </is>
       </c>
       <c r="H480" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Large Molecules / CGT)</t>
+          <t>Quality (Site)</t>
         </is>
       </c>
       <c r="I480" s="13" t="inlineStr">
@@ -37330,37 +37387,41 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J480" s="13" t="inlineStr"/>
+      <c r="J480" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="K480" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="13" t="inlineStr">
         <is>
-          <t>Erik Lorin Rasmussen</t>
+          <t>Roland Gander</t>
         </is>
       </c>
       <c r="B481" s="14" t="inlineStr">
         <is>
-          <t>SVP, Product Supply, Aseptic Manufacturing</t>
+          <t>Global Head Large Molecules / Cell &amp; Gene Therapies; MD, Novartis Pharmaceutical GmbH (Kundl)</t>
         </is>
       </c>
       <c r="C481" s="13" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
-        </is>
-      </c>
-      <c r="D481" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E481" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D481" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E481" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F481" s="22" t="inlineStr">
@@ -37370,12 +37431,12 @@
       </c>
       <c r="G481" s="13" t="inlineStr">
         <is>
-          <t>Hillerod, Denmark (Europe)</t>
+          <t>Kundl, Austria (Europe)</t>
         </is>
       </c>
       <c r="H481" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Aseptic)</t>
+          <t>Manufacturing (Large Molecules / CGT)</t>
         </is>
       </c>
       <c r="I481" s="13" t="inlineStr">
@@ -37386,19 +37447,19 @@
       <c r="J481" s="13" t="inlineStr"/>
       <c r="K481" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="13" t="inlineStr">
         <is>
-          <t>Henrik Wulff</t>
+          <t>Erik Lorin Rasmussen</t>
         </is>
       </c>
       <c r="B482" s="14" t="inlineStr">
         <is>
-          <t>EVP, Product Supply, Quality &amp; IT</t>
+          <t>SVP, Product Supply, Aseptic Manufacturing</t>
         </is>
       </c>
       <c r="C482" s="13" t="inlineStr">
@@ -37423,12 +37484,12 @@
       </c>
       <c r="G482" s="13" t="inlineStr">
         <is>
-          <t>Clayton, NC / Kalundborg, DK (Global)</t>
+          <t>Hillerod, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H482" s="13" t="inlineStr">
         <is>
-          <t>Executive (Supply/Quality)</t>
+          <t>Manufacturing (Aseptic)</t>
         </is>
       </c>
       <c r="I482" s="13" t="inlineStr">
@@ -37439,19 +37500,19 @@
       <c r="J482" s="13" t="inlineStr"/>
       <c r="K482" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="13" t="inlineStr">
         <is>
-          <t>Lasse Holm Clausen</t>
+          <t>Henrik Wulff</t>
         </is>
       </c>
       <c r="B483" s="14" t="inlineStr">
         <is>
-          <t>Head of Process Management, AI &amp; IT Quality</t>
+          <t>EVP, Product Supply, Quality &amp; IT</t>
         </is>
       </c>
       <c r="C483" s="13" t="inlineStr">
@@ -37459,14 +37520,14 @@
           <t>Novo Nordisk</t>
         </is>
       </c>
-      <c r="D483" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E483" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
+      <c r="D483" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E483" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F483" s="22" t="inlineStr">
@@ -37476,17 +37537,17 @@
       </c>
       <c r="G483" s="13" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark (Europe)</t>
+          <t>Clayton, NC / Kalundborg, DK (Global)</t>
         </is>
       </c>
       <c r="H483" s="13" t="inlineStr">
         <is>
-          <t>Process Management / IT Quality</t>
+          <t>Executive (Supply/Quality)</t>
         </is>
       </c>
       <c r="I483" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J483" s="13" t="inlineStr"/>
@@ -37499,12 +37560,12 @@
     <row r="484">
       <c r="A484" s="13" t="inlineStr">
         <is>
-          <t>Søren Thuesen Pedersen</t>
+          <t>Lasse Holm Clausen</t>
         </is>
       </c>
       <c r="B484" s="14" t="inlineStr">
         <is>
-          <t>Director, CMC Manufacturing Development</t>
+          <t>Head of Process Management, AI &amp; IT Quality</t>
         </is>
       </c>
       <c r="C484" s="13" t="inlineStr">
@@ -37517,9 +37578,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E484" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="E484" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F484" s="22" t="inlineStr">
@@ -37529,44 +37590,40 @@
       </c>
       <c r="G484" s="13" t="inlineStr">
         <is>
-          <t>Denmark (Europe)</t>
+          <t>Copenhagen, Denmark (Europe)</t>
         </is>
       </c>
       <c r="H484" s="13" t="inlineStr">
         <is>
-          <t>Process Development / CMC</t>
+          <t>Process Management / IT Quality</t>
         </is>
       </c>
       <c r="I484" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J484" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe; ISPE Nordic</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J484" s="13" t="inlineStr"/>
       <c r="K484" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="13" t="inlineStr">
         <is>
-          <t>Bob Iser</t>
+          <t>Søren Thuesen Pedersen</t>
         </is>
       </c>
       <c r="B485" s="14" t="inlineStr">
         <is>
-          <t>Global Head, Quality Policy &amp; Advocacy</t>
+          <t>Director, CMC Manufacturing Development</t>
         </is>
       </c>
       <c r="C485" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="D485" s="17" t="inlineStr">
@@ -37574,9 +37631,9 @@
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E485" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="E485" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F485" s="22" t="inlineStr">
@@ -37586,12 +37643,12 @@
       </c>
       <c r="G485" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Denmark (Europe)</t>
         </is>
       </c>
       <c r="H485" s="13" t="inlineStr">
         <is>
-          <t>Quality Policy</t>
+          <t>Process Development / CMC</t>
         </is>
       </c>
       <c r="I485" s="13" t="inlineStr">
@@ -37601,24 +37658,24 @@
       </c>
       <c r="J485" s="13" t="inlineStr">
         <is>
-          <t>ISPE Facilities of the Future</t>
+          <t>ISPE Europe; ISPE Nordic</t>
         </is>
       </c>
       <c r="K485" s="14" t="inlineStr">
         <is>
-          <t>QA / validation — influences equipment qualification and change control.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="13" t="inlineStr">
         <is>
-          <t>Marie Czogalla</t>
+          <t>Bob Iser</t>
         </is>
       </c>
       <c r="B486" s="14" t="inlineStr">
         <is>
-          <t>Partnering System Change Specialist Sterile Filling</t>
+          <t>Global Head, Quality Policy &amp; Advocacy</t>
         </is>
       </c>
       <c r="C486" s="13" t="inlineStr">
@@ -37626,14 +37683,14 @@
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D486" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
+      <c r="D486" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
         </is>
       </c>
       <c r="E486" s="13" t="inlineStr">
         <is>
-          <t>Senior IC</t>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F486" s="22" t="inlineStr">
@@ -37643,35 +37700,39 @@
       </c>
       <c r="G486" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H486" s="13" t="inlineStr">
         <is>
-          <t>Process / Sterile Filling</t>
+          <t>Quality Policy</t>
         </is>
       </c>
       <c r="I486" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J486" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J486" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future</t>
+        </is>
+      </c>
       <c r="K486" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>QA / validation — influences equipment qualification and change control.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="13" t="inlineStr">
         <is>
-          <t>Tobias Gerbracht</t>
+          <t>Marie Czogalla</t>
         </is>
       </c>
       <c r="B487" s="14" t="inlineStr">
         <is>
-          <t>Technology Scientific Expert</t>
+          <t>Partnering System Change Specialist Sterile Filling</t>
         </is>
       </c>
       <c r="C487" s="13" t="inlineStr">
@@ -37686,7 +37747,7 @@
       </c>
       <c r="E487" s="13" t="inlineStr">
         <is>
-          <t>Engineer / IC</t>
+          <t>Senior IC</t>
         </is>
       </c>
       <c r="F487" s="22" t="inlineStr">
@@ -37696,12 +37757,12 @@
       </c>
       <c r="G487" s="13" t="inlineStr">
         <is>
-          <t>Grenzach-Wyhlen, Germany (Europe)</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H487" s="13" t="inlineStr">
         <is>
-          <t>Process Development</t>
+          <t>Process / Sterile Filling</t>
         </is>
       </c>
       <c r="I487" s="13" t="inlineStr">
@@ -37712,77 +37773,77 @@
       <c r="J487" s="13" t="inlineStr"/>
       <c r="K487" s="14" t="inlineStr">
         <is>
-          <t>Process development / advanced-mfg — specs process equipment early.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="13" t="inlineStr">
         <is>
-          <t>Azita Saleki-Gerhardt, PhD</t>
+          <t>Tobias Gerbracht</t>
         </is>
       </c>
       <c r="B488" s="14" t="inlineStr">
         <is>
-          <t>EVP, Chief Operations Officer</t>
+          <t>Technology Scientific Expert</t>
         </is>
       </c>
       <c r="C488" s="13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
-        </is>
-      </c>
-      <c r="D488" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E488" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
-        </is>
-      </c>
-      <c r="F488" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D488" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E488" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F488" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G488" s="13" t="inlineStr">
         <is>
-          <t>Global (mfg/eng/quality/supply) (US)</t>
+          <t>Grenzach-Wyhlen, Germany (Europe)</t>
         </is>
       </c>
       <c r="H488" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>Process Development</t>
         </is>
       </c>
       <c r="I488" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J488" s="13" t="inlineStr"/>
       <c r="K488" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Process development / advanced-mfg — specs process equipment early.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="13" t="inlineStr">
         <is>
-          <t>Pam Cheng</t>
+          <t>Azita Saleki-Gerhardt, PhD</t>
         </is>
       </c>
       <c r="B489" s="14" t="inlineStr">
         <is>
-          <t>EVP, Global Operations &amp; IT, Chief Sustainability Officer</t>
+          <t>EVP, Chief Operations Officer</t>
         </is>
       </c>
       <c r="C489" s="13" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="D489" s="15" t="inlineStr">
@@ -37802,7 +37863,7 @@
       </c>
       <c r="G489" s="13" t="inlineStr">
         <is>
-          <t>Global (UK/US)</t>
+          <t>Global (mfg/eng/quality/supply) (US)</t>
         </is>
       </c>
       <c r="H489" s="13" t="inlineStr">
@@ -37825,27 +37886,27 @@
     <row r="490">
       <c r="A490" s="13" t="inlineStr">
         <is>
-          <t>Eamonn Warren</t>
+          <t>Pam Cheng</t>
         </is>
       </c>
       <c r="B490" s="14" t="inlineStr">
         <is>
-          <t>Group VP, API &amp; Dry Products Manufacturing</t>
+          <t>EVP, Global Operations &amp; IT, Chief Sustainability Officer</t>
         </is>
       </c>
       <c r="C490" s="13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="D490" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E490" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="D490" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E490" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F490" s="16" t="inlineStr">
@@ -37855,12 +37916,12 @@
       </c>
       <c r="G490" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Global (UK/US)</t>
         </is>
       </c>
       <c r="H490" s="13" t="inlineStr">
         <is>
-          <t>API Manufacturing (Executive)</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="I490" s="13" t="inlineStr">
@@ -37868,11 +37929,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J490" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit; ISPE Annual</t>
-        </is>
-      </c>
+      <c r="J490" s="13" t="inlineStr"/>
       <c r="K490" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -37882,12 +37939,12 @@
     <row r="491">
       <c r="A491" s="13" t="inlineStr">
         <is>
-          <t>Edgardo Hernandez</t>
+          <t>Eamonn Warren</t>
         </is>
       </c>
       <c r="B491" s="14" t="inlineStr">
         <is>
-          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
+          <t>Group VP, API &amp; Dry Products Manufacturing</t>
         </is>
       </c>
       <c r="C491" s="13" t="inlineStr">
@@ -37895,14 +37952,14 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D491" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E491" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D491" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E491" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F491" s="16" t="inlineStr">
@@ -37912,12 +37969,12 @@
       </c>
       <c r="G491" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H491" s="13" t="inlineStr">
         <is>
-          <t>Executive (Manufacturing)</t>
+          <t>API Manufacturing (Executive)</t>
         </is>
       </c>
       <c r="I491" s="13" t="inlineStr">
@@ -37925,7 +37982,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J491" s="13" t="inlineStr"/>
+      <c r="J491" s="13" t="inlineStr">
+        <is>
+          <t>Pharma Manufacturing World Summit; ISPE Annual</t>
+        </is>
+      </c>
       <c r="K491" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -37935,12 +37996,12 @@
     <row r="492">
       <c r="A492" s="13" t="inlineStr">
         <is>
-          <t>Syed Abbas Yar-Khan</t>
+          <t>Edgardo Hernandez</t>
         </is>
       </c>
       <c r="B492" s="14" t="inlineStr">
         <is>
-          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
+          <t>EVP &amp; President, Lilly Manufacturing Operations</t>
         </is>
       </c>
       <c r="C492" s="13" t="inlineStr">
@@ -37965,12 +38026,12 @@
       </c>
       <c r="G492" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Lebanon, IN / Concord, NC / Limerick, IE / Kinsale, IE (US)</t>
         </is>
       </c>
       <c r="H492" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Parenteral / Devices)</t>
+          <t>Executive (Manufacturing)</t>
         </is>
       </c>
       <c r="I492" s="13" t="inlineStr">
@@ -37978,11 +38039,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J492" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+      <c r="J492" s="13" t="inlineStr"/>
       <c r="K492" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -37992,17 +38049,17 @@
     <row r="493">
       <c r="A493" s="13" t="inlineStr">
         <is>
-          <t>Delphine Caron</t>
+          <t>Syed Abbas Yar-Khan</t>
         </is>
       </c>
       <c r="B493" s="14" t="inlineStr">
         <is>
-          <t>President, Janssen-Cilag (France)</t>
+          <t>Group Vice President, Global Parenteral Products &amp; Devices</t>
         </is>
       </c>
       <c r="C493" s="13" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="D493" s="15" t="inlineStr">
@@ -38022,12 +38079,12 @@
       </c>
       <c r="G493" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H493" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country President)</t>
+          <t>Manufacturing (Parenteral / Devices)</t>
         </is>
       </c>
       <c r="I493" s="13" t="inlineStr">
@@ -38035,7 +38092,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J493" s="13" t="inlineStr"/>
+      <c r="J493" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
+        </is>
+      </c>
       <c r="K493" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38045,12 +38106,12 @@
     <row r="494">
       <c r="A494" s="13" t="inlineStr">
         <is>
-          <t>Joaquin Duato</t>
+          <t>Delphine Caron</t>
         </is>
       </c>
       <c r="B494" s="14" t="inlineStr">
         <is>
-          <t>Chairman &amp; CEO</t>
+          <t>President, Janssen-Cilag (France)</t>
         </is>
       </c>
       <c r="C494" s="13" t="inlineStr">
@@ -38075,12 +38136,12 @@
       </c>
       <c r="G494" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H494" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Executive (Country President)</t>
         </is>
       </c>
       <c r="I494" s="13" t="inlineStr">
@@ -38098,12 +38159,12 @@
     <row r="495">
       <c r="A495" s="13" t="inlineStr">
         <is>
-          <t>John Reed, MD, PhD</t>
+          <t>Joaquin Duato</t>
         </is>
       </c>
       <c r="B495" s="14" t="inlineStr">
         <is>
-          <t>EVP, Innovative Medicine R&amp;D</t>
+          <t>Chairman &amp; CEO</t>
         </is>
       </c>
       <c r="C495" s="13" t="inlineStr">
@@ -38133,7 +38194,7 @@
       </c>
       <c r="H495" s="13" t="inlineStr">
         <is>
-          <t>Executive (R&amp;D)</t>
+          <t>Executive (CEO)</t>
         </is>
       </c>
       <c r="I495" s="13" t="inlineStr">
@@ -38141,11 +38202,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J495" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J495" s="13" t="inlineStr"/>
       <c r="K495" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38155,12 +38212,12 @@
     <row r="496">
       <c r="A496" s="13" t="inlineStr">
         <is>
-          <t>M. Martinez Climent</t>
+          <t>John Reed, MD, PhD</t>
         </is>
       </c>
       <c r="B496" s="14" t="inlineStr">
         <is>
-          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
+          <t>EVP, Innovative Medicine R&amp;D</t>
         </is>
       </c>
       <c r="C496" s="13" t="inlineStr">
@@ -38168,14 +38225,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D496" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E496" s="21" t="inlineStr">
-        <is>
-          <t>Director</t>
+      <c r="D496" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E496" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F496" s="16" t="inlineStr">
@@ -38185,12 +38242,12 @@
       </c>
       <c r="G496" s="13" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, France (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H496" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country DG)</t>
+          <t>Executive (R&amp;D)</t>
         </is>
       </c>
       <c r="I496" s="13" t="inlineStr">
@@ -38198,7 +38255,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J496" s="13" t="inlineStr"/>
+      <c r="J496" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K496" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38208,12 +38269,12 @@
     <row r="497">
       <c r="A497" s="13" t="inlineStr">
         <is>
-          <t>Namal Nawana</t>
+          <t>M. Martinez Climent</t>
         </is>
       </c>
       <c r="B497" s="14" t="inlineStr">
         <is>
-          <t>Worldwide President, DePuy Synthes</t>
+          <t>Director-General, Johnson &amp; Johnson Medical (France)</t>
         </is>
       </c>
       <c r="C497" s="13" t="inlineStr">
@@ -38221,14 +38282,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D497" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E497" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D497" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E497" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
         </is>
       </c>
       <c r="F497" s="16" t="inlineStr">
@@ -38238,12 +38299,12 @@
       </c>
       <c r="G497" s="13" t="inlineStr">
         <is>
-          <t>Orthopedics manufacturing network (Global)</t>
+          <t>Issy-les-Moulineaux, France (Europe)</t>
         </is>
       </c>
       <c r="H497" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (Country DG)</t>
         </is>
       </c>
       <c r="I497" s="13" t="inlineStr">
@@ -38261,12 +38322,12 @@
     <row r="498">
       <c r="A498" s="13" t="inlineStr">
         <is>
-          <t>Nauman Shah</t>
+          <t>Namal Nawana</t>
         </is>
       </c>
       <c r="B498" s="14" t="inlineStr">
         <is>
-          <t>Global Head of Business Development</t>
+          <t>Worldwide President, DePuy Synthes</t>
         </is>
       </c>
       <c r="C498" s="13" t="inlineStr">
@@ -38274,14 +38335,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D498" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E498" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
+      <c r="D498" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E498" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F498" s="16" t="inlineStr">
@@ -38291,12 +38352,12 @@
       </c>
       <c r="G498" s="13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Orthopedics manufacturing network (Global)</t>
         </is>
       </c>
       <c r="H498" s="13" t="inlineStr">
         <is>
-          <t>Executive (Business Development)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I498" s="13" t="inlineStr">
@@ -38304,11 +38365,7 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J498" s="13" t="inlineStr">
-        <is>
-          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
-        </is>
-      </c>
+      <c r="J498" s="13" t="inlineStr"/>
       <c r="K498" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38318,12 +38375,12 @@
     <row r="499">
       <c r="A499" s="13" t="inlineStr">
         <is>
-          <t>Tim Schmid</t>
+          <t>Nauman Shah</t>
         </is>
       </c>
       <c r="B499" s="14" t="inlineStr">
         <is>
-          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
+          <t>Global Head of Business Development</t>
         </is>
       </c>
       <c r="C499" s="13" t="inlineStr">
@@ -38331,14 +38388,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D499" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E499" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+      <c r="D499" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E499" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F499" s="16" t="inlineStr">
@@ -38353,7 +38410,7 @@
       </c>
       <c r="H499" s="13" t="inlineStr">
         <is>
-          <t>Executive (MedTech)</t>
+          <t>Executive (Business Development)</t>
         </is>
       </c>
       <c r="I499" s="13" t="inlineStr">
@@ -38361,7 +38418,11 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J499" s="13" t="inlineStr"/>
+      <c r="J499" s="13" t="inlineStr">
+        <is>
+          <t>BIO International Convention 2026 (Jun 22-25, San Diego, CA)</t>
+        </is>
+      </c>
       <c r="K499" s="14" t="inlineStr">
         <is>
           <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
@@ -38371,12 +38432,12 @@
     <row r="500">
       <c r="A500" s="13" t="inlineStr">
         <is>
-          <t>Tom Heyman</t>
+          <t>Tim Schmid</t>
         </is>
       </c>
       <c r="B500" s="14" t="inlineStr">
         <is>
-          <t>CEO, Janssen Pharmaceutica (Belgium)</t>
+          <t>EVP, Worldwide Chairman, Johnson &amp; Johnson MedTech</t>
         </is>
       </c>
       <c r="C500" s="13" t="inlineStr">
@@ -38384,14 +38445,14 @@
           <t>Johnson &amp; Johnson</t>
         </is>
       </c>
-      <c r="D500" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E500" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="D500" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E500" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F500" s="16" t="inlineStr">
@@ -38401,12 +38462,12 @@
       </c>
       <c r="G500" s="13" t="inlineStr">
         <is>
-          <t>Geel, Belgium (Europe)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H500" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country CEO)</t>
+          <t>Executive (MedTech)</t>
         </is>
       </c>
       <c r="I500" s="13" t="inlineStr">
@@ -38424,27 +38485,27 @@
     <row r="501">
       <c r="A501" s="13" t="inlineStr">
         <is>
-          <t>James Weirich</t>
+          <t>Tom Heyman</t>
         </is>
       </c>
       <c r="B501" s="14" t="inlineStr">
         <is>
-          <t>Vice President, Cell &amp; Gene Therapy Head</t>
+          <t>CEO, Janssen Pharmaceutica (Belgium)</t>
         </is>
       </c>
       <c r="C501" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D501" s="15" t="inlineStr">
-        <is>
-          <t>1. Leadership</t>
-        </is>
-      </c>
-      <c r="E501" s="15" t="inlineStr">
-        <is>
-          <t>Executive (VP+)</t>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D501" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E501" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
         </is>
       </c>
       <c r="F501" s="16" t="inlineStr">
@@ -38454,12 +38515,12 @@
       </c>
       <c r="G501" s="13" t="inlineStr">
         <is>
-          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
+          <t>Geel, Belgium (Europe)</t>
         </is>
       </c>
       <c r="H501" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
+          <t>Executive (Country CEO)</t>
         </is>
       </c>
       <c r="I501" s="13" t="inlineStr">
@@ -38477,12 +38538,12 @@
     <row r="502">
       <c r="A502" s="13" t="inlineStr">
         <is>
-          <t>Steffen Lang, PhD</t>
+          <t>James Weirich</t>
         </is>
       </c>
       <c r="B502" s="14" t="inlineStr">
         <is>
-          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
+          <t>Vice President, Cell &amp; Gene Therapy Head</t>
         </is>
       </c>
       <c r="C502" s="13" t="inlineStr">
@@ -38507,12 +38568,12 @@
       </c>
       <c r="G502" s="13" t="inlineStr">
         <is>
-          <t>Global (incl. Durham, NC / Kundl, AT)</t>
+          <t>Durham, NC / Morris Plains, NJ (CGT) (US)</t>
         </is>
       </c>
       <c r="H502" s="13" t="inlineStr">
         <is>
-          <t>Executive (Operations)</t>
+          <t>Manufacturing (Cell &amp; Gene Therapy)</t>
         </is>
       </c>
       <c r="I502" s="13" t="inlineStr">
@@ -38530,17 +38591,17 @@
     <row r="503">
       <c r="A503" s="13" t="inlineStr">
         <is>
-          <t>Ann Lee</t>
+          <t>Steffen Lang, PhD</t>
         </is>
       </c>
       <c r="B503" s="14" t="inlineStr">
         <is>
-          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
+          <t>President, Operations (former Global Head, Novartis Technical Operations)</t>
         </is>
       </c>
       <c r="C503" s="13" t="inlineStr">
         <is>
-          <t>Roche/Genentech</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D503" s="15" t="inlineStr">
@@ -38560,12 +38621,12 @@
       </c>
       <c r="G503" s="13" t="inlineStr">
         <is>
-          <t>South San Francisco, CA (US)</t>
+          <t>Global (incl. Durham, NC / Kundl, AT)</t>
         </is>
       </c>
       <c r="H503" s="13" t="inlineStr">
         <is>
-          <t>Technical Development / Manufacturing Science</t>
+          <t>Executive (Operations)</t>
         </is>
       </c>
       <c r="I503" s="13" t="inlineStr">
@@ -38583,12 +38644,12 @@
     <row r="504">
       <c r="A504" s="13" t="inlineStr">
         <is>
-          <t>Ashley Magargee</t>
+          <t>Ann Lee</t>
         </is>
       </c>
       <c r="B504" s="14" t="inlineStr">
         <is>
-          <t>CEO, Genentech</t>
+          <t>SVP, Process R&amp;D &amp; Head of Global Technical Development</t>
         </is>
       </c>
       <c r="C504" s="13" t="inlineStr">
@@ -38596,14 +38657,14 @@
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D504" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E504" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="D504" s="15" t="inlineStr">
+        <is>
+          <t>1. Leadership</t>
+        </is>
+      </c>
+      <c r="E504" s="15" t="inlineStr">
+        <is>
+          <t>Executive (VP+)</t>
         </is>
       </c>
       <c r="F504" s="16" t="inlineStr">
@@ -38613,12 +38674,12 @@
       </c>
       <c r="G504" s="13" t="inlineStr">
         <is>
-          <t>Holly Springs, NC (US)</t>
+          <t>South San Francisco, CA (US)</t>
         </is>
       </c>
       <c r="H504" s="13" t="inlineStr">
         <is>
-          <t>Executive (CEO)</t>
+          <t>Technical Development / Manufacturing Science</t>
         </is>
       </c>
       <c r="I504" s="13" t="inlineStr">
@@ -38636,42 +38697,42 @@
     <row r="505">
       <c r="A505" s="13" t="inlineStr">
         <is>
-          <t>Dana Kendall</t>
+          <t>Ashley Magargee</t>
         </is>
       </c>
       <c r="B505" s="14" t="inlineStr">
         <is>
-          <t>General Manager, AbbVie Ireland</t>
+          <t>CEO, Genentech</t>
         </is>
       </c>
       <c r="C505" s="13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
-        </is>
-      </c>
-      <c r="D505" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
-        </is>
-      </c>
-      <c r="E505" s="18" t="inlineStr">
-        <is>
-          <t>Site / Function Head</t>
-        </is>
-      </c>
-      <c r="F505" s="19" t="inlineStr">
-        <is>
-          <t>De-prioritise</t>
+          <t>Roche/Genentech</t>
+        </is>
+      </c>
+      <c r="D505" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E505" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F505" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G505" s="13" t="inlineStr">
         <is>
-          <t>Dublin (Citywest), Ireland (Europe)</t>
+          <t>Holly Springs, NC (US)</t>
         </is>
       </c>
       <c r="H505" s="13" t="inlineStr">
         <is>
-          <t>Executive (Country GM)</t>
+          <t>Executive (CEO)</t>
         </is>
       </c>
       <c r="I505" s="13" t="inlineStr">
@@ -38682,24 +38743,24 @@
       <c r="J505" s="13" t="inlineStr"/>
       <c r="K505" s="14" t="inlineStr">
         <is>
-          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="13" t="inlineStr">
         <is>
-          <t>Guy Oliver</t>
+          <t>Dana Kendall</t>
         </is>
       </c>
       <c r="B506" s="14" t="inlineStr">
         <is>
-          <t>General Manager, UK &amp; Ireland</t>
+          <t>General Manager, AbbVie Ireland</t>
         </is>
       </c>
       <c r="C506" s="13" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="D506" s="17" t="inlineStr">
@@ -38719,7 +38780,7 @@
       </c>
       <c r="G506" s="13" t="inlineStr">
         <is>
-          <t>UK &amp; Ireland (Europe)</t>
+          <t>Dublin (Citywest), Ireland (Europe)</t>
         </is>
       </c>
       <c r="H506" s="13" t="inlineStr">
@@ -38742,27 +38803,27 @@
     <row r="507">
       <c r="A507" s="13" t="inlineStr">
         <is>
-          <t>Maria T.</t>
+          <t>Guy Oliver</t>
         </is>
       </c>
       <c r="B507" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Medical Science Liaison - Immunology CART</t>
+          <t>General Manager, UK &amp; Ireland</t>
         </is>
       </c>
       <c r="C507" s="13" t="inlineStr">
         <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="D507" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E507" s="16" t="inlineStr">
-        <is>
-          <t>Assoc Director</t>
+          <t>Bristol Myers Squibb</t>
+        </is>
+      </c>
+      <c r="D507" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E507" s="18" t="inlineStr">
+        <is>
+          <t>Site / Function Head</t>
         </is>
       </c>
       <c r="F507" s="19" t="inlineStr">
@@ -38772,17 +38833,17 @@
       </c>
       <c r="G507" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>UK &amp; Ireland (Europe)</t>
         </is>
       </c>
       <c r="H507" s="13" t="inlineStr">
         <is>
-          <t>Medical Affairs</t>
+          <t>Executive (Country GM)</t>
         </is>
       </c>
       <c r="I507" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J507" s="13" t="inlineStr"/>
@@ -38795,12 +38856,12 @@
     <row r="508">
       <c r="A508" s="13" t="inlineStr">
         <is>
-          <t>Thierry Diagana</t>
+          <t>Maria T.</t>
         </is>
       </c>
       <c r="B508" s="14" t="inlineStr">
         <is>
-          <t>California Sites Head, Novartis Biomedical Research</t>
+          <t>Associate Director, Medical Science Liaison - Immunology CART</t>
         </is>
       </c>
       <c r="C508" s="13" t="inlineStr">
@@ -38813,9 +38874,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E508" s="13" t="inlineStr">
-        <is>
-          <t>Engineer / IC</t>
+      <c r="E508" s="16" t="inlineStr">
+        <is>
+          <t>Assoc Director</t>
         </is>
       </c>
       <c r="F508" s="19" t="inlineStr">
@@ -38825,17 +38886,17 @@
       </c>
       <c r="G508" s="13" t="inlineStr">
         <is>
-          <t>San Diego / Emeryville, CA (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H508" s="13" t="inlineStr">
         <is>
-          <t>R&amp;D / Research Site Leadership</t>
+          <t>Medical Affairs</t>
         </is>
       </c>
       <c r="I508" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J508" s="13" t="inlineStr"/>
@@ -38848,62 +38909,115 @@
     <row r="509">
       <c r="A509" s="13" t="inlineStr">
         <is>
+          <t>Thierry Diagana</t>
+        </is>
+      </c>
+      <c r="B509" s="14" t="inlineStr">
+        <is>
+          <t>California Sites Head, Novartis Biomedical Research</t>
+        </is>
+      </c>
+      <c r="C509" s="13" t="inlineStr">
+        <is>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D509" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E509" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F509" s="19" t="inlineStr">
+        <is>
+          <t>De-prioritise</t>
+        </is>
+      </c>
+      <c r="G509" s="13" t="inlineStr">
+        <is>
+          <t>San Diego / Emeryville, CA (US)</t>
+        </is>
+      </c>
+      <c r="H509" s="13" t="inlineStr">
+        <is>
+          <t>R&amp;D / Research Site Leadership</t>
+        </is>
+      </c>
+      <c r="I509" s="13" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J509" s="13" t="inlineStr"/>
+      <c r="K509" s="14" t="inlineStr">
+        <is>
+          <t>Medical/commercial/research role — low relevance to valve/equipment decisions (de-prioritise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="13" t="inlineStr">
+        <is>
           <t>Franck Bure</t>
         </is>
       </c>
-      <c r="B509" s="14" t="inlineStr">
+      <c r="B510" s="14" t="inlineStr">
         <is>
           <t>(title not stated in source)</t>
         </is>
       </c>
-      <c r="C509" s="13" t="inlineStr">
+      <c r="C510" s="13" t="inlineStr">
         <is>
           <t>Roche/Genentech</t>
         </is>
       </c>
-      <c r="D509" s="17" t="inlineStr">
+      <c r="D510" s="17" t="inlineStr">
         <is>
           <t>2. Global / Functional</t>
         </is>
       </c>
-      <c r="E509" s="13" t="inlineStr">
+      <c r="E510" s="13" t="inlineStr">
         <is>
           <t>Engineer / IC</t>
         </is>
       </c>
-      <c r="F509" s="19" t="inlineStr">
+      <c r="F510" s="19" t="inlineStr">
         <is>
           <t>De-prioritise</t>
         </is>
       </c>
-      <c r="G509" s="13" t="inlineStr">
+      <c r="G510" s="13" t="inlineStr">
         <is>
           <t>Not specified in source (Global)</t>
         </is>
       </c>
-      <c r="H509" s="13" t="inlineStr">
+      <c r="H510" s="13" t="inlineStr">
         <is>
           <t>Unknown (conference speaker)</t>
         </is>
       </c>
-      <c r="I509" s="13" t="inlineStr">
+      <c r="I510" s="13" t="inlineStr">
         <is>
           <t>Public</t>
         </is>
       </c>
-      <c r="J509" s="13" t="inlineStr">
+      <c r="J510" s="13" t="inlineStr">
         <is>
           <t>ISPE Aseptic Conference 2026</t>
         </is>
       </c>
-      <c r="K509" s="14" t="inlineStr">
+      <c r="K510" s="14" t="inlineStr">
         <is>
           <t>Conference-confirmed contact but role/title unknown — verify function before ranking.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K509"/>
+  <autoFilter ref="A1:K510"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49328,7 +49442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -49836,12 +49950,12 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Molly Wagner</t>
+          <t>Coralie Richard</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Director, Capital Procurement</t>
+          <t>Director (Parenteral)</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -49866,12 +49980,12 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>Strategic Sourcing / Procurement</t>
+          <t>Parenteral / Packaging</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
@@ -49879,22 +49993,26 @@
           <t>Public</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>PDA Parenteral Packaging; PDA Week</t>
+        </is>
+      </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Kenneth Swank</t>
+          <t>Molly Wagner</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Sr. Director - Major Capital Projects</t>
+          <t>Director, Capital Procurement</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -49912,42 +50030,42 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Greenwood, Indiana, United States (US)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Strategic Sourcing / Procurement</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Sourcing / procurement — commercial gatekeeper for valve &amp; equipment contracts.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Robert O'Keeffe</t>
+          <t>Kenneth Swank</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Senior Director, Engineering Tech Centre</t>
+          <t>Sr. Director - Major Capital Projects</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -49972,39 +50090,35 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Limerick NGB) (Europe)</t>
+          <t>Greenwood, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Massimiliano Ammannito</t>
+          <t>Robert O'Keeffe</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Sr Director - Facilities, Utilities &amp; Capital Projects</t>
+          <t>Senior Director, Engineering Tech Centre</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -50029,12 +50143,12 @@
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Italy (Europe)</t>
+          <t>Ireland (Limerick NGB) (Europe)</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Utilities / Capital Projects</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
@@ -50044,24 +50158,24 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>ISPE Aseptic Conference; ISPE Europe</t>
+          <t>ISPE Europe Annual Conference 2026 (Apr 20-22, Copenhagen)</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>F.R. Casal</t>
+          <t>Massimiliano Ammannito</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Assistant Director</t>
+          <t>Sr Director - Facilities, Utilities &amp; Capital Projects</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -50079,42 +50193,46 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Italy (Europe)</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing (Assistant Director)</t>
+          <t>Utilities / Capital Projects</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Aseptic Conference; ISPE Europe</t>
+        </is>
+      </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>John Hillmer</t>
+          <t>F.R. Casal</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Major Capital Projects Procurement Lead</t>
+          <t>Assistant Director</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -50122,29 +50240,29 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>Manager / Lead</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Atlanta Metropolitan Area (US)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects) / Procurement</t>
+          <t>Manufacturing (Assistant Director)</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
@@ -50155,19 +50273,19 @@
       <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Rick Rowe</t>
+          <t>John Hillmer</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Project Manager, Eli Lilly</t>
+          <t>Major Capital Projects Procurement Lead</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -50192,12 +50310,12 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Bargersville, Indiana, United States (US)</t>
+          <t>Atlanta Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Project / PM)</t>
+          <t>Engineering (Capital Projects) / Procurement</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
@@ -50215,12 +50333,12 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Cillian McDowell</t>
+          <t>Rick Rowe</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead</t>
+          <t>Project Manager, Eli Lilly</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -50245,12 +50363,12 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>Belfast Metropolitan Area (Europe)</t>
+          <t>Bargersville, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Project / PM)</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -50261,19 +50379,19 @@
       <c r="J17" s="13" t="inlineStr"/>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Nikhil Singh</t>
+          <t>Cillian McDowell</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Lead - Cell Culture Area</t>
+          <t>CQV Lead</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -50298,7 +50416,7 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Cork, County Cork, Ireland (Europe)</t>
+          <t>Belfast Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -50321,12 +50439,12 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Michael McCarthy</t>
+          <t>Nikhil Singh</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead - Utilities</t>
+          <t>C&amp;Q Lead - Cell Culture Area</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -50351,12 +50469,12 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>County Cork, Ireland (Europe)</t>
+          <t>Cork, County Cork, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Utilities)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
@@ -50367,19 +50485,19 @@
       <c r="J19" s="13" t="inlineStr"/>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Mark Mundow</t>
+          <t>Michael McCarthy</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Receipt Verification / Hot Loop &amp; Calibration Lead</t>
+          <t>CQV Lead - Utilities</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -50404,12 +50522,12 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Dundalk, County Louth, Ireland (Europe)</t>
+          <t>County Cork, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering / C&amp;Q (Utilities)</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
@@ -50420,19 +50538,19 @@
       <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Paola Boffa</t>
+          <t>Mark Mundow</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Sr Principal Engineer - C&amp;Q</t>
+          <t>C&amp;Q Receipt Verification / Hot Loop &amp; Calibration Lead</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -50447,7 +50565,7 @@
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -50457,7 +50575,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>Florence, Tuscany, Italy (Europe)</t>
+          <t>Dundalk, County Louth, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -50473,19 +50591,19 @@
       <c r="J21" s="13" t="inlineStr"/>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Murielle Pernel</t>
+          <t>Paola Boffa</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Sr Principal Scientist (MSAT process expert)</t>
+          <t>Sr Principal Engineer - C&amp;Q</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -50510,12 +50628,12 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>Geispolsheim, Grand Est, France (Europe)</t>
+          <t>Florence, Tuscany, Italy (Europe)</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Process Expert</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
@@ -50533,12 +50651,12 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Orlagh Moran</t>
+          <t>Murielle Pernel</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>EHS Lead Construction &amp; C&amp;Q</t>
+          <t>Sr Principal Scientist (MSAT process expert)</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -50553,7 +50671,7 @@
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -50563,12 +50681,12 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>Germany (Europe)</t>
+          <t>Geispolsheim, Grand Est, France (Europe)</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>MSAT / Process Expert</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
@@ -50579,19 +50697,19 @@
       <c r="J23" s="13" t="inlineStr"/>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Marian Watt</t>
+          <t>Orlagh Moran</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>CQV Document Control Lead</t>
+          <t>EHS Lead Construction &amp; C&amp;Q</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -50616,7 +50734,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>Greater Dublin (Europe)</t>
+          <t>Germany (Europe)</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -50632,19 +50750,19 @@
       <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Corey Povaleri</t>
+          <t>Marian Watt</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Principal Engineer - Project Manager</t>
+          <t>CQV Document Control Lead</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -50659,7 +50777,7 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -50669,12 +50787,12 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Greater Dublin (Europe)</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -50685,19 +50803,19 @@
       <c r="J25" s="13" t="inlineStr"/>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Marlon Johnson</t>
+          <t>Corey Povaleri</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Principal Engineer - Project Manager</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -50712,7 +50830,7 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -50722,12 +50840,12 @@
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>Greenwood, Indiana, United States (US)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -50738,19 +50856,19 @@
       <c r="J26" s="13" t="inlineStr"/>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Andrew Ross, P.E.</t>
+          <t>Marlon Johnson</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Principal Engineer - Facilities Design</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -50765,7 +50883,7 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -50775,12 +50893,12 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>Indianapolis, Indiana, United States (US)</t>
+          <t>Greenwood, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
@@ -50791,19 +50909,19 @@
       <c r="J27" s="13" t="inlineStr"/>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Frank A Glad</t>
+          <t>Andrew Ross, P.E.</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Manager of Engineering</t>
+          <t>Principal Engineer - Facilities Design</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -50818,7 +50936,7 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -50833,7 +50951,7 @@
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I28" s="13" t="inlineStr">
@@ -50844,19 +50962,19 @@
       <c r="J28" s="13" t="inlineStr"/>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>Lauren Blubaugh</t>
+          <t>Frank A Glad</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Principal Engineer - Design Lead, GFD Profiling &amp; Design</t>
+          <t>Manager of Engineering</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -50871,7 +50989,7 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -50886,7 +51004,7 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -50897,19 +51015,19 @@
       <c r="J29" s="13" t="inlineStr"/>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Varun Agrawal</t>
+          <t>Lauren Blubaugh</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Principal Engineer - CQV Process Owner</t>
+          <t>Principal Engineer - Design Lead, GFD Profiling &amp; Design</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -50939,7 +51057,7 @@
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -50957,12 +51075,12 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Ciaran Spratt</t>
+          <t>Varun Agrawal</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Clean Utilities Lead</t>
+          <t>Principal Engineer - CQV Process Owner</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -50977,7 +51095,7 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -50987,12 +51105,12 @@
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Indianapolis, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Utilities)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
@@ -51010,12 +51128,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>Conor Higgins</t>
+          <t>Ciaran Spratt</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>HVAC &amp; Utility C&amp;Q Lead (IE2b project)</t>
+          <t>C&amp;Q Clean Utilities Lead</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -51063,12 +51181,12 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Patrick Harnedy</t>
+          <t>Conor Higgins</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Senior Principal Engineer</t>
+          <t>HVAC &amp; Utility C&amp;Q Lead (IE2b project)</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -51083,7 +51201,7 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -51098,19 +51216,15 @@
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / C&amp;Q (Utilities)</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr"/>
       <c r="K33" s="14" t="inlineStr">
         <is>
           <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
@@ -51120,12 +51234,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>Rachel Jones</t>
+          <t>Patrick Harnedy</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead</t>
+          <t>Senior Principal Engineer</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -51140,7 +51254,7 @@
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -51155,30 +51269,34 @@
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+        </is>
+      </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>Shane Dorgan</t>
+          <t>Rachel Jones</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Lead C&amp;Q Engineer small molecule projects IE8</t>
+          <t>CQV Lead</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -51226,12 +51344,12 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Stephen King</t>
+          <t>Shane Dorgan</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Project Manager</t>
+          <t>Lead C&amp;Q Engineer small molecule projects IE8</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -51279,12 +51397,12 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>Alessandro Massimo Carassai</t>
+          <t>Stephen King</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>CQV Project Lead</t>
+          <t>C&amp;Q Project Manager</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -51309,7 +51427,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Italy (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -51332,12 +51450,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Lulu Tabel</t>
+          <t>Alessandro Massimo Carassai</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Capital Projects Procurement Lead</t>
+          <t>CQV Project Lead</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -51362,12 +51480,12 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Katy, Texas, United States (US)</t>
+          <t>Italy (Europe)</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>Procurement (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
@@ -51378,19 +51496,19 @@
       <c r="J38" s="13" t="inlineStr"/>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Rey Del Valle</t>
+          <t>Lulu Tabel</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Principal Engineer / Project Manager</t>
+          <t>Capital Projects Procurement Lead</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -51405,7 +51523,7 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -51415,12 +51533,12 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Kenosha, Wisconsin, United States (US)</t>
+          <t>Katy, Texas, United States (US)</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Procurement (Capital Projects)</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
@@ -51431,19 +51549,19 @@
       <c r="J39" s="13" t="inlineStr"/>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>Paul McGinley</t>
+          <t>Rey Del Valle</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>CQV Lead</t>
+          <t>Principal Engineer / Project Manager</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
@@ -51458,7 +51576,7 @@
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -51468,12 +51586,12 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Kilbirnie, Scotland, United Kingdom (Europe)</t>
+          <t>Kenosha, Wisconsin, United States (US)</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
@@ -51484,19 +51602,19 @@
       <c r="J40" s="13" t="inlineStr"/>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Bryan Trapp</t>
+          <t>Paul McGinley</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>LP1 Maintenance Manager</t>
+          <t>CQV Lead</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -51521,12 +51639,12 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Lafayette, Indiana, United States (US)</t>
+          <t>Kilbirnie, Scotland, United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
@@ -51537,19 +51655,19 @@
       <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>Andrew D.</t>
+          <t>Bryan Trapp</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Site C&amp;Q Lead - Lilly Limerick</t>
+          <t>LP1 Maintenance Manager</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -51574,12 +51692,12 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Limerick, County Limerick, Ireland (Europe)</t>
+          <t>Lafayette, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Site Lead)</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
@@ -51590,19 +51708,19 @@
       <c r="J42" s="13" t="inlineStr"/>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Gerard O'Halloran</t>
+          <t>Andrew D.</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>CQV Manager - Utilities &amp; HVAC (Jacobs @ Lilly Limerick)</t>
+          <t>Site C&amp;Q Lead - Lilly Limerick</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -51632,7 +51750,7 @@
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Utilities)</t>
+          <t>Engineering / C&amp;Q (Site Lead)</t>
         </is>
       </c>
       <c r="I43" s="13" t="inlineStr">
@@ -51643,19 +51761,19 @@
       <c r="J43" s="13" t="inlineStr"/>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>Mirko Camerotto</t>
+          <t>Gerard O'Halloran</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Automation Lead (SimoTech @ Lilly Limerick)</t>
+          <t>CQV Manager - Utilities &amp; HVAC (Jacobs @ Lilly Limerick)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -51685,7 +51803,7 @@
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Automation)</t>
+          <t>Engineering / C&amp;Q (Utilities)</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -51696,19 +51814,19 @@
       <c r="J44" s="13" t="inlineStr"/>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Abel Padilla</t>
+          <t>Mirko Camerotto</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Capital Projects Manager / Design Lead / Construction Quality Manager</t>
+          <t>C&amp;Q Automation Lead (SimoTech @ Lilly Limerick)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -51733,12 +51851,12 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Limerick, County Limerick, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q (Automation)</t>
         </is>
       </c>
       <c r="I45" s="13" t="inlineStr">
@@ -51749,19 +51867,19 @@
       <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Keith Weseli</t>
+          <t>Abel Padilla</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Advisor - Program Manager</t>
+          <t>Capital Projects Manager / Design Lead / Construction Quality Manager</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -51786,39 +51904,35 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>Engineering / Program Management (Aseptic)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Aseptic Conference 2026 (Conference Chair)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr"/>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Keerthi Reddy Saripalli</t>
+          <t>Keith Weseli</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Sr Principal Engineer - Major Capital Projects &amp; PMO</t>
+          <t>Advisor - Program Manager</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -51833,7 +51947,7 @@
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
@@ -51843,35 +51957,39 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / Program Management (Aseptic)</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Aseptic Conference 2026 (Conference Chair)</t>
+        </is>
+      </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Kofi Appiah-Nkansah</t>
+          <t>Keerthi Reddy Saripalli</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Associate Director, Technical Services / Mfg Science (MSAT)</t>
+          <t>Sr Principal Engineer - Major Capital Projects &amp; PMO</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -51886,7 +52004,7 @@
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>Assoc Director</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
@@ -51901,7 +52019,7 @@
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>MSAT / Technical Services</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -51919,12 +52037,12 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Puja Tanwani</t>
+          <t>Kofi Appiah-Nkansah</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Associate Director - Process Design (Global Engineering Capital Projects)</t>
+          <t>Associate Director, Technical Services / Mfg Science (MSAT)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
@@ -51932,9 +52050,9 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr">
@@ -51954,7 +52072,7 @@
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects / Process Design)</t>
+          <t>MSAT / Technical Services</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
@@ -51965,19 +52083,19 @@
       <c r="J49" s="13" t="inlineStr"/>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Barbara Boodrasang</t>
+          <t>Puja Tanwani</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Sr. Principal Engineer - Project Manager, Capital Projects</t>
+          <t>Associate Director - Process Design (Global Engineering Capital Projects)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -51985,14 +52103,14 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>Sr Manager / Principal</t>
+          <t>Assoc Director</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
@@ -52002,12 +52120,12 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Westfield, Indiana, United States (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Capital Projects / Process Design)</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
@@ -52018,19 +52136,19 @@
       <c r="J50" s="13" t="inlineStr"/>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Edwin Bosshart</t>
+          <t>Barbara Boodrasang</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Maintenance Manager</t>
+          <t>Sr. Principal Engineer - Project Manager, Capital Projects</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -52045,7 +52163,7 @@
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>Manager / Lead</t>
+          <t>Sr Manager / Principal</t>
         </is>
       </c>
       <c r="F51" s="20" t="inlineStr">
@@ -52055,12 +52173,12 @@
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Whitestown, Indiana, United States (US)</t>
+          <t>Westfield, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>Maintenance / Reliability</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
@@ -52071,19 +52189,19 @@
       <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Hafid Gomez Rodriguez</t>
+          <t>Edwin Bosshart</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Senior C&amp;Q Engineer</t>
+          <t>Maintenance Manager</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -52096,9 +52214,9 @@
           <t>3. Site / Working</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>Senior IC</t>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>Manager / Lead</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
@@ -52108,12 +52226,12 @@
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Carmel, Indiana, United States (US)</t>
+          <t>Whitestown, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Maintenance / Reliability</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
@@ -52124,19 +52242,19 @@
       <c r="J52" s="13" t="inlineStr"/>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Asset reliability &amp; maintenance — the predictive-maintenance / lifecycle buyer.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Paul Callanan</t>
+          <t>Hafid Gomez Rodriguez</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Senior Clean Utilities CQV Engineer (Phase 2)</t>
+          <t>Senior C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -52161,12 +52279,12 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Greater Dublin (Europe)</t>
+          <t>Carmel, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Utilities)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
@@ -52177,19 +52295,19 @@
       <c r="J53" s="13" t="inlineStr"/>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Berkan Altun</t>
+          <t>Paul Callanan</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Senior C&amp;Q Parenteral Engineer</t>
+          <t>Senior Clean Utilities CQV Engineer (Phase 2)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -52214,12 +52332,12 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Greater Strasbourg Metropolitan Area (Europe)</t>
+          <t>Greater Dublin (Europe)</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering / C&amp;Q (Utilities)</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -52230,19 +52348,19 @@
       <c r="J54" s="13" t="inlineStr"/>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>Eliyes A.</t>
+          <t>Berkan Altun</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Senior C&amp;Q Engineer</t>
+          <t>Senior C&amp;Q Parenteral Engineer</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -52290,12 +52408,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Kameron Eisenhour</t>
+          <t>Eliyes A.</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Sr Project Engineer</t>
+          <t>Senior C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -52320,12 +52438,12 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Indianapolis, Indiana, United States (US)</t>
+          <t>Greater Strasbourg Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
@@ -52343,12 +52461,12 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>Alan Reen</t>
+          <t>Kameron Eisenhour</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Sr Project Engineer</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -52373,7 +52491,7 @@
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Indianapolis, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -52396,7 +52514,7 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>Dermot Cawley</t>
+          <t>Alan Reen</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -52449,12 +52567,12 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>Kieran Houlihan</t>
+          <t>Dermot Cawley</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Senior CQV Engineer</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -52484,7 +52602,7 @@
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr">
@@ -52502,12 +52620,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Kieran O' Connell</t>
+          <t>Kieran Houlihan</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Senior CQV Engineer (Jacobs @ Lilly)</t>
+          <t>Senior CQV Engineer</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -52555,12 +52673,12 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>Mary Lafferty</t>
+          <t>Kieran O' Connell</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>Biopharmaceutical C&amp;Q SME</t>
+          <t>Senior CQV Engineer (Jacobs @ Lilly)</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -52608,12 +52726,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>Sinead Dullaghan</t>
+          <t>Mary Lafferty</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Senior Principal Scientist, TSMS</t>
+          <t>Biopharmaceutical C&amp;Q SME</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -52643,34 +52761,30 @@
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing Science (TSMS)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J62" s="13" t="inlineStr">
-        <is>
-          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr"/>
       <c r="K62" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Shane Lawler</t>
+          <t>Sinead Dullaghan</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Senior CQV Engineer (Clean &amp; Grey Utilities, CIP)</t>
+          <t>Senior Principal Scientist, TSMS</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -52695,20 +52809,24 @@
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>Limerick Metropolitan Area (Europe)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Utilities)</t>
+          <t>Manufacturing Science (TSMS)</t>
         </is>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J63" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>BioProcess International Europe 2026 (Apr 28-30, Vienna)</t>
+        </is>
+      </c>
       <c r="K63" s="14" t="inlineStr">
         <is>
           <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
@@ -52718,12 +52836,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>Keshav Jha</t>
+          <t>Shane Lawler</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Senior CQV Engineer (Clean &amp; Grey Utilities, CIP)</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -52748,12 +52866,12 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>New York City Metropolitan Area (US)</t>
+          <t>Limerick Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q (Utilities)</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr">
@@ -52764,19 +52882,19 @@
       <c r="J64" s="13" t="inlineStr"/>
       <c r="K64" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>Lauren Battaglia</t>
+          <t>Keshav Jha</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Senior Site Project Engineer</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -52801,7 +52919,7 @@
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>Northbrook, Illinois, United States (US)</t>
+          <t>New York City Metropolitan Area (US)</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -52824,12 +52942,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Jorge Paraliticci</t>
+          <t>Lauren Battaglia</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Sr. Project Engineer</t>
+          <t>Senior Site Project Engineer</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -52854,7 +52972,7 @@
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>Puerto Rico (US)</t>
+          <t>Northbrook, Illinois, United States (US)</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -52877,7 +52995,7 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Karl Johnson</t>
+          <t>Jorge Paraliticci</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -52907,7 +53025,7 @@
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>Puerto Rico (US)</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -52930,12 +53048,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>Nitu Gupta</t>
+          <t>Karl Johnson</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Advisor -Engineering Projects/ Capital Steward</t>
+          <t>Sr. Project Engineer</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -52965,7 +53083,7 @@
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -52983,12 +53101,12 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>Melanie Jackson</t>
+          <t>Nitu Gupta</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Sr Project Engineer, Plant Engineering</t>
+          <t>Advisor -Engineering Projects/ Capital Steward</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -53013,12 +53131,12 @@
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>West Orange, New Jersey, United States (US)</t>
+          <t>United States (US)</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
@@ -53036,12 +53154,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Joe Griffin</t>
+          <t>Melanie Jackson</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Lab CQV Engineer</t>
+          <t>Sr Project Engineer, Plant Engineering</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -53056,7 +53174,7 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>Engineer / IC</t>
+          <t>Senior IC</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
@@ -53066,12 +53184,12 @@
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Alzey, Rhineland-Palatinate, Germany (Europe)</t>
+          <t>West Orange, New Jersey, United States (US)</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
@@ -53089,12 +53207,12 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Sean Kelly</t>
+          <t>Joe Griffin</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer (Doc Prep)</t>
+          <t>Lab CQV Engineer</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -53119,7 +53237,7 @@
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Belfast Metropolitan Area (Europe)</t>
+          <t>Alzey, Rhineland-Palatinate, Germany (Europe)</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -53142,12 +53260,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>William Foley</t>
+          <t>Sean Kelly</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>C&amp;Q Engineer (Doc Prep)</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -53172,7 +53290,7 @@
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>Cork / Alzey (Germany) (Europe)</t>
+          <t>Belfast Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -53195,12 +53313,12 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Fay Fitzpatrick</t>
+          <t>William Foley</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -53225,7 +53343,7 @@
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>Cork Metropolitan Area (Europe)</t>
+          <t>Cork / Alzey (Germany) (Europe)</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -53248,12 +53366,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>Darragh Metcalfe</t>
+          <t>Fay Fitzpatrick</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -53278,12 +53396,12 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>Cork, County Cork, Ireland (Europe)</t>
+          <t>Cork Metropolitan Area (Europe)</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
@@ -53301,12 +53419,12 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Don O Driscoll</t>
+          <t>Darragh Metcalfe</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -53336,7 +53454,7 @@
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
@@ -53354,12 +53472,12 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>Evan Murphy</t>
+          <t>Don O Driscoll</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -53407,12 +53525,12 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>Nicola Roche</t>
+          <t>Evan Murphy</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Project Process Engineer</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -53442,7 +53560,7 @@
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Process)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
@@ -53460,12 +53578,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>Shaun O'Callaghan</t>
+          <t>Nicola Roche</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>Project Process Engineer</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -53495,7 +53613,7 @@
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Process)</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -53513,12 +53631,12 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>Shirin Lutfiya Afzal Khan</t>
+          <t>Shaun O'Callaghan</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Engineer (C&amp;Q)</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -53566,12 +53684,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>Himanshu Sharma</t>
+          <t>Shirin Lutfiya Afzal Khan</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q</t>
+          <t>Engineer (C&amp;Q)</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -53596,7 +53714,7 @@
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>Dublin, County Dublin, Ireland (Europe)</t>
+          <t>Cork, County Cork, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -53619,12 +53737,12 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>Mark Tobin</t>
+          <t>Himanshu Sharma</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>C&amp;Q</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -53654,7 +53772,7 @@
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I81" s="13" t="inlineStr">
@@ -53672,12 +53790,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>Saikrishna Sanathanan</t>
+          <t>Mark Tobin</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -53707,7 +53825,7 @@
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I82" s="13" t="inlineStr">
@@ -53725,12 +53843,12 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>Tracy McEntee</t>
+          <t>Saikrishna Sanathanan</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -53755,7 +53873,7 @@
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>Dundalk, County Louth, Ireland (Europe)</t>
+          <t>Dublin, County Dublin, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -53778,12 +53896,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>Demetrius Symonette II</t>
+          <t>Tracy McEntee</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -53808,7 +53926,7 @@
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>Freeport, The Bahamas (Americas)</t>
+          <t>Dundalk, County Louth, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -53831,12 +53949,12 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>Alicja Zagozdzon</t>
+          <t>Demetrius Symonette II</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -53861,7 +53979,7 @@
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>Germany (Europe)</t>
+          <t>Freeport, The Bahamas (Americas)</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -53884,7 +54002,7 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>Dean F.</t>
+          <t>Alicja Zagozdzon</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -53937,12 +54055,12 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>Sarah M.</t>
+          <t>Dean F.</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q QA Compliance</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -53990,12 +54108,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>Theofylaktos Tokas</t>
+          <t>Sarah M.</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>C&amp;Q QA Compliance</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -54043,12 +54161,12 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>Tyra Hugill</t>
+          <t>Theofylaktos Tokas</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -54096,12 +54214,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>Connor T.</t>
+          <t>Tyra Hugill</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -54126,12 +54244,12 @@
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>Greater Indianapolis (US)</t>
+          <t>Germany (Europe)</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I90" s="13" t="inlineStr">
@@ -54149,12 +54267,12 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>Conor O Neill</t>
+          <t>Connor T.</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -54184,7 +54302,7 @@
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I91" s="13" t="inlineStr">
@@ -54202,12 +54320,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>Vincent Margiotta</t>
+          <t>Conor O Neill</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -54237,7 +54355,7 @@
       </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I92" s="13" t="inlineStr">
@@ -54255,12 +54373,12 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>Anthony Byrne</t>
+          <t>Vincent Margiotta</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -54285,12 +54403,12 @@
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>Greater Liverpool Area (Europe)</t>
+          <t>Greater Indianapolis (US)</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I93" s="13" t="inlineStr">
@@ -54308,12 +54426,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>Elizabeth Robin</t>
+          <t>Anthony Byrne</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>Consulting Engineer (Design, Large Capital Projects)</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -54338,12 +54456,12 @@
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>Indianapolis, Indiana, United States (US)</t>
+          <t>Greater Liverpool Area (Europe)</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I94" s="13" t="inlineStr">
@@ -54354,19 +54472,19 @@
       <c r="J94" s="13" t="inlineStr"/>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>Lizmarie C.</t>
+          <t>Elizabeth Robin</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer - Global Facilities Delivery</t>
+          <t>Consulting Engineer (Design, Large Capital Projects)</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -54374,9 +54492,9 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D95" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
+      <c r="D95" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
@@ -54414,12 +54532,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>Nathan Rhoades</t>
+          <t>Lizmarie C.</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Consultant Engineer - Project Engineering &amp; Program Management (Major Capital), IAPI</t>
+          <t>Project Engineer - Global Facilities Delivery</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -54427,9 +54545,9 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D96" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
@@ -54467,12 +54585,12 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>Nathan Wright</t>
+          <t>Nathan Rhoades</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer (Automation, Fermentation)</t>
+          <t>Consultant Engineer - Project Engineering &amp; Program Management (Major Capital), IAPI</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -54502,7 +54620,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Automation)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
@@ -54513,19 +54631,19 @@
       <c r="J97" s="13" t="inlineStr"/>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>Samantha Kahn</t>
+          <t>Nathan Wright</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Engineer - Project, IAPI</t>
+          <t>Project Engineer (Automation, Fermentation)</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -54555,7 +54673,7 @@
       </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q (Automation)</t>
         </is>
       </c>
       <c r="I98" s="13" t="inlineStr">
@@ -54573,12 +54691,12 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>Scott Ronczka</t>
+          <t>Samantha Kahn</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Engineer - Project, IAPI</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -54626,12 +54744,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>Sean Barry-Murphy</t>
+          <t>Scott Ronczka</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -54661,7 +54779,7 @@
       </c>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr">
@@ -54679,12 +54797,12 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>Tom Gorgol</t>
+          <t>Sean Barry-Murphy</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
@@ -54714,7 +54832,7 @@
       </c>
       <c r="H101" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I101" s="13" t="inlineStr">
@@ -54732,12 +54850,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>Eamon Judge</t>
+          <t>Tom Gorgol</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>EMEA Major Project Planning Leader</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -54762,35 +54880,35 @@
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>Ireland (EMEA) (Europe)</t>
+          <t>Indianapolis, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H102" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Project Planning)</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J102" s="13" t="inlineStr"/>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>Arjan Toebes</t>
+          <t>Eamon Judge</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>EMEA Major Project Planning Leader</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -54815,35 +54933,35 @@
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Ireland (Europe)</t>
+          <t>Ireland (EMEA) (Europe)</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Capital Project Planning)</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J103" s="13" t="inlineStr"/>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>David Eighan</t>
+          <t>Arjan Toebes</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>CQV Planner</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -54891,12 +55009,12 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>Diarmuid Geary</t>
+          <t>David Eighan</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>CQV Downstream</t>
+          <t>CQV Planner</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -54944,12 +55062,12 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>Jamie Hodnett</t>
+          <t>Diarmuid Geary</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>Commissioning Engineer</t>
+          <t>CQV Downstream</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -54997,12 +55115,12 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>Jerry Crowley</t>
+          <t>Jamie Hodnett</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Commissioning Engineer</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
@@ -55032,7 +55150,7 @@
       </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -55050,12 +55168,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>Leo R.</t>
+          <t>Jerry Crowley</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>CQV Consultant</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -55085,7 +55203,7 @@
       </c>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I108" s="13" t="inlineStr">
@@ -55103,12 +55221,12 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>Leonard Sheehan</t>
+          <t>Leo R.</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>CQV Consultant</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -55156,12 +55274,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>Mary O'Mahony</t>
+          <t>Leonard Sheehan</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>Project Process Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
@@ -55191,7 +55309,7 @@
       </c>
       <c r="H110" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Process)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I110" s="13" t="inlineStr">
@@ -55209,12 +55327,12 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>Michael Creswell</t>
+          <t>Mary O'Mahony</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Project Process Engineer</t>
         </is>
       </c>
       <c r="C111" s="13" t="inlineStr">
@@ -55244,7 +55362,7 @@
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Process)</t>
         </is>
       </c>
       <c r="I111" s="13" t="inlineStr">
@@ -55262,12 +55380,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>Michael Robinson</t>
+          <t>Michael Creswell</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
@@ -55297,7 +55415,7 @@
       </c>
       <c r="H112" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I112" s="13" t="inlineStr">
@@ -55315,12 +55433,12 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>Niamh Kingston</t>
+          <t>Michael Robinson</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
@@ -55350,7 +55468,7 @@
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I113" s="13" t="inlineStr">
@@ -55368,12 +55486,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>Paul Linehan</t>
+          <t>Niamh Kingston</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>Engineer - C&amp;Q Strategy</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
@@ -55421,12 +55539,12 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>Stephen O'Farrell</t>
+          <t>Paul Linehan</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Engineer - C&amp;Q Strategy</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
@@ -55474,7 +55592,7 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>Vincent Li</t>
+          <t>Stephen O'Farrell</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
@@ -55527,12 +55645,12 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>Ainhoa Nieto</t>
+          <t>Vincent Li</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>Associate VP, Manufacturing</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
@@ -55540,9 +55658,9 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D117" s="17" t="inlineStr">
-        <is>
-          <t>2. Global / Functional</t>
+      <c r="D117" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
@@ -55550,46 +55668,42 @@
           <t>Engineer / IC</t>
         </is>
       </c>
-      <c r="F117" s="22" t="inlineStr">
-        <is>
-          <t>Tier 2</t>
+      <c r="F117" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>Japan (Global)</t>
+          <t>Ireland (Europe)</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J117" s="13" t="inlineStr">
-        <is>
-          <t>ISPE Facilities of the Future 2026</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J117" s="13" t="inlineStr"/>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>Christopher S.</t>
+          <t>Ainhoa Nieto</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>CQ Project Engineer</t>
+          <t>Associate VP, Manufacturing</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
@@ -55597,9 +55711,9 @@
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D118" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>2. Global / Functional</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
@@ -55607,42 +55721,46 @@
           <t>Engineer / IC</t>
         </is>
       </c>
-      <c r="F118" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
+      <c r="F118" s="22" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>Lebanon, Indiana, United States (US)</t>
+          <t>Japan (Global)</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J118" s="13" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J118" s="13" t="inlineStr">
+        <is>
+          <t>ISPE Facilities of the Future 2026</t>
+        </is>
+      </c>
       <c r="K118" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Manufacturing-adjacent influencer — moderate valve/equipment relevance.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>Barry Sherlock</t>
+          <t>Christopher S.</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer (contracted into Lilly)</t>
+          <t>CQ Project Engineer</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
@@ -55667,12 +55785,12 @@
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>Limerick, County Limerick, Ireland (Europe)</t>
+          <t>Lebanon, Indiana, United States (US)</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Utilities)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I119" s="13" t="inlineStr">
@@ -55683,19 +55801,19 @@
       <c r="J119" s="13" t="inlineStr"/>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>Conor Quinn</t>
+          <t>Barry Sherlock</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>C&amp;Q Engineer (contracted into Lilly)</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
@@ -55725,7 +55843,7 @@
       </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q (Utilities)</t>
         </is>
       </c>
       <c r="I120" s="13" t="inlineStr">
@@ -55736,19 +55854,19 @@
       <c r="J120" s="13" t="inlineStr"/>
       <c r="K120" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>Diana Andrea Rodriguez Diaz</t>
+          <t>Conor Quinn</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
@@ -55778,7 +55896,7 @@
       </c>
       <c r="H121" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I121" s="13" t="inlineStr">
@@ -55796,12 +55914,12 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>Karthick Pachaiyappan</t>
+          <t>Diana Andrea Rodriguez Diaz</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>Project DeltaV Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C122" s="13" t="inlineStr">
@@ -55831,7 +55949,7 @@
       </c>
       <c r="H122" s="13" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I122" s="13" t="inlineStr">
@@ -55849,12 +55967,12 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>Priya Kanekal</t>
+          <t>Karthick Pachaiyappan</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineer</t>
+          <t>Project DeltaV Engineer</t>
         </is>
       </c>
       <c r="C123" s="13" t="inlineStr">
@@ -55884,7 +56002,7 @@
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="I123" s="13" t="inlineStr">
@@ -55902,12 +56020,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>Michael O Halloran</t>
+          <t>Priya Kanekal</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>CQV Engineer</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
@@ -55932,12 +56050,12 @@
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>Limerick, Ireland (Europe)</t>
+          <t>Limerick, County Limerick, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Project)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I124" s="13" t="inlineStr">
@@ -55955,12 +56073,12 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>Eamon Davern</t>
+          <t>Michael O Halloran</t>
         </is>
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>BMS/QBMS CQV Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
@@ -55985,12 +56103,12 @@
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>Mainz, Rhineland-Palatinate, Germany (Europe)</t>
+          <t>Limerick, Ireland (Europe)</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q</t>
+          <t>Engineering (Project)</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -56008,12 +56126,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>Benjamin Kang</t>
+          <t>Eamon Davern</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>C&amp;Q Engineer</t>
+          <t>BMS/QBMS CQV Engineer</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
@@ -56038,7 +56156,7 @@
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>Singapore (Asia)</t>
+          <t>Mainz, Rhineland-Palatinate, Germany (Europe)</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
@@ -56061,7 +56179,7 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>Ardán Quinn</t>
+          <t>Benjamin Kang</t>
         </is>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -56091,7 +56209,7 @@
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>Switzerland (Europe)</t>
+          <t>Singapore (Asia)</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
@@ -56114,12 +56232,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>Carolina Serrano Martinez</t>
+          <t>Ardán Quinn</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>Operations Improvement Engineer</t>
+          <t>C&amp;Q Engineer</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
@@ -56144,17 +56262,17 @@
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>US (Great Lakes region)</t>
+          <t>Switzerland (Europe)</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Operations Improvement)</t>
+          <t>Engineering / C&amp;Q</t>
         </is>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="J128" s="13" t="inlineStr"/>
@@ -56167,12 +56285,12 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>Sasha Adib-Yaghmai</t>
+          <t>Carolina Serrano Martinez</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>NPI Engineer – Capital Projects &amp; Operational Readiness</t>
+          <t>Operations Improvement Engineer</t>
         </is>
       </c>
       <c r="C129" s="13" t="inlineStr">
@@ -56197,35 +56315,35 @@
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>United Kingdom (Europe)</t>
+          <t>US (Great Lakes region)</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t>Engineering (Capital Projects)</t>
+          <t>Engineering (Operations Improvement)</t>
         </is>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J129" s="13" t="inlineStr"/>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>Felipe Rivera-Monserrate</t>
+          <t>Sasha Adib-Yaghmai</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>CQV Engineering Automation Owner's Representative</t>
+          <t>NPI Engineer – Capital Projects &amp; Operational Readiness</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
@@ -56250,12 +56368,12 @@
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>United States (US)</t>
+          <t>United Kingdom (Europe)</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q (Automation)</t>
+          <t>Engineering (Capital Projects)</t>
         </is>
       </c>
       <c r="I130" s="13" t="inlineStr">
@@ -56266,19 +56384,19 @@
       <c r="J130" s="13" t="inlineStr"/>
       <c r="K130" s="14" t="inlineStr">
         <is>
-          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
+          <t>Capital-project delivery — direct owner of valve/equipment spec &amp; procurement on an active build.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>Eamonn Warren</t>
+          <t>Felipe Rivera-Monserrate</t>
         </is>
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>Group VP, API &amp; Dry Products Manufacturing</t>
+          <t>CQV Engineering Automation Owner's Representative</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
@@ -56296,9 +56414,9 @@
           <t>Engineer / IC</t>
         </is>
       </c>
-      <c r="F131" s="16" t="inlineStr">
-        <is>
-          <t>Tier 3</t>
+      <c r="F131" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
@@ -56308,80 +56426,133 @@
       </c>
       <c r="H131" s="13" t="inlineStr">
         <is>
-          <t>API Manufacturing (Executive)</t>
+          <t>Engineering / C&amp;Q (Automation)</t>
         </is>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J131" s="13" t="inlineStr">
-        <is>
-          <t>Pharma Manufacturing World Summit; ISPE Annual</t>
-        </is>
-      </c>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J131" s="13" t="inlineStr"/>
       <c r="K131" s="14" t="inlineStr">
         <is>
-          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+          <t>Engineering / C&amp;Q — specifies and standardises process valves &amp; equipment.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
+          <t>Eamonn Warren</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>Group VP, API &amp; Dry Products Manufacturing</t>
+        </is>
+      </c>
+      <c r="C132" s="13" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="D132" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>Engineer / IC</t>
+        </is>
+      </c>
+      <c r="F132" s="16" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="G132" s="13" t="inlineStr">
+        <is>
+          <t>United States (US)</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t>API Manufacturing (Executive)</t>
+        </is>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J132" s="13" t="inlineStr">
+        <is>
+          <t>Pharma Manufacturing World Summit; ISPE Annual</t>
+        </is>
+      </c>
+      <c r="K132" s="14" t="inlineStr">
+        <is>
+          <t>Executive manufacturing/operations sponsor — budget, direction and executive access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="inlineStr">
+        <is>
           <t>Toni Roman</t>
         </is>
       </c>
-      <c r="B132" s="14" t="inlineStr">
+      <c r="B133" s="14" t="inlineStr">
         <is>
           <t>C&amp;Q HVAC/CR Engineer</t>
         </is>
       </c>
-      <c r="C132" s="13" t="inlineStr">
+      <c r="C133" s="13" t="inlineStr">
         <is>
           <t>Eli Lilly</t>
         </is>
       </c>
-      <c r="D132" s="23" t="inlineStr">
-        <is>
-          <t>3. Site / Working</t>
-        </is>
-      </c>
-      <c r="E132" s="13" t="inlineStr">
+      <c r="D133" s="23" t="inlineStr">
+        <is>
+          <t>3. Site / Working</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
         <is>
           <t>Engineer / IC</t>
         </is>
       </c>
-      <c r="F132" s="20" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="G132" s="13" t="inlineStr">
+      <c r="F133" s="20" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
         <is>
           <t>Zagreb, Croatia (Europe)</t>
         </is>
       </c>
-      <c r="H132" s="13" t="inlineStr">
+      <c r="H133" s="13" t="inlineStr">
         <is>
           <t>Engineering / C&amp;Q (Utilities)</t>
         </is>
       </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>Navigator</t>
-        </is>
-      </c>
-      <c r="J132" s="13" t="inlineStr"/>
-      <c r="K132" s="14" t="inlineStr">
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>Navigator</t>
+        </is>
+      </c>
+      <c r="J133" s="13" t="inlineStr"/>
+      <c r="K133" s="14" t="inlineStr">
         <is>
           <t>Utilities/technical services — owns clean-utility &amp; CIP/SIP systems where diaphragm valves spec in.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K132"/>
+  <autoFilter ref="A1:K133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
